--- a/data/Site_Summary_Master.xlsx
+++ b/data/Site_Summary_Master.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://doimspp-my.sharepoint.com/personal/kbutton_nps_gov/Documents/Katie Button/NCBN/ENE/R_repos/Seagrass-Temp-Resiliency/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{FAF626FD-A2A0-491E-AF7F-B1579B1E1A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E3C2C1A-0FDF-4DE3-91CB-6ED8E47108E3}"/>
+  <xr:revisionPtr revIDLastSave="21" documentId="8_{FAF626FD-A2A0-491E-AF7F-B1579B1E1A14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA778EF2-8546-4B14-89E7-329C34ED4A38}"/>
   <bookViews>
     <workbookView xWindow="-38520" yWindow="0" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{79C877D3-2B70-4D93-9239-27F7DCCAB4D1}"/>
   </bookViews>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1660" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1688" uniqueCount="174">
   <si>
     <t>State</t>
   </si>
@@ -622,6 +622,12 @@
   <si>
     <t>Paramore</t>
   </si>
+  <si>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
 </sst>
 </file>
 
@@ -630,7 +636,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.000"/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -717,6 +723,19 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF242424"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="8">
     <fill>
@@ -774,7 +793,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -819,6 +838,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6352,7 +6374,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4573B4BA-CB31-49B4-ABC2-F6AC4FA62BB7}">
-  <dimension ref="A1:AI193"/>
+  <dimension ref="A1:AI197"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="27.5703125" customWidth="1"/>
@@ -6551,27 +6573,27 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA2" s="21">
-        <f>V2/153</f>
+        <f t="shared" ref="AA2:AA33" si="0">V2/153</f>
         <v>0.68627450980392157</v>
       </c>
       <c r="AB2" s="21">
-        <f>MAX(0, MIN(I2, DATE(YEAR(H2),5,31)) - MAX(H2, DATE(YEAR(H2),5,1)) + 1)</f>
+        <f t="shared" ref="AB2:AB33" si="1">MAX(0, MIN(I2, DATE(YEAR(H2),5,31)) - MAX(H2, DATE(YEAR(H2),5,1)) + 1)</f>
         <v>0</v>
       </c>
       <c r="AC2" s="21">
-        <f>MAX(0, MIN(I2, DATE(YEAR(H2),6,31)) - MAX(H2, DATE(YEAR(H2),6,1)) + 1)</f>
+        <f t="shared" ref="AC2:AC33" si="2">MAX(0, MIN(I2, DATE(YEAR(H2),6,31)) - MAX(H2, DATE(YEAR(H2),6,1)) + 1)</f>
         <v>15</v>
       </c>
       <c r="AD2" s="21">
-        <f>MAX(0, MIN(I2, DATE(YEAR(H2),7,31)) - MAX(H2, DATE(YEAR(H2),7,1)) + 1)</f>
+        <f t="shared" ref="AD2:AD33" si="3">MAX(0, MIN(I2, DATE(YEAR(H2),7,31)) - MAX(H2, DATE(YEAR(H2),7,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AE2" s="21">
-        <f>MAX(0, MIN(I2, DATE(YEAR(H2),8,31)) - MAX(H2, DATE(YEAR(H2),8,1)) + 1)</f>
+        <f t="shared" ref="AE2:AE33" si="4">MAX(0, MIN(I2, DATE(YEAR(H2),8,31)) - MAX(H2, DATE(YEAR(H2),8,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AF2" s="21">
-        <f>MAX(0, MIN(I2, DATE(YEAR(H2),9,31)) - MAX(H2, DATE(YEAR(H2),9,1)) + 1)</f>
+        <f t="shared" ref="AF2:AF33" si="5">MAX(0, MIN(I2, DATE(YEAR(H2),9,31)) - MAX(H2, DATE(YEAR(H2),9,1)) + 1)</f>
         <v>30</v>
       </c>
       <c r="AG2" s="21">
@@ -6664,39 +6686,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA3" s="21">
-        <f>V3/153</f>
+        <f t="shared" si="0"/>
         <v>0.81045751633986929</v>
       </c>
       <c r="AB3" s="21">
-        <f>MAX(0, MIN(I3, DATE(YEAR(H3),5,31)) - MAX(H3, DATE(YEAR(H3),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC3" s="21">
-        <f>MAX(0, MIN(I3, DATE(YEAR(H3),6,31)) - MAX(H3, DATE(YEAR(H3),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD3" s="21">
-        <f>MAX(0, MIN(I3, DATE(YEAR(H3),7,31)) - MAX(H3, DATE(YEAR(H3),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE3" s="21">
-        <f>MAX(0, MIN(I3, DATE(YEAR(H3),8,31)) - MAX(H3, DATE(YEAR(H3),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF3" s="21">
-        <f>MAX(0, MIN(I3, DATE(YEAR(H3),9,31)) - MAX(H3, DATE(YEAR(H3),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AG3" s="21">
-        <f t="shared" ref="AG3:AG66" si="0">COUNTIF(AB3:AF3, "&gt;=10")</f>
+        <f t="shared" ref="AG3:AG66" si="6">COUNTIF(AB3:AF3, "&gt;=10")</f>
         <v>4</v>
       </c>
       <c r="AH3" s="21" t="str">
-        <f t="shared" ref="AH3:AH66" si="1">IF(COUNTIF(AB3:AF3,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
+        <f t="shared" ref="AH3:AH66" si="7">IF(COUNTIF(AB3:AF3,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="AI3" s="21" t="str">
-        <f t="shared" ref="AI3:AI66" si="2">IF(AND(AA3&gt;=0.8, COUNTIF(AB3:AF3, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
+        <f t="shared" ref="AI3:AI66" si="8">IF(AND(AA3&gt;=0.8, COUNTIF(AB3:AF3, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -6777,39 +6799,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA4" s="21">
-        <f>V4/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB4" s="21">
-        <f>MAX(0, MIN(I4, DATE(YEAR(H4),5,31)) - MAX(H4, DATE(YEAR(H4),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC4" s="21">
-        <f>MAX(0, MIN(I4, DATE(YEAR(H4),6,31)) - MAX(H4, DATE(YEAR(H4),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD4" s="21">
-        <f>MAX(0, MIN(I4, DATE(YEAR(H4),7,31)) - MAX(H4, DATE(YEAR(H4),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE4" s="21">
-        <f>MAX(0, MIN(I4, DATE(YEAR(H4),8,31)) - MAX(H4, DATE(YEAR(H4),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF4" s="21">
-        <f>MAX(0, MIN(I4, DATE(YEAR(H4),9,31)) - MAX(H4, DATE(YEAR(H4),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG4" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH4" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI4" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -6890,39 +6912,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA5" s="21">
-        <f>V5/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB5" s="21">
-        <f>MAX(0, MIN(I5, DATE(YEAR(H5),5,31)) - MAX(H5, DATE(YEAR(H5),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC5" s="21">
-        <f>MAX(0, MIN(I5, DATE(YEAR(H5),6,31)) - MAX(H5, DATE(YEAR(H5),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD5" s="21">
-        <f>MAX(0, MIN(I5, DATE(YEAR(H5),7,31)) - MAX(H5, DATE(YEAR(H5),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE5" s="21">
-        <f>MAX(0, MIN(I5, DATE(YEAR(H5),8,31)) - MAX(H5, DATE(YEAR(H5),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF5" s="21">
-        <f>MAX(0, MIN(I5, DATE(YEAR(H5),9,31)) - MAX(H5, DATE(YEAR(H5),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG5" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH5" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI5" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -7003,39 +7025,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA6" s="21">
-        <f>V6/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB6" s="21">
-        <f>MAX(0, MIN(I6, DATE(YEAR(H6),5,31)) - MAX(H6, DATE(YEAR(H6),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC6" s="21">
-        <f>MAX(0, MIN(I6, DATE(YEAR(H6),6,31)) - MAX(H6, DATE(YEAR(H6),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD6" s="21">
-        <f>MAX(0, MIN(I6, DATE(YEAR(H6),7,31)) - MAX(H6, DATE(YEAR(H6),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE6" s="21">
-        <f>MAX(0, MIN(I6, DATE(YEAR(H6),8,31)) - MAX(H6, DATE(YEAR(H6),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF6" s="21">
-        <f>MAX(0, MIN(I6, DATE(YEAR(H6),9,31)) - MAX(H6, DATE(YEAR(H6),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG6" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH6" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI6" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -7116,39 +7138,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA7" s="21">
-        <f>V7/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB7" s="21">
-        <f>MAX(0, MIN(I7, DATE(YEAR(H7),5,31)) - MAX(H7, DATE(YEAR(H7),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC7" s="21">
-        <f>MAX(0, MIN(I7, DATE(YEAR(H7),6,31)) - MAX(H7, DATE(YEAR(H7),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD7" s="21">
-        <f>MAX(0, MIN(I7, DATE(YEAR(H7),7,31)) - MAX(H7, DATE(YEAR(H7),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE7" s="21">
-        <f>MAX(0, MIN(I7, DATE(YEAR(H7),8,31)) - MAX(H7, DATE(YEAR(H7),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF7" s="21">
-        <f>MAX(0, MIN(I7, DATE(YEAR(H7),9,31)) - MAX(H7, DATE(YEAR(H7),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG7" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH7" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI7" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -7229,39 +7251,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA8" s="21">
-        <f>V8/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB8" s="21">
-        <f>MAX(0, MIN(I8, DATE(YEAR(H8),5,31)) - MAX(H8, DATE(YEAR(H8),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC8" s="21">
-        <f>MAX(0, MIN(I8, DATE(YEAR(H8),6,31)) - MAX(H8, DATE(YEAR(H8),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD8" s="21">
-        <f>MAX(0, MIN(I8, DATE(YEAR(H8),7,31)) - MAX(H8, DATE(YEAR(H8),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE8" s="21">
-        <f>MAX(0, MIN(I8, DATE(YEAR(H8),8,31)) - MAX(H8, DATE(YEAR(H8),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF8" s="21">
-        <f>MAX(0, MIN(I8, DATE(YEAR(H8),9,31)) - MAX(H8, DATE(YEAR(H8),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG8" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH8" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI8" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -7342,39 +7364,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA9" s="21">
-        <f>V9/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB9" s="21">
-        <f>MAX(0, MIN(I9, DATE(YEAR(H9),5,31)) - MAX(H9, DATE(YEAR(H9),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC9" s="21">
-        <f>MAX(0, MIN(I9, DATE(YEAR(H9),6,31)) - MAX(H9, DATE(YEAR(H9),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD9" s="21">
-        <f>MAX(0, MIN(I9, DATE(YEAR(H9),7,31)) - MAX(H9, DATE(YEAR(H9),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE9" s="21">
-        <f>MAX(0, MIN(I9, DATE(YEAR(H9),8,31)) - MAX(H9, DATE(YEAR(H9),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF9" s="21">
-        <f>MAX(0, MIN(I9, DATE(YEAR(H9),9,31)) - MAX(H9, DATE(YEAR(H9),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG9" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH9" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI9" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -7455,39 +7477,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA10" s="21">
-        <f>V10/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB10" s="21">
-        <f>MAX(0, MIN(I10, DATE(YEAR(H10),5,31)) - MAX(H10, DATE(YEAR(H10),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC10" s="21">
-        <f>MAX(0, MIN(I10, DATE(YEAR(H10),6,31)) - MAX(H10, DATE(YEAR(H10),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD10" s="21">
-        <f>MAX(0, MIN(I10, DATE(YEAR(H10),7,31)) - MAX(H10, DATE(YEAR(H10),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE10" s="21">
-        <f>MAX(0, MIN(I10, DATE(YEAR(H10),8,31)) - MAX(H10, DATE(YEAR(H10),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF10" s="21">
-        <f>MAX(0, MIN(I10, DATE(YEAR(H10),9,31)) - MAX(H10, DATE(YEAR(H10),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG10" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH10" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI10" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -7568,39 +7590,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA11" s="21">
-        <f>V11/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB11" s="21">
-        <f>MAX(0, MIN(I11, DATE(YEAR(H11),5,31)) - MAX(H11, DATE(YEAR(H11),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC11" s="21">
-        <f>MAX(0, MIN(I11, DATE(YEAR(H11),6,31)) - MAX(H11, DATE(YEAR(H11),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD11" s="21">
-        <f>MAX(0, MIN(I11, DATE(YEAR(H11),7,31)) - MAX(H11, DATE(YEAR(H11),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE11" s="21">
-        <f>MAX(0, MIN(I11, DATE(YEAR(H11),8,31)) - MAX(H11, DATE(YEAR(H11),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF11" s="21">
-        <f>MAX(0, MIN(I11, DATE(YEAR(H11),9,31)) - MAX(H11, DATE(YEAR(H11),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG11" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH11" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI11" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -7681,39 +7703,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA12" s="21">
-        <f>V12/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB12" s="21">
-        <f>MAX(0, MIN(I12, DATE(YEAR(H12),5,31)) - MAX(H12, DATE(YEAR(H12),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC12" s="21">
-        <f>MAX(0, MIN(I12, DATE(YEAR(H12),6,31)) - MAX(H12, DATE(YEAR(H12),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD12" s="21">
-        <f>MAX(0, MIN(I12, DATE(YEAR(H12),7,31)) - MAX(H12, DATE(YEAR(H12),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE12" s="21">
-        <f>MAX(0, MIN(I12, DATE(YEAR(H12),8,31)) - MAX(H12, DATE(YEAR(H12),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF12" s="21">
-        <f>MAX(0, MIN(I12, DATE(YEAR(H12),9,31)) - MAX(H12, DATE(YEAR(H12),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG12" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH12" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI12" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -7794,39 +7816,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA13" s="21">
-        <f>V13/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB13" s="21">
-        <f>MAX(0, MIN(I13, DATE(YEAR(H13),5,31)) - MAX(H13, DATE(YEAR(H13),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC13" s="21">
-        <f>MAX(0, MIN(I13, DATE(YEAR(H13),6,31)) - MAX(H13, DATE(YEAR(H13),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD13" s="21">
-        <f>MAX(0, MIN(I13, DATE(YEAR(H13),7,31)) - MAX(H13, DATE(YEAR(H13),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE13" s="21">
-        <f>MAX(0, MIN(I13, DATE(YEAR(H13),8,31)) - MAX(H13, DATE(YEAR(H13),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF13" s="21">
-        <f>MAX(0, MIN(I13, DATE(YEAR(H13),9,31)) - MAX(H13, DATE(YEAR(H13),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG13" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH13" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI13" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -7907,39 +7929,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA14" s="21">
-        <f>V14/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB14" s="21">
-        <f>MAX(0, MIN(I14, DATE(YEAR(H14),5,31)) - MAX(H14, DATE(YEAR(H14),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC14" s="21">
-        <f>MAX(0, MIN(I14, DATE(YEAR(H14),6,31)) - MAX(H14, DATE(YEAR(H14),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD14" s="21">
-        <f>MAX(0, MIN(I14, DATE(YEAR(H14),7,31)) - MAX(H14, DATE(YEAR(H14),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE14" s="21">
-        <f>MAX(0, MIN(I14, DATE(YEAR(H14),8,31)) - MAX(H14, DATE(YEAR(H14),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF14" s="21">
-        <f>MAX(0, MIN(I14, DATE(YEAR(H14),9,31)) - MAX(H14, DATE(YEAR(H14),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG14" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH14" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI14" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -8020,39 +8042,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA15" s="21">
-        <f>V15/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB15" s="21">
-        <f>MAX(0, MIN(I15, DATE(YEAR(H15),5,31)) - MAX(H15, DATE(YEAR(H15),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC15" s="21">
-        <f>MAX(0, MIN(I15, DATE(YEAR(H15),6,31)) - MAX(H15, DATE(YEAR(H15),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD15" s="21">
-        <f>MAX(0, MIN(I15, DATE(YEAR(H15),7,31)) - MAX(H15, DATE(YEAR(H15),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE15" s="21">
-        <f>MAX(0, MIN(I15, DATE(YEAR(H15),8,31)) - MAX(H15, DATE(YEAR(H15),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF15" s="21">
-        <f>MAX(0, MIN(I15, DATE(YEAR(H15),9,31)) - MAX(H15, DATE(YEAR(H15),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG15" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH15" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI15" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -8133,39 +8155,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA16" s="21">
-        <f>V16/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB16" s="21">
-        <f>MAX(0, MIN(I16, DATE(YEAR(H16),5,31)) - MAX(H16, DATE(YEAR(H16),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC16" s="21">
-        <f>MAX(0, MIN(I16, DATE(YEAR(H16),6,31)) - MAX(H16, DATE(YEAR(H16),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD16" s="21">
-        <f>MAX(0, MIN(I16, DATE(YEAR(H16),7,31)) - MAX(H16, DATE(YEAR(H16),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE16" s="21">
-        <f>MAX(0, MIN(I16, DATE(YEAR(H16),8,31)) - MAX(H16, DATE(YEAR(H16),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF16" s="21">
-        <f>MAX(0, MIN(I16, DATE(YEAR(H16),9,31)) - MAX(H16, DATE(YEAR(H16),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG16" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH16" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI16" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -8246,39 +8268,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA17" s="21">
-        <f>V17/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB17" s="21">
-        <f>MAX(0, MIN(I17, DATE(YEAR(H17),5,31)) - MAX(H17, DATE(YEAR(H17),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC17" s="21">
-        <f>MAX(0, MIN(I17, DATE(YEAR(H17),6,31)) - MAX(H17, DATE(YEAR(H17),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD17" s="21">
-        <f>MAX(0, MIN(I17, DATE(YEAR(H17),7,31)) - MAX(H17, DATE(YEAR(H17),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE17" s="21">
-        <f>MAX(0, MIN(I17, DATE(YEAR(H17),8,31)) - MAX(H17, DATE(YEAR(H17),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF17" s="21">
-        <f>MAX(0, MIN(I17, DATE(YEAR(H17),9,31)) - MAX(H17, DATE(YEAR(H17),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG17" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH17" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI17" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -8359,39 +8381,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA18" s="21">
-        <f>V18/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB18" s="21">
-        <f>MAX(0, MIN(I18, DATE(YEAR(H18),5,31)) - MAX(H18, DATE(YEAR(H18),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC18" s="21">
-        <f>MAX(0, MIN(I18, DATE(YEAR(H18),6,31)) - MAX(H18, DATE(YEAR(H18),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD18" s="21">
-        <f>MAX(0, MIN(I18, DATE(YEAR(H18),7,31)) - MAX(H18, DATE(YEAR(H18),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE18" s="21">
-        <f>MAX(0, MIN(I18, DATE(YEAR(H18),8,31)) - MAX(H18, DATE(YEAR(H18),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF18" s="21">
-        <f>MAX(0, MIN(I18, DATE(YEAR(H18),9,31)) - MAX(H18, DATE(YEAR(H18),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG18" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH18" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI18" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -8472,39 +8494,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA19" s="21">
-        <f>V19/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB19" s="21">
-        <f>MAX(0, MIN(I19, DATE(YEAR(H19),5,31)) - MAX(H19, DATE(YEAR(H19),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC19" s="21">
-        <f>MAX(0, MIN(I19, DATE(YEAR(H19),6,31)) - MAX(H19, DATE(YEAR(H19),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD19" s="21">
-        <f>MAX(0, MIN(I19, DATE(YEAR(H19),7,31)) - MAX(H19, DATE(YEAR(H19),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE19" s="21">
-        <f>MAX(0, MIN(I19, DATE(YEAR(H19),8,31)) - MAX(H19, DATE(YEAR(H19),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF19" s="21">
-        <f>MAX(0, MIN(I19, DATE(YEAR(H19),9,31)) - MAX(H19, DATE(YEAR(H19),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG19" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH19" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI19" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -8585,39 +8607,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA20" s="21">
-        <f>V20/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB20" s="21">
-        <f>MAX(0, MIN(I20, DATE(YEAR(H20),5,31)) - MAX(H20, DATE(YEAR(H20),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC20" s="21">
-        <f>MAX(0, MIN(I20, DATE(YEAR(H20),6,31)) - MAX(H20, DATE(YEAR(H20),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD20" s="21">
-        <f>MAX(0, MIN(I20, DATE(YEAR(H20),7,31)) - MAX(H20, DATE(YEAR(H20),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE20" s="21">
-        <f>MAX(0, MIN(I20, DATE(YEAR(H20),8,31)) - MAX(H20, DATE(YEAR(H20),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF20" s="21">
-        <f>MAX(0, MIN(I20, DATE(YEAR(H20),9,31)) - MAX(H20, DATE(YEAR(H20),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG20" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH20" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI20" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -8698,39 +8720,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA21" s="21">
-        <f>V21/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB21" s="21">
-        <f>MAX(0, MIN(I21, DATE(YEAR(H21),5,31)) - MAX(H21, DATE(YEAR(H21),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC21" s="21">
-        <f>MAX(0, MIN(I21, DATE(YEAR(H21),6,31)) - MAX(H21, DATE(YEAR(H21),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD21" s="21">
-        <f>MAX(0, MIN(I21, DATE(YEAR(H21),7,31)) - MAX(H21, DATE(YEAR(H21),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE21" s="21">
-        <f>MAX(0, MIN(I21, DATE(YEAR(H21),8,31)) - MAX(H21, DATE(YEAR(H21),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF21" s="21">
-        <f>MAX(0, MIN(I21, DATE(YEAR(H21),9,31)) - MAX(H21, DATE(YEAR(H21),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG21" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH21" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI21" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -8811,39 +8833,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA22" s="21">
-        <f>V22/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB22" s="21">
-        <f>MAX(0, MIN(I22, DATE(YEAR(H22),5,31)) - MAX(H22, DATE(YEAR(H22),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC22" s="21">
-        <f>MAX(0, MIN(I22, DATE(YEAR(H22),6,31)) - MAX(H22, DATE(YEAR(H22),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD22" s="21">
-        <f>MAX(0, MIN(I22, DATE(YEAR(H22),7,31)) - MAX(H22, DATE(YEAR(H22),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE22" s="21">
-        <f>MAX(0, MIN(I22, DATE(YEAR(H22),8,31)) - MAX(H22, DATE(YEAR(H22),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF22" s="21">
-        <f>MAX(0, MIN(I22, DATE(YEAR(H22),9,31)) - MAX(H22, DATE(YEAR(H22),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG22" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH22" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI22" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -8924,39 +8946,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA23" s="21">
-        <f>V23/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB23" s="21">
-        <f>MAX(0, MIN(I23, DATE(YEAR(H23),5,31)) - MAX(H23, DATE(YEAR(H23),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC23" s="21">
-        <f>MAX(0, MIN(I23, DATE(YEAR(H23),6,31)) - MAX(H23, DATE(YEAR(H23),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD23" s="21">
-        <f>MAX(0, MIN(I23, DATE(YEAR(H23),7,31)) - MAX(H23, DATE(YEAR(H23),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE23" s="21">
-        <f>MAX(0, MIN(I23, DATE(YEAR(H23),8,31)) - MAX(H23, DATE(YEAR(H23),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF23" s="21">
-        <f>MAX(0, MIN(I23, DATE(YEAR(H23),9,31)) - MAX(H23, DATE(YEAR(H23),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG23" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH23" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI23" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -9037,39 +9059,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA24" s="21">
-        <f>V24/153</f>
+        <f t="shared" si="0"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="AB24" s="21">
-        <f>MAX(0, MIN(I24, DATE(YEAR(H24),5,31)) - MAX(H24, DATE(YEAR(H24),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC24" s="21">
-        <f>MAX(0, MIN(I24, DATE(YEAR(H24),6,31)) - MAX(H24, DATE(YEAR(H24),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD24" s="21">
-        <f>MAX(0, MIN(I24, DATE(YEAR(H24),7,31)) - MAX(H24, DATE(YEAR(H24),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="AE24" s="21">
-        <f>MAX(0, MIN(I24, DATE(YEAR(H24),8,31)) - MAX(H24, DATE(YEAR(H24),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF24" s="21">
-        <f>MAX(0, MIN(I24, DATE(YEAR(H24),9,31)) - MAX(H24, DATE(YEAR(H24),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AG24" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="AH24" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI24" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -9150,39 +9172,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA25" s="21">
-        <f>V25/153</f>
+        <f t="shared" si="0"/>
         <v>0.45751633986928103</v>
       </c>
       <c r="AB25" s="21">
-        <f>MAX(0, MIN(I25, DATE(YEAR(H25),5,31)) - MAX(H25, DATE(YEAR(H25),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC25" s="21">
-        <f>MAX(0, MIN(I25, DATE(YEAR(H25),6,31)) - MAX(H25, DATE(YEAR(H25),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="AD25" s="21">
-        <f>MAX(0, MIN(I25, DATE(YEAR(H25),7,31)) - MAX(H25, DATE(YEAR(H25),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>9</v>
       </c>
       <c r="AE25" s="21">
-        <f>MAX(0, MIN(I25, DATE(YEAR(H25),8,31)) - MAX(H25, DATE(YEAR(H25),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF25" s="21">
-        <f>MAX(0, MIN(I25, DATE(YEAR(H25),9,31)) - MAX(H25, DATE(YEAR(H25),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG25" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="AH25" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>FAIL</v>
       </c>
       <c r="AI25" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -9263,39 +9285,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA26" s="21">
-        <f>V26/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB26" s="21">
-        <f>MAX(0, MIN(I26, DATE(YEAR(H26),5,31)) - MAX(H26, DATE(YEAR(H26),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC26" s="21">
-        <f>MAX(0, MIN(I26, DATE(YEAR(H26),6,31)) - MAX(H26, DATE(YEAR(H26),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD26" s="21">
-        <f>MAX(0, MIN(I26, DATE(YEAR(H26),7,31)) - MAX(H26, DATE(YEAR(H26),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE26" s="21">
-        <f>MAX(0, MIN(I26, DATE(YEAR(H26),8,31)) - MAX(H26, DATE(YEAR(H26),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF26" s="21">
-        <f>MAX(0, MIN(I26, DATE(YEAR(H26),9,31)) - MAX(H26, DATE(YEAR(H26),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG26" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH26" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI26" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -9376,39 +9398,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA27" s="21">
-        <f>V27/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB27" s="21">
-        <f>MAX(0, MIN(I27, DATE(YEAR(H27),5,31)) - MAX(H27, DATE(YEAR(H27),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC27" s="21">
-        <f>MAX(0, MIN(I27, DATE(YEAR(H27),6,31)) - MAX(H27, DATE(YEAR(H27),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD27" s="21">
-        <f>MAX(0, MIN(I27, DATE(YEAR(H27),7,31)) - MAX(H27, DATE(YEAR(H27),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE27" s="21">
-        <f>MAX(0, MIN(I27, DATE(YEAR(H27),8,31)) - MAX(H27, DATE(YEAR(H27),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF27" s="21">
-        <f>MAX(0, MIN(I27, DATE(YEAR(H27),9,31)) - MAX(H27, DATE(YEAR(H27),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG27" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH27" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI27" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -9489,39 +9511,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA28" s="21">
-        <f>V28/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB28" s="21">
-        <f>MAX(0, MIN(I28, DATE(YEAR(H28),5,31)) - MAX(H28, DATE(YEAR(H28),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC28" s="21">
-        <f>MAX(0, MIN(I28, DATE(YEAR(H28),6,31)) - MAX(H28, DATE(YEAR(H28),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD28" s="21">
-        <f>MAX(0, MIN(I28, DATE(YEAR(H28),7,31)) - MAX(H28, DATE(YEAR(H28),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE28" s="21">
-        <f>MAX(0, MIN(I28, DATE(YEAR(H28),8,31)) - MAX(H28, DATE(YEAR(H28),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF28" s="21">
-        <f>MAX(0, MIN(I28, DATE(YEAR(H28),9,31)) - MAX(H28, DATE(YEAR(H28),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG28" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH28" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI28" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -9602,39 +9624,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA29" s="21">
-        <f>V29/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB29" s="21">
-        <f>MAX(0, MIN(I29, DATE(YEAR(H29),5,31)) - MAX(H29, DATE(YEAR(H29),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC29" s="21">
-        <f>MAX(0, MIN(I29, DATE(YEAR(H29),6,31)) - MAX(H29, DATE(YEAR(H29),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD29" s="21">
-        <f>MAX(0, MIN(I29, DATE(YEAR(H29),7,31)) - MAX(H29, DATE(YEAR(H29),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE29" s="21">
-        <f>MAX(0, MIN(I29, DATE(YEAR(H29),8,31)) - MAX(H29, DATE(YEAR(H29),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF29" s="21">
-        <f>MAX(0, MIN(I29, DATE(YEAR(H29),9,31)) - MAX(H29, DATE(YEAR(H29),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG29" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH29" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI29" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -9715,39 +9737,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA30" s="21">
-        <f>V30/153</f>
+        <f t="shared" si="0"/>
         <v>0.58823529411764708</v>
       </c>
       <c r="AB30" s="21">
-        <f>MAX(0, MIN(I30, DATE(YEAR(H30),5,31)) - MAX(H30, DATE(YEAR(H30),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC30" s="21">
-        <f>MAX(0, MIN(I30, DATE(YEAR(H30),6,31)) - MAX(H30, DATE(YEAR(H30),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD30" s="21">
-        <f>MAX(0, MIN(I30, DATE(YEAR(H30),7,31)) - MAX(H30, DATE(YEAR(H30),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>29</v>
       </c>
       <c r="AE30" s="21">
-        <f>MAX(0, MIN(I30, DATE(YEAR(H30),8,31)) - MAX(H30, DATE(YEAR(H30),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="AF30" s="21">
-        <f>MAX(0, MIN(I30, DATE(YEAR(H30),9,31)) - MAX(H30, DATE(YEAR(H30),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="AG30" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="AH30" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI30" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -9828,39 +9850,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA31" s="21">
-        <f>V31/153</f>
+        <f t="shared" si="0"/>
         <v>0.68627450980392157</v>
       </c>
       <c r="AB31" s="21">
-        <f>MAX(0, MIN(I31, DATE(YEAR(H31),5,31)) - MAX(H31, DATE(YEAR(H31),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="AC31" s="21">
-        <f>MAX(0, MIN(I31, DATE(YEAR(H31),6,31)) - MAX(H31, DATE(YEAR(H31),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>15</v>
       </c>
       <c r="AD31" s="21">
-        <f>MAX(0, MIN(I31, DATE(YEAR(H31),7,31)) - MAX(H31, DATE(YEAR(H31),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE31" s="21">
-        <f>MAX(0, MIN(I31, DATE(YEAR(H31),8,31)) - MAX(H31, DATE(YEAR(H31),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF31" s="21">
-        <f>MAX(0, MIN(I31, DATE(YEAR(H31),9,31)) - MAX(H31, DATE(YEAR(H31),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG31" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="AH31" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI31" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -9941,39 +9963,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA32" s="21">
-        <f>V32/153</f>
+        <f t="shared" si="0"/>
         <v>0.81045751633986929</v>
       </c>
       <c r="AB32" s="21">
-        <f>MAX(0, MIN(I32, DATE(YEAR(H32),5,31)) - MAX(H32, DATE(YEAR(H32),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC32" s="21">
-        <f>MAX(0, MIN(I32, DATE(YEAR(H32),6,31)) - MAX(H32, DATE(YEAR(H32),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD32" s="21">
-        <f>MAX(0, MIN(I32, DATE(YEAR(H32),7,31)) - MAX(H32, DATE(YEAR(H32),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE32" s="21">
-        <f>MAX(0, MIN(I32, DATE(YEAR(H32),8,31)) - MAX(H32, DATE(YEAR(H32),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF32" s="21">
-        <f>MAX(0, MIN(I32, DATE(YEAR(H32),9,31)) - MAX(H32, DATE(YEAR(H32),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="AG32" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="AH32" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI32" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -10054,39 +10076,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA33" s="21">
-        <f>V33/153</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="AB33" s="21">
-        <f>MAX(0, MIN(I33, DATE(YEAR(H33),5,31)) - MAX(H33, DATE(YEAR(H33),5,1)) + 1)</f>
+        <f t="shared" si="1"/>
         <v>31</v>
       </c>
       <c r="AC33" s="21">
-        <f>MAX(0, MIN(I33, DATE(YEAR(H33),6,31)) - MAX(H33, DATE(YEAR(H33),6,1)) + 1)</f>
+        <f t="shared" si="2"/>
         <v>31</v>
       </c>
       <c r="AD33" s="21">
-        <f>MAX(0, MIN(I33, DATE(YEAR(H33),7,31)) - MAX(H33, DATE(YEAR(H33),7,1)) + 1)</f>
+        <f t="shared" si="3"/>
         <v>31</v>
       </c>
       <c r="AE33" s="21">
-        <f>MAX(0, MIN(I33, DATE(YEAR(H33),8,31)) - MAX(H33, DATE(YEAR(H33),8,1)) + 1)</f>
+        <f t="shared" si="4"/>
         <v>31</v>
       </c>
       <c r="AF33" s="21">
-        <f>MAX(0, MIN(I33, DATE(YEAR(H33),9,31)) - MAX(H33, DATE(YEAR(H33),9,1)) + 1)</f>
+        <f t="shared" si="5"/>
         <v>30</v>
       </c>
       <c r="AG33" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH33" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI33" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -10167,39 +10189,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA34" s="21">
-        <f>V34/153</f>
+        <f t="shared" ref="AA34:AA65" si="9">V34/153</f>
         <v>1</v>
       </c>
       <c r="AB34" s="21">
-        <f>MAX(0, MIN(I34, DATE(YEAR(H34),5,31)) - MAX(H34, DATE(YEAR(H34),5,1)) + 1)</f>
+        <f t="shared" ref="AB34:AB65" si="10">MAX(0, MIN(I34, DATE(YEAR(H34),5,31)) - MAX(H34, DATE(YEAR(H34),5,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AC34" s="21">
-        <f>MAX(0, MIN(I34, DATE(YEAR(H34),6,31)) - MAX(H34, DATE(YEAR(H34),6,1)) + 1)</f>
+        <f t="shared" ref="AC34:AC65" si="11">MAX(0, MIN(I34, DATE(YEAR(H34),6,31)) - MAX(H34, DATE(YEAR(H34),6,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AD34" s="21">
-        <f>MAX(0, MIN(I34, DATE(YEAR(H34),7,31)) - MAX(H34, DATE(YEAR(H34),7,1)) + 1)</f>
+        <f t="shared" ref="AD34:AD65" si="12">MAX(0, MIN(I34, DATE(YEAR(H34),7,31)) - MAX(H34, DATE(YEAR(H34),7,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AE34" s="21">
-        <f>MAX(0, MIN(I34, DATE(YEAR(H34),8,31)) - MAX(H34, DATE(YEAR(H34),8,1)) + 1)</f>
+        <f t="shared" ref="AE34:AE65" si="13">MAX(0, MIN(I34, DATE(YEAR(H34),8,31)) - MAX(H34, DATE(YEAR(H34),8,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AF34" s="21">
-        <f>MAX(0, MIN(I34, DATE(YEAR(H34),9,31)) - MAX(H34, DATE(YEAR(H34),9,1)) + 1)</f>
+        <f t="shared" ref="AF34:AF65" si="14">MAX(0, MIN(I34, DATE(YEAR(H34),9,31)) - MAX(H34, DATE(YEAR(H34),9,1)) + 1)</f>
         <v>30</v>
       </c>
       <c r="AG34" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH34" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI34" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -10280,39 +10302,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA35" s="21">
-        <f>V35/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB35" s="21">
-        <f>MAX(0, MIN(I35, DATE(YEAR(H35),5,31)) - MAX(H35, DATE(YEAR(H35),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC35" s="21">
-        <f>MAX(0, MIN(I35, DATE(YEAR(H35),6,31)) - MAX(H35, DATE(YEAR(H35),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD35" s="21">
-        <f>MAX(0, MIN(I35, DATE(YEAR(H35),7,31)) - MAX(H35, DATE(YEAR(H35),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE35" s="21">
-        <f>MAX(0, MIN(I35, DATE(YEAR(H35),8,31)) - MAX(H35, DATE(YEAR(H35),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF35" s="21">
-        <f>MAX(0, MIN(I35, DATE(YEAR(H35),9,31)) - MAX(H35, DATE(YEAR(H35),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG35" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH35" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI35" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -10393,39 +10415,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA36" s="21">
-        <f>V36/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB36" s="21">
-        <f>MAX(0, MIN(I36, DATE(YEAR(H36),5,31)) - MAX(H36, DATE(YEAR(H36),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC36" s="21">
-        <f>MAX(0, MIN(I36, DATE(YEAR(H36),6,31)) - MAX(H36, DATE(YEAR(H36),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD36" s="21">
-        <f>MAX(0, MIN(I36, DATE(YEAR(H36),7,31)) - MAX(H36, DATE(YEAR(H36),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE36" s="21">
-        <f>MAX(0, MIN(I36, DATE(YEAR(H36),8,31)) - MAX(H36, DATE(YEAR(H36),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF36" s="21">
-        <f>MAX(0, MIN(I36, DATE(YEAR(H36),9,31)) - MAX(H36, DATE(YEAR(H36),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG36" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH36" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI36" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -10506,39 +10528,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA37" s="21">
-        <f>V37/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB37" s="21">
-        <f>MAX(0, MIN(I37, DATE(YEAR(H37),5,31)) - MAX(H37, DATE(YEAR(H37),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC37" s="21">
-        <f>MAX(0, MIN(I37, DATE(YEAR(H37),6,31)) - MAX(H37, DATE(YEAR(H37),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD37" s="21">
-        <f>MAX(0, MIN(I37, DATE(YEAR(H37),7,31)) - MAX(H37, DATE(YEAR(H37),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE37" s="21">
-        <f>MAX(0, MIN(I37, DATE(YEAR(H37),8,31)) - MAX(H37, DATE(YEAR(H37),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF37" s="21">
-        <f>MAX(0, MIN(I37, DATE(YEAR(H37),9,31)) - MAX(H37, DATE(YEAR(H37),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG37" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH37" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI37" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -10619,39 +10641,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA38" s="21">
-        <f>V38/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB38" s="21">
-        <f>MAX(0, MIN(I38, DATE(YEAR(H38),5,31)) - MAX(H38, DATE(YEAR(H38),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC38" s="21">
-        <f>MAX(0, MIN(I38, DATE(YEAR(H38),6,31)) - MAX(H38, DATE(YEAR(H38),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD38" s="21">
-        <f>MAX(0, MIN(I38, DATE(YEAR(H38),7,31)) - MAX(H38, DATE(YEAR(H38),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE38" s="21">
-        <f>MAX(0, MIN(I38, DATE(YEAR(H38),8,31)) - MAX(H38, DATE(YEAR(H38),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF38" s="21">
-        <f>MAX(0, MIN(I38, DATE(YEAR(H38),9,31)) - MAX(H38, DATE(YEAR(H38),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG38" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH38" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI38" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -10732,39 +10754,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA39" s="21">
-        <f>V39/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB39" s="21">
-        <f>MAX(0, MIN(I39, DATE(YEAR(H39),5,31)) - MAX(H39, DATE(YEAR(H39),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC39" s="21">
-        <f>MAX(0, MIN(I39, DATE(YEAR(H39),6,31)) - MAX(H39, DATE(YEAR(H39),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD39" s="21">
-        <f>MAX(0, MIN(I39, DATE(YEAR(H39),7,31)) - MAX(H39, DATE(YEAR(H39),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE39" s="21">
-        <f>MAX(0, MIN(I39, DATE(YEAR(H39),8,31)) - MAX(H39, DATE(YEAR(H39),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF39" s="21">
-        <f>MAX(0, MIN(I39, DATE(YEAR(H39),9,31)) - MAX(H39, DATE(YEAR(H39),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG39" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH39" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI39" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -10845,39 +10867,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA40" s="21">
-        <f>V40/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB40" s="21">
-        <f>MAX(0, MIN(I40, DATE(YEAR(H40),5,31)) - MAX(H40, DATE(YEAR(H40),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC40" s="21">
-        <f>MAX(0, MIN(I40, DATE(YEAR(H40),6,31)) - MAX(H40, DATE(YEAR(H40),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD40" s="21">
-        <f>MAX(0, MIN(I40, DATE(YEAR(H40),7,31)) - MAX(H40, DATE(YEAR(H40),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE40" s="21">
-        <f>MAX(0, MIN(I40, DATE(YEAR(H40),8,31)) - MAX(H40, DATE(YEAR(H40),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF40" s="21">
-        <f>MAX(0, MIN(I40, DATE(YEAR(H40),9,31)) - MAX(H40, DATE(YEAR(H40),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG40" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH40" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI40" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -10958,39 +10980,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA41" s="21">
-        <f>V41/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB41" s="21">
-        <f>MAX(0, MIN(I41, DATE(YEAR(H41),5,31)) - MAX(H41, DATE(YEAR(H41),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC41" s="21">
-        <f>MAX(0, MIN(I41, DATE(YEAR(H41),6,31)) - MAX(H41, DATE(YEAR(H41),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD41" s="21">
-        <f>MAX(0, MIN(I41, DATE(YEAR(H41),7,31)) - MAX(H41, DATE(YEAR(H41),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE41" s="21">
-        <f>MAX(0, MIN(I41, DATE(YEAR(H41),8,31)) - MAX(H41, DATE(YEAR(H41),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF41" s="21">
-        <f>MAX(0, MIN(I41, DATE(YEAR(H41),9,31)) - MAX(H41, DATE(YEAR(H41),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG41" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH41" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI41" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -11071,39 +11093,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA42" s="21">
-        <f>V42/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB42" s="21">
-        <f>MAX(0, MIN(I42, DATE(YEAR(H42),5,31)) - MAX(H42, DATE(YEAR(H42),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC42" s="21">
-        <f>MAX(0, MIN(I42, DATE(YEAR(H42),6,31)) - MAX(H42, DATE(YEAR(H42),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD42" s="21">
-        <f>MAX(0, MIN(I42, DATE(YEAR(H42),7,31)) - MAX(H42, DATE(YEAR(H42),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE42" s="21">
-        <f>MAX(0, MIN(I42, DATE(YEAR(H42),8,31)) - MAX(H42, DATE(YEAR(H42),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF42" s="21">
-        <f>MAX(0, MIN(I42, DATE(YEAR(H42),9,31)) - MAX(H42, DATE(YEAR(H42),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG42" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH42" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI42" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -11184,39 +11206,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA43" s="21">
-        <f>V43/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB43" s="21">
-        <f>MAX(0, MIN(I43, DATE(YEAR(H43),5,31)) - MAX(H43, DATE(YEAR(H43),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC43" s="21">
-        <f>MAX(0, MIN(I43, DATE(YEAR(H43),6,31)) - MAX(H43, DATE(YEAR(H43),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD43" s="21">
-        <f>MAX(0, MIN(I43, DATE(YEAR(H43),7,31)) - MAX(H43, DATE(YEAR(H43),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE43" s="21">
-        <f>MAX(0, MIN(I43, DATE(YEAR(H43),8,31)) - MAX(H43, DATE(YEAR(H43),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF43" s="21">
-        <f>MAX(0, MIN(I43, DATE(YEAR(H43),9,31)) - MAX(H43, DATE(YEAR(H43),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG43" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH43" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI43" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -11297,39 +11319,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA44" s="21">
-        <f>V44/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB44" s="21">
-        <f>MAX(0, MIN(I44, DATE(YEAR(H44),5,31)) - MAX(H44, DATE(YEAR(H44),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC44" s="21">
-        <f>MAX(0, MIN(I44, DATE(YEAR(H44),6,31)) - MAX(H44, DATE(YEAR(H44),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD44" s="21">
-        <f>MAX(0, MIN(I44, DATE(YEAR(H44),7,31)) - MAX(H44, DATE(YEAR(H44),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE44" s="21">
-        <f>MAX(0, MIN(I44, DATE(YEAR(H44),8,31)) - MAX(H44, DATE(YEAR(H44),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF44" s="21">
-        <f>MAX(0, MIN(I44, DATE(YEAR(H44),9,31)) - MAX(H44, DATE(YEAR(H44),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG44" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH44" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI44" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -11410,39 +11432,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA45" s="21">
-        <f>V45/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB45" s="21">
-        <f>MAX(0, MIN(I45, DATE(YEAR(H45),5,31)) - MAX(H45, DATE(YEAR(H45),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC45" s="21">
-        <f>MAX(0, MIN(I45, DATE(YEAR(H45),6,31)) - MAX(H45, DATE(YEAR(H45),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD45" s="21">
-        <f>MAX(0, MIN(I45, DATE(YEAR(H45),7,31)) - MAX(H45, DATE(YEAR(H45),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE45" s="21">
-        <f>MAX(0, MIN(I45, DATE(YEAR(H45),8,31)) - MAX(H45, DATE(YEAR(H45),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF45" s="21">
-        <f>MAX(0, MIN(I45, DATE(YEAR(H45),9,31)) - MAX(H45, DATE(YEAR(H45),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG45" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH45" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI45" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -11523,39 +11545,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA46" s="21">
-        <f>V46/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB46" s="21">
-        <f>MAX(0, MIN(I46, DATE(YEAR(H46),5,31)) - MAX(H46, DATE(YEAR(H46),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC46" s="21">
-        <f>MAX(0, MIN(I46, DATE(YEAR(H46),6,31)) - MAX(H46, DATE(YEAR(H46),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD46" s="21">
-        <f>MAX(0, MIN(I46, DATE(YEAR(H46),7,31)) - MAX(H46, DATE(YEAR(H46),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE46" s="21">
-        <f>MAX(0, MIN(I46, DATE(YEAR(H46),8,31)) - MAX(H46, DATE(YEAR(H46),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF46" s="21">
-        <f>MAX(0, MIN(I46, DATE(YEAR(H46),9,31)) - MAX(H46, DATE(YEAR(H46),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG46" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH46" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI46" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -11636,39 +11658,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA47" s="21">
-        <f>V47/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB47" s="21">
-        <f>MAX(0, MIN(I47, DATE(YEAR(H47),5,31)) - MAX(H47, DATE(YEAR(H47),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC47" s="21">
-        <f>MAX(0, MIN(I47, DATE(YEAR(H47),6,31)) - MAX(H47, DATE(YEAR(H47),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD47" s="21">
-        <f>MAX(0, MIN(I47, DATE(YEAR(H47),7,31)) - MAX(H47, DATE(YEAR(H47),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE47" s="21">
-        <f>MAX(0, MIN(I47, DATE(YEAR(H47),8,31)) - MAX(H47, DATE(YEAR(H47),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF47" s="21">
-        <f>MAX(0, MIN(I47, DATE(YEAR(H47),9,31)) - MAX(H47, DATE(YEAR(H47),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG47" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH47" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI47" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -11749,39 +11771,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA48" s="21">
-        <f>V48/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB48" s="21">
-        <f>MAX(0, MIN(I48, DATE(YEAR(H48),5,31)) - MAX(H48, DATE(YEAR(H48),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC48" s="21">
-        <f>MAX(0, MIN(I48, DATE(YEAR(H48),6,31)) - MAX(H48, DATE(YEAR(H48),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD48" s="21">
-        <f>MAX(0, MIN(I48, DATE(YEAR(H48),7,31)) - MAX(H48, DATE(YEAR(H48),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE48" s="21">
-        <f>MAX(0, MIN(I48, DATE(YEAR(H48),8,31)) - MAX(H48, DATE(YEAR(H48),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF48" s="21">
-        <f>MAX(0, MIN(I48, DATE(YEAR(H48),9,31)) - MAX(H48, DATE(YEAR(H48),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG48" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH48" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI48" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -11862,39 +11884,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA49" s="21">
-        <f>V49/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB49" s="21">
-        <f>MAX(0, MIN(I49, DATE(YEAR(H49),5,31)) - MAX(H49, DATE(YEAR(H49),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC49" s="21">
-        <f>MAX(0, MIN(I49, DATE(YEAR(H49),6,31)) - MAX(H49, DATE(YEAR(H49),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD49" s="21">
-        <f>MAX(0, MIN(I49, DATE(YEAR(H49),7,31)) - MAX(H49, DATE(YEAR(H49),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE49" s="21">
-        <f>MAX(0, MIN(I49, DATE(YEAR(H49),8,31)) - MAX(H49, DATE(YEAR(H49),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF49" s="21">
-        <f>MAX(0, MIN(I49, DATE(YEAR(H49),9,31)) - MAX(H49, DATE(YEAR(H49),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG49" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH49" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI49" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -11975,39 +11997,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA50" s="21">
-        <f>V50/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB50" s="21">
-        <f>MAX(0, MIN(I50, DATE(YEAR(H50),5,31)) - MAX(H50, DATE(YEAR(H50),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC50" s="21">
-        <f>MAX(0, MIN(I50, DATE(YEAR(H50),6,31)) - MAX(H50, DATE(YEAR(H50),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD50" s="21">
-        <f>MAX(0, MIN(I50, DATE(YEAR(H50),7,31)) - MAX(H50, DATE(YEAR(H50),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE50" s="21">
-        <f>MAX(0, MIN(I50, DATE(YEAR(H50),8,31)) - MAX(H50, DATE(YEAR(H50),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF50" s="21">
-        <f>MAX(0, MIN(I50, DATE(YEAR(H50),9,31)) - MAX(H50, DATE(YEAR(H50),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG50" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH50" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI50" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -12088,39 +12110,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA51" s="21">
-        <f>V51/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB51" s="21">
-        <f>MAX(0, MIN(I51, DATE(YEAR(H51),5,31)) - MAX(H51, DATE(YEAR(H51),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC51" s="21">
-        <f>MAX(0, MIN(I51, DATE(YEAR(H51),6,31)) - MAX(H51, DATE(YEAR(H51),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD51" s="21">
-        <f>MAX(0, MIN(I51, DATE(YEAR(H51),7,31)) - MAX(H51, DATE(YEAR(H51),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE51" s="21">
-        <f>MAX(0, MIN(I51, DATE(YEAR(H51),8,31)) - MAX(H51, DATE(YEAR(H51),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF51" s="21">
-        <f>MAX(0, MIN(I51, DATE(YEAR(H51),9,31)) - MAX(H51, DATE(YEAR(H51),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG51" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH51" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI51" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -12201,39 +12223,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA52" s="21">
-        <f>V52/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB52" s="21">
-        <f>MAX(0, MIN(I52, DATE(YEAR(H52),5,31)) - MAX(H52, DATE(YEAR(H52),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC52" s="21">
-        <f>MAX(0, MIN(I52, DATE(YEAR(H52),6,31)) - MAX(H52, DATE(YEAR(H52),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD52" s="21">
-        <f>MAX(0, MIN(I52, DATE(YEAR(H52),7,31)) - MAX(H52, DATE(YEAR(H52),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE52" s="21">
-        <f>MAX(0, MIN(I52, DATE(YEAR(H52),8,31)) - MAX(H52, DATE(YEAR(H52),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF52" s="21">
-        <f>MAX(0, MIN(I52, DATE(YEAR(H52),9,31)) - MAX(H52, DATE(YEAR(H52),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG52" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH52" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI52" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -12314,39 +12336,39 @@
         <v>-69.955561399999993</v>
       </c>
       <c r="AA53" s="21">
-        <f>V53/153</f>
+        <f t="shared" si="9"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="AB53" s="21">
-        <f>MAX(0, MIN(I53, DATE(YEAR(H53),5,31)) - MAX(H53, DATE(YEAR(H53),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC53" s="21">
-        <f>MAX(0, MIN(I53, DATE(YEAR(H53),6,31)) - MAX(H53, DATE(YEAR(H53),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD53" s="21">
-        <f>MAX(0, MIN(I53, DATE(YEAR(H53),7,31)) - MAX(H53, DATE(YEAR(H53),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>24</v>
       </c>
       <c r="AE53" s="21">
-        <f>MAX(0, MIN(I53, DATE(YEAR(H53),8,31)) - MAX(H53, DATE(YEAR(H53),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="AF53" s="21">
-        <f>MAX(0, MIN(I53, DATE(YEAR(H53),9,31)) - MAX(H53, DATE(YEAR(H53),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="AG53" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="AH53" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI53" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -12427,39 +12449,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA54" s="21">
-        <f>V54/153</f>
+        <f t="shared" si="9"/>
         <v>0.49673202614379086</v>
       </c>
       <c r="AB54" s="21">
-        <f>MAX(0, MIN(I54, DATE(YEAR(H54),5,31)) - MAX(H54, DATE(YEAR(H54),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="AC54" s="21">
-        <f>MAX(0, MIN(I54, DATE(YEAR(H54),6,31)) - MAX(H54, DATE(YEAR(H54),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="AD54" s="21">
-        <f>MAX(0, MIN(I54, DATE(YEAR(H54),7,31)) - MAX(H54, DATE(YEAR(H54),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>15</v>
       </c>
       <c r="AE54" s="21">
-        <f>MAX(0, MIN(I54, DATE(YEAR(H54),8,31)) - MAX(H54, DATE(YEAR(H54),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF54" s="21">
-        <f>MAX(0, MIN(I54, DATE(YEAR(H54),9,31)) - MAX(H54, DATE(YEAR(H54),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG54" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="AH54" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI54" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -12540,39 +12562,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA55" s="21">
-        <f>V55/153</f>
+        <f t="shared" si="9"/>
         <v>0.81045751633986929</v>
       </c>
       <c r="AB55" s="21">
-        <f>MAX(0, MIN(I55, DATE(YEAR(H55),5,31)) - MAX(H55, DATE(YEAR(H55),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC55" s="21">
-        <f>MAX(0, MIN(I55, DATE(YEAR(H55),6,31)) - MAX(H55, DATE(YEAR(H55),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD55" s="21">
-        <f>MAX(0, MIN(I55, DATE(YEAR(H55),7,31)) - MAX(H55, DATE(YEAR(H55),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE55" s="21">
-        <f>MAX(0, MIN(I55, DATE(YEAR(H55),8,31)) - MAX(H55, DATE(YEAR(H55),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF55" s="21">
-        <f>MAX(0, MIN(I55, DATE(YEAR(H55),9,31)) - MAX(H55, DATE(YEAR(H55),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>1</v>
       </c>
       <c r="AG55" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="AH55" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI55" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -12653,39 +12675,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA56" s="21">
-        <f>V56/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB56" s="21">
-        <f>MAX(0, MIN(I56, DATE(YEAR(H56),5,31)) - MAX(H56, DATE(YEAR(H56),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC56" s="21">
-        <f>MAX(0, MIN(I56, DATE(YEAR(H56),6,31)) - MAX(H56, DATE(YEAR(H56),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD56" s="21">
-        <f>MAX(0, MIN(I56, DATE(YEAR(H56),7,31)) - MAX(H56, DATE(YEAR(H56),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE56" s="21">
-        <f>MAX(0, MIN(I56, DATE(YEAR(H56),8,31)) - MAX(H56, DATE(YEAR(H56),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF56" s="21">
-        <f>MAX(0, MIN(I56, DATE(YEAR(H56),9,31)) - MAX(H56, DATE(YEAR(H56),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG56" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH56" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI56" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -12766,39 +12788,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA57" s="21">
-        <f>V57/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB57" s="21">
-        <f>MAX(0, MIN(I57, DATE(YEAR(H57),5,31)) - MAX(H57, DATE(YEAR(H57),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC57" s="21">
-        <f>MAX(0, MIN(I57, DATE(YEAR(H57),6,31)) - MAX(H57, DATE(YEAR(H57),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD57" s="21">
-        <f>MAX(0, MIN(I57, DATE(YEAR(H57),7,31)) - MAX(H57, DATE(YEAR(H57),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE57" s="21">
-        <f>MAX(0, MIN(I57, DATE(YEAR(H57),8,31)) - MAX(H57, DATE(YEAR(H57),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF57" s="21">
-        <f>MAX(0, MIN(I57, DATE(YEAR(H57),9,31)) - MAX(H57, DATE(YEAR(H57),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG57" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH57" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI57" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -12879,39 +12901,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA58" s="21">
-        <f>V58/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB58" s="21">
-        <f>MAX(0, MIN(I58, DATE(YEAR(H58),5,31)) - MAX(H58, DATE(YEAR(H58),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC58" s="21">
-        <f>MAX(0, MIN(I58, DATE(YEAR(H58),6,31)) - MAX(H58, DATE(YEAR(H58),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD58" s="21">
-        <f>MAX(0, MIN(I58, DATE(YEAR(H58),7,31)) - MAX(H58, DATE(YEAR(H58),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE58" s="21">
-        <f>MAX(0, MIN(I58, DATE(YEAR(H58),8,31)) - MAX(H58, DATE(YEAR(H58),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF58" s="21">
-        <f>MAX(0, MIN(I58, DATE(YEAR(H58),9,31)) - MAX(H58, DATE(YEAR(H58),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG58" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH58" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI58" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -12992,39 +13014,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA59" s="21">
-        <f>V59/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB59" s="21">
-        <f>MAX(0, MIN(I59, DATE(YEAR(H59),5,31)) - MAX(H59, DATE(YEAR(H59),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC59" s="21">
-        <f>MAX(0, MIN(I59, DATE(YEAR(H59),6,31)) - MAX(H59, DATE(YEAR(H59),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD59" s="21">
-        <f>MAX(0, MIN(I59, DATE(YEAR(H59),7,31)) - MAX(H59, DATE(YEAR(H59),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE59" s="21">
-        <f>MAX(0, MIN(I59, DATE(YEAR(H59),8,31)) - MAX(H59, DATE(YEAR(H59),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF59" s="21">
-        <f>MAX(0, MIN(I59, DATE(YEAR(H59),9,31)) - MAX(H59, DATE(YEAR(H59),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG59" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH59" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI59" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -13105,39 +13127,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA60" s="21">
-        <f>V60/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB60" s="21">
-        <f>MAX(0, MIN(I60, DATE(YEAR(H60),5,31)) - MAX(H60, DATE(YEAR(H60),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC60" s="21">
-        <f>MAX(0, MIN(I60, DATE(YEAR(H60),6,31)) - MAX(H60, DATE(YEAR(H60),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD60" s="21">
-        <f>MAX(0, MIN(I60, DATE(YEAR(H60),7,31)) - MAX(H60, DATE(YEAR(H60),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE60" s="21">
-        <f>MAX(0, MIN(I60, DATE(YEAR(H60),8,31)) - MAX(H60, DATE(YEAR(H60),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF60" s="21">
-        <f>MAX(0, MIN(I60, DATE(YEAR(H60),9,31)) - MAX(H60, DATE(YEAR(H60),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG60" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH60" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI60" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -13218,39 +13240,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA61" s="21">
-        <f>V61/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB61" s="21">
-        <f>MAX(0, MIN(I61, DATE(YEAR(H61),5,31)) - MAX(H61, DATE(YEAR(H61),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC61" s="21">
-        <f>MAX(0, MIN(I61, DATE(YEAR(H61),6,31)) - MAX(H61, DATE(YEAR(H61),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD61" s="21">
-        <f>MAX(0, MIN(I61, DATE(YEAR(H61),7,31)) - MAX(H61, DATE(YEAR(H61),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE61" s="21">
-        <f>MAX(0, MIN(I61, DATE(YEAR(H61),8,31)) - MAX(H61, DATE(YEAR(H61),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF61" s="21">
-        <f>MAX(0, MIN(I61, DATE(YEAR(H61),9,31)) - MAX(H61, DATE(YEAR(H61),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG61" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH61" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI61" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -13331,39 +13353,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA62" s="21">
-        <f>V62/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB62" s="21">
-        <f>MAX(0, MIN(I62, DATE(YEAR(H62),5,31)) - MAX(H62, DATE(YEAR(H62),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC62" s="21">
-        <f>MAX(0, MIN(I62, DATE(YEAR(H62),6,31)) - MAX(H62, DATE(YEAR(H62),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD62" s="21">
-        <f>MAX(0, MIN(I62, DATE(YEAR(H62),7,31)) - MAX(H62, DATE(YEAR(H62),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE62" s="21">
-        <f>MAX(0, MIN(I62, DATE(YEAR(H62),8,31)) - MAX(H62, DATE(YEAR(H62),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF62" s="21">
-        <f>MAX(0, MIN(I62, DATE(YEAR(H62),9,31)) - MAX(H62, DATE(YEAR(H62),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG62" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH62" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI62" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -13444,39 +13466,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA63" s="21">
-        <f>V63/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB63" s="21">
-        <f>MAX(0, MIN(I63, DATE(YEAR(H63),5,31)) - MAX(H63, DATE(YEAR(H63),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC63" s="21">
-        <f>MAX(0, MIN(I63, DATE(YEAR(H63),6,31)) - MAX(H63, DATE(YEAR(H63),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD63" s="21">
-        <f>MAX(0, MIN(I63, DATE(YEAR(H63),7,31)) - MAX(H63, DATE(YEAR(H63),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE63" s="21">
-        <f>MAX(0, MIN(I63, DATE(YEAR(H63),8,31)) - MAX(H63, DATE(YEAR(H63),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF63" s="21">
-        <f>MAX(0, MIN(I63, DATE(YEAR(H63),9,31)) - MAX(H63, DATE(YEAR(H63),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG63" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH63" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI63" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -13557,39 +13579,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA64" s="21">
-        <f>V64/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB64" s="21">
-        <f>MAX(0, MIN(I64, DATE(YEAR(H64),5,31)) - MAX(H64, DATE(YEAR(H64),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC64" s="21">
-        <f>MAX(0, MIN(I64, DATE(YEAR(H64),6,31)) - MAX(H64, DATE(YEAR(H64),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD64" s="21">
-        <f>MAX(0, MIN(I64, DATE(YEAR(H64),7,31)) - MAX(H64, DATE(YEAR(H64),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE64" s="21">
-        <f>MAX(0, MIN(I64, DATE(YEAR(H64),8,31)) - MAX(H64, DATE(YEAR(H64),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF64" s="21">
-        <f>MAX(0, MIN(I64, DATE(YEAR(H64),9,31)) - MAX(H64, DATE(YEAR(H64),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG64" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH64" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI64" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -13670,39 +13692,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA65" s="21">
-        <f>V65/153</f>
+        <f t="shared" si="9"/>
         <v>1</v>
       </c>
       <c r="AB65" s="21">
-        <f>MAX(0, MIN(I65, DATE(YEAR(H65),5,31)) - MAX(H65, DATE(YEAR(H65),5,1)) + 1)</f>
+        <f t="shared" si="10"/>
         <v>31</v>
       </c>
       <c r="AC65" s="21">
-        <f>MAX(0, MIN(I65, DATE(YEAR(H65),6,31)) - MAX(H65, DATE(YEAR(H65),6,1)) + 1)</f>
+        <f t="shared" si="11"/>
         <v>31</v>
       </c>
       <c r="AD65" s="21">
-        <f>MAX(0, MIN(I65, DATE(YEAR(H65),7,31)) - MAX(H65, DATE(YEAR(H65),7,1)) + 1)</f>
+        <f t="shared" si="12"/>
         <v>31</v>
       </c>
       <c r="AE65" s="21">
-        <f>MAX(0, MIN(I65, DATE(YEAR(H65),8,31)) - MAX(H65, DATE(YEAR(H65),8,1)) + 1)</f>
+        <f t="shared" si="13"/>
         <v>31</v>
       </c>
       <c r="AF65" s="21">
-        <f>MAX(0, MIN(I65, DATE(YEAR(H65),9,31)) - MAX(H65, DATE(YEAR(H65),9,1)) + 1)</f>
+        <f t="shared" si="14"/>
         <v>30</v>
       </c>
       <c r="AG65" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH65" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI65" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -13783,39 +13805,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA66" s="21">
-        <f>V66/153</f>
+        <f t="shared" ref="AA66:AA97" si="15">V66/153</f>
         <v>1</v>
       </c>
       <c r="AB66" s="21">
-        <f>MAX(0, MIN(I66, DATE(YEAR(H66),5,31)) - MAX(H66, DATE(YEAR(H66),5,1)) + 1)</f>
+        <f t="shared" ref="AB66:AB97" si="16">MAX(0, MIN(I66, DATE(YEAR(H66),5,31)) - MAX(H66, DATE(YEAR(H66),5,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AC66" s="21">
-        <f>MAX(0, MIN(I66, DATE(YEAR(H66),6,31)) - MAX(H66, DATE(YEAR(H66),6,1)) + 1)</f>
+        <f t="shared" ref="AC66:AC97" si="17">MAX(0, MIN(I66, DATE(YEAR(H66),6,31)) - MAX(H66, DATE(YEAR(H66),6,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AD66" s="21">
-        <f>MAX(0, MIN(I66, DATE(YEAR(H66),7,31)) - MAX(H66, DATE(YEAR(H66),7,1)) + 1)</f>
+        <f t="shared" ref="AD66:AD97" si="18">MAX(0, MIN(I66, DATE(YEAR(H66),7,31)) - MAX(H66, DATE(YEAR(H66),7,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AE66" s="21">
-        <f>MAX(0, MIN(I66, DATE(YEAR(H66),8,31)) - MAX(H66, DATE(YEAR(H66),8,1)) + 1)</f>
+        <f t="shared" ref="AE66:AE97" si="19">MAX(0, MIN(I66, DATE(YEAR(H66),8,31)) - MAX(H66, DATE(YEAR(H66),8,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AF66" s="21">
-        <f>MAX(0, MIN(I66, DATE(YEAR(H66),9,31)) - MAX(H66, DATE(YEAR(H66),9,1)) + 1)</f>
+        <f t="shared" ref="AF66:AF97" si="20">MAX(0, MIN(I66, DATE(YEAR(H66),9,31)) - MAX(H66, DATE(YEAR(H66),9,1)) + 1)</f>
         <v>30</v>
       </c>
       <c r="AG66" s="21">
-        <f t="shared" si="0"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="AH66" s="21" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" si="7"/>
         <v>PASS</v>
       </c>
       <c r="AI66" s="21" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="8"/>
         <v>PASS</v>
       </c>
     </row>
@@ -13896,39 +13918,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA67" s="21">
-        <f>V67/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB67" s="21">
-        <f>MAX(0, MIN(I67, DATE(YEAR(H67),5,31)) - MAX(H67, DATE(YEAR(H67),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC67" s="21">
-        <f>MAX(0, MIN(I67, DATE(YEAR(H67),6,31)) - MAX(H67, DATE(YEAR(H67),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD67" s="21">
-        <f>MAX(0, MIN(I67, DATE(YEAR(H67),7,31)) - MAX(H67, DATE(YEAR(H67),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE67" s="21">
-        <f>MAX(0, MIN(I67, DATE(YEAR(H67),8,31)) - MAX(H67, DATE(YEAR(H67),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF67" s="21">
-        <f>MAX(0, MIN(I67, DATE(YEAR(H67),9,31)) - MAX(H67, DATE(YEAR(H67),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG67" s="21">
-        <f t="shared" ref="AG67:AG130" si="3">COUNTIF(AB67:AF67, "&gt;=10")</f>
+        <f t="shared" ref="AG67:AG130" si="21">COUNTIF(AB67:AF67, "&gt;=10")</f>
         <v>5</v>
       </c>
       <c r="AH67" s="21" t="str">
-        <f t="shared" ref="AH67:AH130" si="4">IF(COUNTIF(AB67:AF67,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
+        <f t="shared" ref="AH67:AH130" si="22">IF(COUNTIF(AB67:AF67,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="AI67" s="21" t="str">
-        <f t="shared" ref="AI67:AI130" si="5">IF(AND(AA67&gt;=0.8, COUNTIF(AB67:AF67, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
+        <f t="shared" ref="AI67:AI130" si="23">IF(AND(AA67&gt;=0.8, COUNTIF(AB67:AF67, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -14009,39 +14031,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA68" s="21">
-        <f>V68/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB68" s="21">
-        <f>MAX(0, MIN(I68, DATE(YEAR(H68),5,31)) - MAX(H68, DATE(YEAR(H68),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC68" s="21">
-        <f>MAX(0, MIN(I68, DATE(YEAR(H68),6,31)) - MAX(H68, DATE(YEAR(H68),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD68" s="21">
-        <f>MAX(0, MIN(I68, DATE(YEAR(H68),7,31)) - MAX(H68, DATE(YEAR(H68),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE68" s="21">
-        <f>MAX(0, MIN(I68, DATE(YEAR(H68),8,31)) - MAX(H68, DATE(YEAR(H68),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF68" s="21">
-        <f>MAX(0, MIN(I68, DATE(YEAR(H68),9,31)) - MAX(H68, DATE(YEAR(H68),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG68" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH68" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI68" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -14122,39 +14144,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA69" s="21">
-        <f>V69/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB69" s="21">
-        <f>MAX(0, MIN(I69, DATE(YEAR(H69),5,31)) - MAX(H69, DATE(YEAR(H69),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC69" s="21">
-        <f>MAX(0, MIN(I69, DATE(YEAR(H69),6,31)) - MAX(H69, DATE(YEAR(H69),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD69" s="21">
-        <f>MAX(0, MIN(I69, DATE(YEAR(H69),7,31)) - MAX(H69, DATE(YEAR(H69),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE69" s="21">
-        <f>MAX(0, MIN(I69, DATE(YEAR(H69),8,31)) - MAX(H69, DATE(YEAR(H69),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF69" s="21">
-        <f>MAX(0, MIN(I69, DATE(YEAR(H69),9,31)) - MAX(H69, DATE(YEAR(H69),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG69" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH69" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI69" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -14235,39 +14257,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA70" s="21">
-        <f>V70/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB70" s="21">
-        <f>MAX(0, MIN(I70, DATE(YEAR(H70),5,31)) - MAX(H70, DATE(YEAR(H70),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC70" s="21">
-        <f>MAX(0, MIN(I70, DATE(YEAR(H70),6,31)) - MAX(H70, DATE(YEAR(H70),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD70" s="21">
-        <f>MAX(0, MIN(I70, DATE(YEAR(H70),7,31)) - MAX(H70, DATE(YEAR(H70),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE70" s="21">
-        <f>MAX(0, MIN(I70, DATE(YEAR(H70),8,31)) - MAX(H70, DATE(YEAR(H70),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF70" s="21">
-        <f>MAX(0, MIN(I70, DATE(YEAR(H70),9,31)) - MAX(H70, DATE(YEAR(H70),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG70" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH70" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI70" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -14348,39 +14370,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA71" s="21">
-        <f>V71/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB71" s="21">
-        <f>MAX(0, MIN(I71, DATE(YEAR(H71),5,31)) - MAX(H71, DATE(YEAR(H71),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC71" s="21">
-        <f>MAX(0, MIN(I71, DATE(YEAR(H71),6,31)) - MAX(H71, DATE(YEAR(H71),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD71" s="21">
-        <f>MAX(0, MIN(I71, DATE(YEAR(H71),7,31)) - MAX(H71, DATE(YEAR(H71),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE71" s="21">
-        <f>MAX(0, MIN(I71, DATE(YEAR(H71),8,31)) - MAX(H71, DATE(YEAR(H71),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF71" s="21">
-        <f>MAX(0, MIN(I71, DATE(YEAR(H71),9,31)) - MAX(H71, DATE(YEAR(H71),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG71" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH71" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI71" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -14461,39 +14483,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA72" s="21">
-        <f>V72/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB72" s="21">
-        <f>MAX(0, MIN(I72, DATE(YEAR(H72),5,31)) - MAX(H72, DATE(YEAR(H72),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC72" s="21">
-        <f>MAX(0, MIN(I72, DATE(YEAR(H72),6,31)) - MAX(H72, DATE(YEAR(H72),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD72" s="21">
-        <f>MAX(0, MIN(I72, DATE(YEAR(H72),7,31)) - MAX(H72, DATE(YEAR(H72),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE72" s="21">
-        <f>MAX(0, MIN(I72, DATE(YEAR(H72),8,31)) - MAX(H72, DATE(YEAR(H72),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF72" s="21">
-        <f>MAX(0, MIN(I72, DATE(YEAR(H72),9,31)) - MAX(H72, DATE(YEAR(H72),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG72" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH72" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI72" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -14574,39 +14596,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA73" s="21">
-        <f>V73/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB73" s="21">
-        <f>MAX(0, MIN(I73, DATE(YEAR(H73),5,31)) - MAX(H73, DATE(YEAR(H73),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC73" s="21">
-        <f>MAX(0, MIN(I73, DATE(YEAR(H73),6,31)) - MAX(H73, DATE(YEAR(H73),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD73" s="21">
-        <f>MAX(0, MIN(I73, DATE(YEAR(H73),7,31)) - MAX(H73, DATE(YEAR(H73),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE73" s="21">
-        <f>MAX(0, MIN(I73, DATE(YEAR(H73),8,31)) - MAX(H73, DATE(YEAR(H73),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF73" s="21">
-        <f>MAX(0, MIN(I73, DATE(YEAR(H73),9,31)) - MAX(H73, DATE(YEAR(H73),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG73" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH73" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI73" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -14687,39 +14709,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA74" s="21">
-        <f>V74/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB74" s="21">
-        <f>MAX(0, MIN(I74, DATE(YEAR(H74),5,31)) - MAX(H74, DATE(YEAR(H74),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC74" s="21">
-        <f>MAX(0, MIN(I74, DATE(YEAR(H74),6,31)) - MAX(H74, DATE(YEAR(H74),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD74" s="21">
-        <f>MAX(0, MIN(I74, DATE(YEAR(H74),7,31)) - MAX(H74, DATE(YEAR(H74),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE74" s="21">
-        <f>MAX(0, MIN(I74, DATE(YEAR(H74),8,31)) - MAX(H74, DATE(YEAR(H74),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF74" s="21">
-        <f>MAX(0, MIN(I74, DATE(YEAR(H74),9,31)) - MAX(H74, DATE(YEAR(H74),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG74" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH74" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI74" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -14800,39 +14822,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA75" s="21">
-        <f>V75/153</f>
+        <f t="shared" si="15"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="AB75" s="21">
-        <f>MAX(0, MIN(I75, DATE(YEAR(H75),5,31)) - MAX(H75, DATE(YEAR(H75),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC75" s="21">
-        <f>MAX(0, MIN(I75, DATE(YEAR(H75),6,31)) - MAX(H75, DATE(YEAR(H75),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD75" s="21">
-        <f>MAX(0, MIN(I75, DATE(YEAR(H75),7,31)) - MAX(H75, DATE(YEAR(H75),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>24</v>
       </c>
       <c r="AE75" s="21">
-        <f>MAX(0, MIN(I75, DATE(YEAR(H75),8,31)) - MAX(H75, DATE(YEAR(H75),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AF75" s="21">
-        <f>MAX(0, MIN(I75, DATE(YEAR(H75),9,31)) - MAX(H75, DATE(YEAR(H75),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AG75" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="AH75" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI75" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -14913,39 +14935,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA76" s="21">
-        <f>V76/153</f>
+        <f t="shared" si="15"/>
         <v>0.45751633986928103</v>
       </c>
       <c r="AB76" s="21">
-        <f>MAX(0, MIN(I76, DATE(YEAR(H76),5,31)) - MAX(H76, DATE(YEAR(H76),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AC76" s="21">
-        <f>MAX(0, MIN(I76, DATE(YEAR(H76),6,31)) - MAX(H76, DATE(YEAR(H76),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AD76" s="21">
-        <f>MAX(0, MIN(I76, DATE(YEAR(H76),7,31)) - MAX(H76, DATE(YEAR(H76),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>9</v>
       </c>
       <c r="AE76" s="21">
-        <f>MAX(0, MIN(I76, DATE(YEAR(H76),8,31)) - MAX(H76, DATE(YEAR(H76),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF76" s="21">
-        <f>MAX(0, MIN(I76, DATE(YEAR(H76),9,31)) - MAX(H76, DATE(YEAR(H76),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG76" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>2</v>
       </c>
       <c r="AH76" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>FAIL</v>
       </c>
       <c r="AI76" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -15026,39 +15048,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA77" s="21">
-        <f>V77/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB77" s="21">
-        <f>MAX(0, MIN(I77, DATE(YEAR(H77),5,31)) - MAX(H77, DATE(YEAR(H77),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC77" s="21">
-        <f>MAX(0, MIN(I77, DATE(YEAR(H77),6,31)) - MAX(H77, DATE(YEAR(H77),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD77" s="21">
-        <f>MAX(0, MIN(I77, DATE(YEAR(H77),7,31)) - MAX(H77, DATE(YEAR(H77),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE77" s="21">
-        <f>MAX(0, MIN(I77, DATE(YEAR(H77),8,31)) - MAX(H77, DATE(YEAR(H77),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF77" s="21">
-        <f>MAX(0, MIN(I77, DATE(YEAR(H77),9,31)) - MAX(H77, DATE(YEAR(H77),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG77" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH77" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI77" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -15139,39 +15161,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA78" s="21">
-        <f>V78/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB78" s="21">
-        <f>MAX(0, MIN(I78, DATE(YEAR(H78),5,31)) - MAX(H78, DATE(YEAR(H78),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC78" s="21">
-        <f>MAX(0, MIN(I78, DATE(YEAR(H78),6,31)) - MAX(H78, DATE(YEAR(H78),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD78" s="21">
-        <f>MAX(0, MIN(I78, DATE(YEAR(H78),7,31)) - MAX(H78, DATE(YEAR(H78),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE78" s="21">
-        <f>MAX(0, MIN(I78, DATE(YEAR(H78),8,31)) - MAX(H78, DATE(YEAR(H78),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF78" s="21">
-        <f>MAX(0, MIN(I78, DATE(YEAR(H78),9,31)) - MAX(H78, DATE(YEAR(H78),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG78" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH78" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI78" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -15252,39 +15274,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA79" s="21">
-        <f>V79/153</f>
+        <f t="shared" si="15"/>
         <v>0.86274509803921573</v>
       </c>
       <c r="AB79" s="21">
-        <f>MAX(0, MIN(I79, DATE(YEAR(H79),5,31)) - MAX(H79, DATE(YEAR(H79),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC79" s="21">
-        <f>MAX(0, MIN(I79, DATE(YEAR(H79),6,31)) - MAX(H79, DATE(YEAR(H79),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD79" s="21">
-        <f>MAX(0, MIN(I79, DATE(YEAR(H79),7,31)) - MAX(H79, DATE(YEAR(H79),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE79" s="21">
-        <f>MAX(0, MIN(I79, DATE(YEAR(H79),8,31)) - MAX(H79, DATE(YEAR(H79),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF79" s="21">
-        <f>MAX(0, MIN(I79, DATE(YEAR(H79),9,31)) - MAX(H79, DATE(YEAR(H79),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG79" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH79" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI79" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -15365,39 +15387,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA80" s="21">
-        <f>V80/153</f>
+        <f t="shared" si="15"/>
         <v>0.55555555555555558</v>
       </c>
       <c r="AB80" s="21">
-        <f>MAX(0, MIN(I80, DATE(YEAR(H80),5,31)) - MAX(H80, DATE(YEAR(H80),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC80" s="21">
-        <f>MAX(0, MIN(I80, DATE(YEAR(H80),6,31)) - MAX(H80, DATE(YEAR(H80),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD80" s="21">
-        <f>MAX(0, MIN(I80, DATE(YEAR(H80),7,31)) - MAX(H80, DATE(YEAR(H80),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>24</v>
       </c>
       <c r="AE80" s="21">
-        <f>MAX(0, MIN(I80, DATE(YEAR(H80),8,31)) - MAX(H80, DATE(YEAR(H80),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AF80" s="21">
-        <f>MAX(0, MIN(I80, DATE(YEAR(H80),9,31)) - MAX(H80, DATE(YEAR(H80),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AG80" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="AH80" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI80" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -15478,39 +15500,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA81" s="21">
-        <f>V81/153</f>
+        <f t="shared" si="15"/>
         <v>0.6797385620915033</v>
       </c>
       <c r="AB81" s="21">
-        <f>MAX(0, MIN(I81, DATE(YEAR(H81),5,31)) - MAX(H81, DATE(YEAR(H81),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AC81" s="21">
-        <f>MAX(0, MIN(I81, DATE(YEAR(H81),6,31)) - MAX(H81, DATE(YEAR(H81),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>15</v>
       </c>
       <c r="AD81" s="21">
-        <f>MAX(0, MIN(I81, DATE(YEAR(H81),7,31)) - MAX(H81, DATE(YEAR(H81),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE81" s="21">
-        <f>MAX(0, MIN(I81, DATE(YEAR(H81),8,31)) - MAX(H81, DATE(YEAR(H81),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF81" s="21">
-        <f>MAX(0, MIN(I81, DATE(YEAR(H81),9,31)) - MAX(H81, DATE(YEAR(H81),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG81" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
       <c r="AH81" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI81" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -15591,39 +15613,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA82" s="21">
-        <f>V82/153</f>
+        <f t="shared" si="15"/>
         <v>0.81045751633986929</v>
       </c>
       <c r="AB82" s="21">
-        <f>MAX(0, MIN(I82, DATE(YEAR(H82),5,31)) - MAX(H82, DATE(YEAR(H82),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC82" s="21">
-        <f>MAX(0, MIN(I82, DATE(YEAR(H82),6,31)) - MAX(H82, DATE(YEAR(H82),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD82" s="21">
-        <f>MAX(0, MIN(I82, DATE(YEAR(H82),7,31)) - MAX(H82, DATE(YEAR(H82),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE82" s="21">
-        <f>MAX(0, MIN(I82, DATE(YEAR(H82),8,31)) - MAX(H82, DATE(YEAR(H82),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF82" s="21">
-        <f>MAX(0, MIN(I82, DATE(YEAR(H82),9,31)) - MAX(H82, DATE(YEAR(H82),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>1</v>
       </c>
       <c r="AG82" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
       <c r="AH82" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI82" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -15704,39 +15726,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA83" s="21">
-        <f>V83/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB83" s="21">
-        <f>MAX(0, MIN(I83, DATE(YEAR(H83),5,31)) - MAX(H83, DATE(YEAR(H83),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC83" s="21">
-        <f>MAX(0, MIN(I83, DATE(YEAR(H83),6,31)) - MAX(H83, DATE(YEAR(H83),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD83" s="21">
-        <f>MAX(0, MIN(I83, DATE(YEAR(H83),7,31)) - MAX(H83, DATE(YEAR(H83),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE83" s="21">
-        <f>MAX(0, MIN(I83, DATE(YEAR(H83),8,31)) - MAX(H83, DATE(YEAR(H83),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF83" s="21">
-        <f>MAX(0, MIN(I83, DATE(YEAR(H83),9,31)) - MAX(H83, DATE(YEAR(H83),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG83" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH83" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI83" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -15817,39 +15839,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA84" s="21">
-        <f>V84/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB84" s="21">
-        <f>MAX(0, MIN(I84, DATE(YEAR(H84),5,31)) - MAX(H84, DATE(YEAR(H84),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC84" s="21">
-        <f>MAX(0, MIN(I84, DATE(YEAR(H84),6,31)) - MAX(H84, DATE(YEAR(H84),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD84" s="21">
-        <f>MAX(0, MIN(I84, DATE(YEAR(H84),7,31)) - MAX(H84, DATE(YEAR(H84),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE84" s="21">
-        <f>MAX(0, MIN(I84, DATE(YEAR(H84),8,31)) - MAX(H84, DATE(YEAR(H84),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF84" s="21">
-        <f>MAX(0, MIN(I84, DATE(YEAR(H84),9,31)) - MAX(H84, DATE(YEAR(H84),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG84" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH84" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI84" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -15930,39 +15952,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA85" s="21">
-        <f>V85/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB85" s="21">
-        <f>MAX(0, MIN(I85, DATE(YEAR(H85),5,31)) - MAX(H85, DATE(YEAR(H85),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC85" s="21">
-        <f>MAX(0, MIN(I85, DATE(YEAR(H85),6,31)) - MAX(H85, DATE(YEAR(H85),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD85" s="21">
-        <f>MAX(0, MIN(I85, DATE(YEAR(H85),7,31)) - MAX(H85, DATE(YEAR(H85),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE85" s="21">
-        <f>MAX(0, MIN(I85, DATE(YEAR(H85),8,31)) - MAX(H85, DATE(YEAR(H85),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF85" s="21">
-        <f>MAX(0, MIN(I85, DATE(YEAR(H85),9,31)) - MAX(H85, DATE(YEAR(H85),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG85" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH85" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI85" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -16043,39 +16065,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA86" s="21">
-        <f>V86/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB86" s="21">
-        <f>MAX(0, MIN(I86, DATE(YEAR(H86),5,31)) - MAX(H86, DATE(YEAR(H86),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC86" s="21">
-        <f>MAX(0, MIN(I86, DATE(YEAR(H86),6,31)) - MAX(H86, DATE(YEAR(H86),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD86" s="21">
-        <f>MAX(0, MIN(I86, DATE(YEAR(H86),7,31)) - MAX(H86, DATE(YEAR(H86),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE86" s="21">
-        <f>MAX(0, MIN(I86, DATE(YEAR(H86),8,31)) - MAX(H86, DATE(YEAR(H86),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF86" s="21">
-        <f>MAX(0, MIN(I86, DATE(YEAR(H86),9,31)) - MAX(H86, DATE(YEAR(H86),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG86" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH86" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI86" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -16156,39 +16178,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA87" s="21">
-        <f>V87/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB87" s="21">
-        <f>MAX(0, MIN(I87, DATE(YEAR(H87),5,31)) - MAX(H87, DATE(YEAR(H87),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC87" s="21">
-        <f>MAX(0, MIN(I87, DATE(YEAR(H87),6,31)) - MAX(H87, DATE(YEAR(H87),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD87" s="21">
-        <f>MAX(0, MIN(I87, DATE(YEAR(H87),7,31)) - MAX(H87, DATE(YEAR(H87),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE87" s="21">
-        <f>MAX(0, MIN(I87, DATE(YEAR(H87),8,31)) - MAX(H87, DATE(YEAR(H87),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF87" s="21">
-        <f>MAX(0, MIN(I87, DATE(YEAR(H87),9,31)) - MAX(H87, DATE(YEAR(H87),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG87" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH87" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI87" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -16269,39 +16291,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA88" s="21">
-        <f>V88/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB88" s="21">
-        <f>MAX(0, MIN(I88, DATE(YEAR(H88),5,31)) - MAX(H88, DATE(YEAR(H88),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC88" s="21">
-        <f>MAX(0, MIN(I88, DATE(YEAR(H88),6,31)) - MAX(H88, DATE(YEAR(H88),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD88" s="21">
-        <f>MAX(0, MIN(I88, DATE(YEAR(H88),7,31)) - MAX(H88, DATE(YEAR(H88),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE88" s="21">
-        <f>MAX(0, MIN(I88, DATE(YEAR(H88),8,31)) - MAX(H88, DATE(YEAR(H88),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF88" s="21">
-        <f>MAX(0, MIN(I88, DATE(YEAR(H88),9,31)) - MAX(H88, DATE(YEAR(H88),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG88" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH88" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI88" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -16382,39 +16404,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA89" s="21">
-        <f>V89/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB89" s="21">
-        <f>MAX(0, MIN(I89, DATE(YEAR(H89),5,31)) - MAX(H89, DATE(YEAR(H89),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC89" s="21">
-        <f>MAX(0, MIN(I89, DATE(YEAR(H89),6,31)) - MAX(H89, DATE(YEAR(H89),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD89" s="21">
-        <f>MAX(0, MIN(I89, DATE(YEAR(H89),7,31)) - MAX(H89, DATE(YEAR(H89),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE89" s="21">
-        <f>MAX(0, MIN(I89, DATE(YEAR(H89),8,31)) - MAX(H89, DATE(YEAR(H89),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF89" s="21">
-        <f>MAX(0, MIN(I89, DATE(YEAR(H89),9,31)) - MAX(H89, DATE(YEAR(H89),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG89" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH89" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI89" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -16495,39 +16517,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA90" s="21">
-        <f>V90/153</f>
+        <f t="shared" si="15"/>
         <v>0.23529411764705882</v>
       </c>
       <c r="AB90" s="21">
-        <f>MAX(0, MIN(I90, DATE(YEAR(H90),5,31)) - MAX(H90, DATE(YEAR(H90),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC90" s="21">
-        <f>MAX(0, MIN(I90, DATE(YEAR(H90),6,31)) - MAX(H90, DATE(YEAR(H90),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>5</v>
       </c>
       <c r="AD90" s="21">
-        <f>MAX(0, MIN(I90, DATE(YEAR(H90),7,31)) - MAX(H90, DATE(YEAR(H90),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AE90" s="21">
-        <f>MAX(0, MIN(I90, DATE(YEAR(H90),8,31)) - MAX(H90, DATE(YEAR(H90),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AF90" s="21">
-        <f>MAX(0, MIN(I90, DATE(YEAR(H90),9,31)) - MAX(H90, DATE(YEAR(H90),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>0</v>
       </c>
       <c r="AG90" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="AH90" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>FAIL</v>
       </c>
       <c r="AI90" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -16608,39 +16630,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA91" s="21">
-        <f>V91/153</f>
+        <f t="shared" si="15"/>
         <v>0.64052287581699341</v>
       </c>
       <c r="AB91" s="21">
-        <f>MAX(0, MIN(I91, DATE(YEAR(H91),5,31)) - MAX(H91, DATE(YEAR(H91),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>0</v>
       </c>
       <c r="AC91" s="21">
-        <f>MAX(0, MIN(I91, DATE(YEAR(H91),6,31)) - MAX(H91, DATE(YEAR(H91),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>7</v>
       </c>
       <c r="AD91" s="21">
-        <f>MAX(0, MIN(I91, DATE(YEAR(H91),7,31)) - MAX(H91, DATE(YEAR(H91),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE91" s="21">
-        <f>MAX(0, MIN(I91, DATE(YEAR(H91),8,31)) - MAX(H91, DATE(YEAR(H91),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF91" s="21">
-        <f>MAX(0, MIN(I91, DATE(YEAR(H91),9,31)) - MAX(H91, DATE(YEAR(H91),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG91" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="AH91" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI91" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -16721,39 +16743,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA92" s="21">
-        <f>V92/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB92" s="21">
-        <f>MAX(0, MIN(I92, DATE(YEAR(H92),5,31)) - MAX(H92, DATE(YEAR(H92),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC92" s="21">
-        <f>MAX(0, MIN(I92, DATE(YEAR(H92),6,31)) - MAX(H92, DATE(YEAR(H92),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD92" s="21">
-        <f>MAX(0, MIN(I92, DATE(YEAR(H92),7,31)) - MAX(H92, DATE(YEAR(H92),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE92" s="21">
-        <f>MAX(0, MIN(I92, DATE(YEAR(H92),8,31)) - MAX(H92, DATE(YEAR(H92),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF92" s="21">
-        <f>MAX(0, MIN(I92, DATE(YEAR(H92),9,31)) - MAX(H92, DATE(YEAR(H92),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG92" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH92" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI92" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -16834,39 +16856,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA93" s="21">
-        <f>V93/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB93" s="21">
-        <f>MAX(0, MIN(I93, DATE(YEAR(H93),5,31)) - MAX(H93, DATE(YEAR(H93),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC93" s="21">
-        <f>MAX(0, MIN(I93, DATE(YEAR(H93),6,31)) - MAX(H93, DATE(YEAR(H93),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD93" s="21">
-        <f>MAX(0, MIN(I93, DATE(YEAR(H93),7,31)) - MAX(H93, DATE(YEAR(H93),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE93" s="21">
-        <f>MAX(0, MIN(I93, DATE(YEAR(H93),8,31)) - MAX(H93, DATE(YEAR(H93),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF93" s="21">
-        <f>MAX(0, MIN(I93, DATE(YEAR(H93),9,31)) - MAX(H93, DATE(YEAR(H93),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG93" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH93" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI93" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -16947,39 +16969,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA94" s="21">
-        <f>V94/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB94" s="21">
-        <f>MAX(0, MIN(I94, DATE(YEAR(H94),5,31)) - MAX(H94, DATE(YEAR(H94),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC94" s="21">
-        <f>MAX(0, MIN(I94, DATE(YEAR(H94),6,31)) - MAX(H94, DATE(YEAR(H94),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD94" s="21">
-        <f>MAX(0, MIN(I94, DATE(YEAR(H94),7,31)) - MAX(H94, DATE(YEAR(H94),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE94" s="21">
-        <f>MAX(0, MIN(I94, DATE(YEAR(H94),8,31)) - MAX(H94, DATE(YEAR(H94),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF94" s="21">
-        <f>MAX(0, MIN(I94, DATE(YEAR(H94),9,31)) - MAX(H94, DATE(YEAR(H94),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG94" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH94" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI94" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -17060,39 +17082,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA95" s="21">
-        <f>V95/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB95" s="21">
-        <f>MAX(0, MIN(I95, DATE(YEAR(H95),5,31)) - MAX(H95, DATE(YEAR(H95),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC95" s="21">
-        <f>MAX(0, MIN(I95, DATE(YEAR(H95),6,31)) - MAX(H95, DATE(YEAR(H95),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD95" s="21">
-        <f>MAX(0, MIN(I95, DATE(YEAR(H95),7,31)) - MAX(H95, DATE(YEAR(H95),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE95" s="21">
-        <f>MAX(0, MIN(I95, DATE(YEAR(H95),8,31)) - MAX(H95, DATE(YEAR(H95),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF95" s="21">
-        <f>MAX(0, MIN(I95, DATE(YEAR(H95),9,31)) - MAX(H95, DATE(YEAR(H95),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG95" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH95" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI95" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -17173,39 +17195,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA96" s="21">
-        <f>V96/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB96" s="21">
-        <f>MAX(0, MIN(I96, DATE(YEAR(H96),5,31)) - MAX(H96, DATE(YEAR(H96),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC96" s="21">
-        <f>MAX(0, MIN(I96, DATE(YEAR(H96),6,31)) - MAX(H96, DATE(YEAR(H96),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD96" s="21">
-        <f>MAX(0, MIN(I96, DATE(YEAR(H96),7,31)) - MAX(H96, DATE(YEAR(H96),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE96" s="21">
-        <f>MAX(0, MIN(I96, DATE(YEAR(H96),8,31)) - MAX(H96, DATE(YEAR(H96),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF96" s="21">
-        <f>MAX(0, MIN(I96, DATE(YEAR(H96),9,31)) - MAX(H96, DATE(YEAR(H96),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG96" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH96" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI96" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -17286,39 +17308,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA97" s="21">
-        <f>V97/153</f>
+        <f t="shared" si="15"/>
         <v>1</v>
       </c>
       <c r="AB97" s="21">
-        <f>MAX(0, MIN(I97, DATE(YEAR(H97),5,31)) - MAX(H97, DATE(YEAR(H97),5,1)) + 1)</f>
+        <f t="shared" si="16"/>
         <v>31</v>
       </c>
       <c r="AC97" s="21">
-        <f>MAX(0, MIN(I97, DATE(YEAR(H97),6,31)) - MAX(H97, DATE(YEAR(H97),6,1)) + 1)</f>
+        <f t="shared" si="17"/>
         <v>31</v>
       </c>
       <c r="AD97" s="21">
-        <f>MAX(0, MIN(I97, DATE(YEAR(H97),7,31)) - MAX(H97, DATE(YEAR(H97),7,1)) + 1)</f>
+        <f t="shared" si="18"/>
         <v>31</v>
       </c>
       <c r="AE97" s="21">
-        <f>MAX(0, MIN(I97, DATE(YEAR(H97),8,31)) - MAX(H97, DATE(YEAR(H97),8,1)) + 1)</f>
+        <f t="shared" si="19"/>
         <v>31</v>
       </c>
       <c r="AF97" s="21">
-        <f>MAX(0, MIN(I97, DATE(YEAR(H97),9,31)) - MAX(H97, DATE(YEAR(H97),9,1)) + 1)</f>
+        <f t="shared" si="20"/>
         <v>30</v>
       </c>
       <c r="AG97" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH97" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI97" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -17399,39 +17421,39 @@
         <v>-70.079599999999999</v>
       </c>
       <c r="AA98" s="21">
-        <f>V98/153</f>
+        <f t="shared" ref="AA98:AA129" si="24">V98/153</f>
         <v>1</v>
       </c>
       <c r="AB98" s="21">
-        <f>MAX(0, MIN(I98, DATE(YEAR(H98),5,31)) - MAX(H98, DATE(YEAR(H98),5,1)) + 1)</f>
+        <f t="shared" ref="AB98:AB129" si="25">MAX(0, MIN(I98, DATE(YEAR(H98),5,31)) - MAX(H98, DATE(YEAR(H98),5,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AC98" s="21">
-        <f>MAX(0, MIN(I98, DATE(YEAR(H98),6,31)) - MAX(H98, DATE(YEAR(H98),6,1)) + 1)</f>
+        <f t="shared" ref="AC98:AC129" si="26">MAX(0, MIN(I98, DATE(YEAR(H98),6,31)) - MAX(H98, DATE(YEAR(H98),6,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AD98" s="21">
-        <f>MAX(0, MIN(I98, DATE(YEAR(H98),7,31)) - MAX(H98, DATE(YEAR(H98),7,1)) + 1)</f>
+        <f t="shared" ref="AD98:AD129" si="27">MAX(0, MIN(I98, DATE(YEAR(H98),7,31)) - MAX(H98, DATE(YEAR(H98),7,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AE98" s="21">
-        <f>MAX(0, MIN(I98, DATE(YEAR(H98),8,31)) - MAX(H98, DATE(YEAR(H98),8,1)) + 1)</f>
+        <f t="shared" ref="AE98:AE129" si="28">MAX(0, MIN(I98, DATE(YEAR(H98),8,31)) - MAX(H98, DATE(YEAR(H98),8,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AF98" s="21">
-        <f>MAX(0, MIN(I98, DATE(YEAR(H98),9,31)) - MAX(H98, DATE(YEAR(H98),9,1)) + 1)</f>
+        <f t="shared" ref="AF98:AF129" si="29">MAX(0, MIN(I98, DATE(YEAR(H98),9,31)) - MAX(H98, DATE(YEAR(H98),9,1)) + 1)</f>
         <v>30</v>
       </c>
       <c r="AG98" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH98" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI98" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -17512,39 +17534,39 @@
         <v>70.124089999999995</v>
       </c>
       <c r="AA99" s="21">
-        <f>V99/153</f>
+        <f t="shared" si="24"/>
         <v>0.59477124183006536</v>
       </c>
       <c r="AB99" s="21">
-        <f>MAX(0, MIN(I99, DATE(YEAR(H99),5,31)) - MAX(H99, DATE(YEAR(H99),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC99" s="21">
-        <f>MAX(0, MIN(I99, DATE(YEAR(H99),6,31)) - MAX(H99, DATE(YEAR(H99),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="AD99" s="21">
-        <f>MAX(0, MIN(I99, DATE(YEAR(H99),7,31)) - MAX(H99, DATE(YEAR(H99),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>30</v>
       </c>
       <c r="AE99" s="21">
-        <f>MAX(0, MIN(I99, DATE(YEAR(H99),8,31)) - MAX(H99, DATE(YEAR(H99),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF99" s="21">
-        <f>MAX(0, MIN(I99, DATE(YEAR(H99),9,31)) - MAX(H99, DATE(YEAR(H99),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG99" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="AH99" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI99" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -17625,39 +17647,39 @@
         <v>70.124089999999995</v>
       </c>
       <c r="AA100" s="21">
-        <f>V100/153</f>
+        <f t="shared" si="24"/>
         <v>0.92156862745098034</v>
       </c>
       <c r="AB100" s="21">
-        <f>MAX(0, MIN(I100, DATE(YEAR(H100),5,31)) - MAX(H100, DATE(YEAR(H100),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>20</v>
       </c>
       <c r="AC100" s="21">
-        <f>MAX(0, MIN(I100, DATE(YEAR(H100),6,31)) - MAX(H100, DATE(YEAR(H100),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD100" s="21">
-        <f>MAX(0, MIN(I100, DATE(YEAR(H100),7,31)) - MAX(H100, DATE(YEAR(H100),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE100" s="21">
-        <f>MAX(0, MIN(I100, DATE(YEAR(H100),8,31)) - MAX(H100, DATE(YEAR(H100),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF100" s="21">
-        <f>MAX(0, MIN(I100, DATE(YEAR(H100),9,31)) - MAX(H100, DATE(YEAR(H100),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG100" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH100" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI100" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -17738,39 +17760,39 @@
         <v>70.124089999999995</v>
       </c>
       <c r="AA101" s="21">
-        <f>V101/153</f>
+        <f t="shared" si="24"/>
         <v>0.85620915032679734</v>
       </c>
       <c r="AB101" s="21">
-        <f>MAX(0, MIN(I101, DATE(YEAR(H101),5,31)) - MAX(H101, DATE(YEAR(H101),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>16</v>
       </c>
       <c r="AC101" s="21">
-        <f>MAX(0, MIN(I101, DATE(YEAR(H101),6,31)) - MAX(H101, DATE(YEAR(H101),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD101" s="21">
-        <f>MAX(0, MIN(I101, DATE(YEAR(H101),7,31)) - MAX(H101, DATE(YEAR(H101),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE101" s="21">
-        <f>MAX(0, MIN(I101, DATE(YEAR(H101),8,31)) - MAX(H101, DATE(YEAR(H101),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF101" s="21">
-        <f>MAX(0, MIN(I101, DATE(YEAR(H101),9,31)) - MAX(H101, DATE(YEAR(H101),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG101" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH101" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI101" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -17851,39 +17873,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA102" s="21">
-        <f>V102/153</f>
+        <f t="shared" si="24"/>
         <v>0.73856209150326801</v>
       </c>
       <c r="AB102" s="21">
-        <f>MAX(0, MIN(I102, DATE(YEAR(H102),5,31)) - MAX(H102, DATE(YEAR(H102),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC102" s="21">
-        <f>MAX(0, MIN(I102, DATE(YEAR(H102),6,31)) - MAX(H102, DATE(YEAR(H102),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="AD102" s="21">
-        <f>MAX(0, MIN(I102, DATE(YEAR(H102),7,31)) - MAX(H102, DATE(YEAR(H102),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE102" s="21">
-        <f>MAX(0, MIN(I102, DATE(YEAR(H102),8,31)) - MAX(H102, DATE(YEAR(H102),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF102" s="21">
-        <f>MAX(0, MIN(I102, DATE(YEAR(H102),9,31)) - MAX(H102, DATE(YEAR(H102),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG102" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
       <c r="AH102" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI102" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -17964,39 +17986,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA103" s="21">
-        <f>V103/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB103" s="21">
-        <f>MAX(0, MIN(I103, DATE(YEAR(H103),5,31)) - MAX(H103, DATE(YEAR(H103),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC103" s="21">
-        <f>MAX(0, MIN(I103, DATE(YEAR(H103),6,31)) - MAX(H103, DATE(YEAR(H103),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD103" s="21">
-        <f>MAX(0, MIN(I103, DATE(YEAR(H103),7,31)) - MAX(H103, DATE(YEAR(H103),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE103" s="21">
-        <f>MAX(0, MIN(I103, DATE(YEAR(H103),8,31)) - MAX(H103, DATE(YEAR(H103),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF103" s="21">
-        <f>MAX(0, MIN(I103, DATE(YEAR(H103),9,31)) - MAX(H103, DATE(YEAR(H103),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG103" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH103" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI103" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -18077,39 +18099,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA104" s="21">
-        <f>V104/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB104" s="21">
-        <f>MAX(0, MIN(I104, DATE(YEAR(H104),5,31)) - MAX(H104, DATE(YEAR(H104),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC104" s="21">
-        <f>MAX(0, MIN(I104, DATE(YEAR(H104),6,31)) - MAX(H104, DATE(YEAR(H104),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD104" s="21">
-        <f>MAX(0, MIN(I104, DATE(YEAR(H104),7,31)) - MAX(H104, DATE(YEAR(H104),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE104" s="21">
-        <f>MAX(0, MIN(I104, DATE(YEAR(H104),8,31)) - MAX(H104, DATE(YEAR(H104),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF104" s="21">
-        <f>MAX(0, MIN(I104, DATE(YEAR(H104),9,31)) - MAX(H104, DATE(YEAR(H104),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG104" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH104" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI104" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -18190,39 +18212,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA105" s="21">
-        <f>V105/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB105" s="21">
-        <f>MAX(0, MIN(I105, DATE(YEAR(H105),5,31)) - MAX(H105, DATE(YEAR(H105),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC105" s="21">
-        <f>MAX(0, MIN(I105, DATE(YEAR(H105),6,31)) - MAX(H105, DATE(YEAR(H105),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD105" s="21">
-        <f>MAX(0, MIN(I105, DATE(YEAR(H105),7,31)) - MAX(H105, DATE(YEAR(H105),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE105" s="21">
-        <f>MAX(0, MIN(I105, DATE(YEAR(H105),8,31)) - MAX(H105, DATE(YEAR(H105),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF105" s="21">
-        <f>MAX(0, MIN(I105, DATE(YEAR(H105),9,31)) - MAX(H105, DATE(YEAR(H105),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG105" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH105" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI105" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -18303,39 +18325,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA106" s="21">
-        <f>V106/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB106" s="21">
-        <f>MAX(0, MIN(I106, DATE(YEAR(H106),5,31)) - MAX(H106, DATE(YEAR(H106),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC106" s="21">
-        <f>MAX(0, MIN(I106, DATE(YEAR(H106),6,31)) - MAX(H106, DATE(YEAR(H106),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD106" s="21">
-        <f>MAX(0, MIN(I106, DATE(YEAR(H106),7,31)) - MAX(H106, DATE(YEAR(H106),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE106" s="21">
-        <f>MAX(0, MIN(I106, DATE(YEAR(H106),8,31)) - MAX(H106, DATE(YEAR(H106),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF106" s="21">
-        <f>MAX(0, MIN(I106, DATE(YEAR(H106),9,31)) - MAX(H106, DATE(YEAR(H106),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG106" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH106" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI106" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -18416,39 +18438,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA107" s="21">
-        <f>V107/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB107" s="21">
-        <f>MAX(0, MIN(I107, DATE(YEAR(H107),5,31)) - MAX(H107, DATE(YEAR(H107),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC107" s="21">
-        <f>MAX(0, MIN(I107, DATE(YEAR(H107),6,31)) - MAX(H107, DATE(YEAR(H107),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD107" s="21">
-        <f>MAX(0, MIN(I107, DATE(YEAR(H107),7,31)) - MAX(H107, DATE(YEAR(H107),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE107" s="21">
-        <f>MAX(0, MIN(I107, DATE(YEAR(H107),8,31)) - MAX(H107, DATE(YEAR(H107),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF107" s="21">
-        <f>MAX(0, MIN(I107, DATE(YEAR(H107),9,31)) - MAX(H107, DATE(YEAR(H107),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG107" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH107" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI107" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -18529,39 +18551,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA108" s="21">
-        <f>V108/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB108" s="21">
-        <f>MAX(0, MIN(I108, DATE(YEAR(H108),5,31)) - MAX(H108, DATE(YEAR(H108),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC108" s="21">
-        <f>MAX(0, MIN(I108, DATE(YEAR(H108),6,31)) - MAX(H108, DATE(YEAR(H108),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD108" s="21">
-        <f>MAX(0, MIN(I108, DATE(YEAR(H108),7,31)) - MAX(H108, DATE(YEAR(H108),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE108" s="21">
-        <f>MAX(0, MIN(I108, DATE(YEAR(H108),8,31)) - MAX(H108, DATE(YEAR(H108),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF108" s="21">
-        <f>MAX(0, MIN(I108, DATE(YEAR(H108),9,31)) - MAX(H108, DATE(YEAR(H108),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG108" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH108" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI108" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -18642,39 +18664,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA109" s="21">
-        <f>V109/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB109" s="21">
-        <f>MAX(0, MIN(I109, DATE(YEAR(H109),5,31)) - MAX(H109, DATE(YEAR(H109),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC109" s="21">
-        <f>MAX(0, MIN(I109, DATE(YEAR(H109),6,31)) - MAX(H109, DATE(YEAR(H109),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD109" s="21">
-        <f>MAX(0, MIN(I109, DATE(YEAR(H109),7,31)) - MAX(H109, DATE(YEAR(H109),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE109" s="21">
-        <f>MAX(0, MIN(I109, DATE(YEAR(H109),8,31)) - MAX(H109, DATE(YEAR(H109),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF109" s="21">
-        <f>MAX(0, MIN(I109, DATE(YEAR(H109),9,31)) - MAX(H109, DATE(YEAR(H109),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG109" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH109" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI109" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -18755,39 +18777,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA110" s="21">
-        <f>V110/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB110" s="21">
-        <f>MAX(0, MIN(I110, DATE(YEAR(H110),5,31)) - MAX(H110, DATE(YEAR(H110),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC110" s="21">
-        <f>MAX(0, MIN(I110, DATE(YEAR(H110),6,31)) - MAX(H110, DATE(YEAR(H110),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD110" s="21">
-        <f>MAX(0, MIN(I110, DATE(YEAR(H110),7,31)) - MAX(H110, DATE(YEAR(H110),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE110" s="21">
-        <f>MAX(0, MIN(I110, DATE(YEAR(H110),8,31)) - MAX(H110, DATE(YEAR(H110),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF110" s="21">
-        <f>MAX(0, MIN(I110, DATE(YEAR(H110),9,31)) - MAX(H110, DATE(YEAR(H110),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG110" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH110" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI110" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -18868,39 +18890,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA111" s="21">
-        <f>V111/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB111" s="21">
-        <f>MAX(0, MIN(I111, DATE(YEAR(H111),5,31)) - MAX(H111, DATE(YEAR(H111),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC111" s="21">
-        <f>MAX(0, MIN(I111, DATE(YEAR(H111),6,31)) - MAX(H111, DATE(YEAR(H111),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD111" s="21">
-        <f>MAX(0, MIN(I111, DATE(YEAR(H111),7,31)) - MAX(H111, DATE(YEAR(H111),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE111" s="21">
-        <f>MAX(0, MIN(I111, DATE(YEAR(H111),8,31)) - MAX(H111, DATE(YEAR(H111),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF111" s="21">
-        <f>MAX(0, MIN(I111, DATE(YEAR(H111),9,31)) - MAX(H111, DATE(YEAR(H111),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG111" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH111" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI111" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -18981,39 +19003,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA112" s="21">
-        <f>V112/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB112" s="21">
-        <f>MAX(0, MIN(I112, DATE(YEAR(H112),5,31)) - MAX(H112, DATE(YEAR(H112),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC112" s="21">
-        <f>MAX(0, MIN(I112, DATE(YEAR(H112),6,31)) - MAX(H112, DATE(YEAR(H112),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD112" s="21">
-        <f>MAX(0, MIN(I112, DATE(YEAR(H112),7,31)) - MAX(H112, DATE(YEAR(H112),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE112" s="21">
-        <f>MAX(0, MIN(I112, DATE(YEAR(H112),8,31)) - MAX(H112, DATE(YEAR(H112),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF112" s="21">
-        <f>MAX(0, MIN(I112, DATE(YEAR(H112),9,31)) - MAX(H112, DATE(YEAR(H112),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG112" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH112" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI112" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -19094,39 +19116,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA113" s="21">
-        <f>V113/153</f>
+        <f t="shared" si="24"/>
         <v>0.95424836601307195</v>
       </c>
       <c r="AB113" s="21">
-        <f>MAX(0, MIN(I113, DATE(YEAR(H113),5,31)) - MAX(H113, DATE(YEAR(H113),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC113" s="21">
-        <f>MAX(0, MIN(I113, DATE(YEAR(H113),6,31)) - MAX(H113, DATE(YEAR(H113),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD113" s="21">
-        <f>MAX(0, MIN(I113, DATE(YEAR(H113),7,31)) - MAX(H113, DATE(YEAR(H113),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE113" s="21">
-        <f>MAX(0, MIN(I113, DATE(YEAR(H113),8,31)) - MAX(H113, DATE(YEAR(H113),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF113" s="21">
-        <f>MAX(0, MIN(I113, DATE(YEAR(H113),9,31)) - MAX(H113, DATE(YEAR(H113),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>23</v>
       </c>
       <c r="AG113" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH113" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI113" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -19207,39 +19229,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA114" s="21">
-        <f>V114/153</f>
+        <f t="shared" si="24"/>
         <v>0.26143790849673204</v>
       </c>
       <c r="AB114" s="21">
-        <f>MAX(0, MIN(I114, DATE(YEAR(H114),5,31)) - MAX(H114, DATE(YEAR(H114),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC114" s="21">
-        <f>MAX(0, MIN(I114, DATE(YEAR(H114),6,31)) - MAX(H114, DATE(YEAR(H114),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>9</v>
       </c>
       <c r="AD114" s="21">
-        <f>MAX(0, MIN(I114, DATE(YEAR(H114),7,31)) - MAX(H114, DATE(YEAR(H114),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE114" s="21">
-        <f>MAX(0, MIN(I114, DATE(YEAR(H114),8,31)) - MAX(H114, DATE(YEAR(H114),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF114" s="21">
-        <f>MAX(0, MIN(I114, DATE(YEAR(H114),9,31)) - MAX(H114, DATE(YEAR(H114),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG114" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="AH114" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>FAIL</v>
       </c>
       <c r="AI114" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -19320,39 +19342,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA115" s="21">
-        <f>V115/153</f>
+        <f t="shared" si="24"/>
         <v>0.62745098039215685</v>
       </c>
       <c r="AB115" s="21">
-        <f>MAX(0, MIN(I115, DATE(YEAR(H115),5,31)) - MAX(H115, DATE(YEAR(H115),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC115" s="21">
-        <f>MAX(0, MIN(I115, DATE(YEAR(H115),6,31)) - MAX(H115, DATE(YEAR(H115),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>5</v>
       </c>
       <c r="AD115" s="21">
-        <f>MAX(0, MIN(I115, DATE(YEAR(H115),7,31)) - MAX(H115, DATE(YEAR(H115),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE115" s="21">
-        <f>MAX(0, MIN(I115, DATE(YEAR(H115),8,31)) - MAX(H115, DATE(YEAR(H115),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF115" s="21">
-        <f>MAX(0, MIN(I115, DATE(YEAR(H115),9,31)) - MAX(H115, DATE(YEAR(H115),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG115" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>3</v>
       </c>
       <c r="AH115" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI115" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -19433,39 +19455,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA116" s="21">
-        <f>V116/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB116" s="21">
-        <f>MAX(0, MIN(I116, DATE(YEAR(H116),5,31)) - MAX(H116, DATE(YEAR(H116),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC116" s="21">
-        <f>MAX(0, MIN(I116, DATE(YEAR(H116),6,31)) - MAX(H116, DATE(YEAR(H116),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD116" s="21">
-        <f>MAX(0, MIN(I116, DATE(YEAR(H116),7,31)) - MAX(H116, DATE(YEAR(H116),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE116" s="21">
-        <f>MAX(0, MIN(I116, DATE(YEAR(H116),8,31)) - MAX(H116, DATE(YEAR(H116),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF116" s="21">
-        <f>MAX(0, MIN(I116, DATE(YEAR(H116),9,31)) - MAX(H116, DATE(YEAR(H116),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG116" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH116" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI116" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -19546,39 +19568,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA117" s="21">
-        <f>V117/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB117" s="21">
-        <f>MAX(0, MIN(I117, DATE(YEAR(H117),5,31)) - MAX(H117, DATE(YEAR(H117),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC117" s="21">
-        <f>MAX(0, MIN(I117, DATE(YEAR(H117),6,31)) - MAX(H117, DATE(YEAR(H117),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD117" s="21">
-        <f>MAX(0, MIN(I117, DATE(YEAR(H117),7,31)) - MAX(H117, DATE(YEAR(H117),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE117" s="21">
-        <f>MAX(0, MIN(I117, DATE(YEAR(H117),8,31)) - MAX(H117, DATE(YEAR(H117),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF117" s="21">
-        <f>MAX(0, MIN(I117, DATE(YEAR(H117),9,31)) - MAX(H117, DATE(YEAR(H117),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG117" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH117" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI117" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -19659,39 +19681,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA118" s="21">
-        <f>V118/153</f>
+        <f t="shared" si="24"/>
         <v>0.23529411764705882</v>
       </c>
       <c r="AB118" s="21">
-        <f>MAX(0, MIN(I118, DATE(YEAR(H118),5,31)) - MAX(H118, DATE(YEAR(H118),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC118" s="21">
-        <f>MAX(0, MIN(I118, DATE(YEAR(H118),6,31)) - MAX(H118, DATE(YEAR(H118),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>5</v>
       </c>
       <c r="AD118" s="21">
-        <f>MAX(0, MIN(I118, DATE(YEAR(H118),7,31)) - MAX(H118, DATE(YEAR(H118),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE118" s="21">
-        <f>MAX(0, MIN(I118, DATE(YEAR(H118),8,31)) - MAX(H118, DATE(YEAR(H118),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF118" s="21">
-        <f>MAX(0, MIN(I118, DATE(YEAR(H118),9,31)) - MAX(H118, DATE(YEAR(H118),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG118" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="AH118" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>FAIL</v>
       </c>
       <c r="AI118" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -19772,39 +19794,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA119" s="21">
-        <f>V119/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB119" s="21">
-        <f>MAX(0, MIN(I119, DATE(YEAR(H119),5,31)) - MAX(H119, DATE(YEAR(H119),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC119" s="21">
-        <f>MAX(0, MIN(I119, DATE(YEAR(H119),6,31)) - MAX(H119, DATE(YEAR(H119),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD119" s="21">
-        <f>MAX(0, MIN(I119, DATE(YEAR(H119),7,31)) - MAX(H119, DATE(YEAR(H119),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE119" s="21">
-        <f>MAX(0, MIN(I119, DATE(YEAR(H119),8,31)) - MAX(H119, DATE(YEAR(H119),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF119" s="21">
-        <f>MAX(0, MIN(I119, DATE(YEAR(H119),9,31)) - MAX(H119, DATE(YEAR(H119),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG119" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH119" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI119" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -19885,39 +19907,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA120" s="21">
-        <f>V120/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB120" s="21">
-        <f>MAX(0, MIN(I120, DATE(YEAR(H120),5,31)) - MAX(H120, DATE(YEAR(H120),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC120" s="21">
-        <f>MAX(0, MIN(I120, DATE(YEAR(H120),6,31)) - MAX(H120, DATE(YEAR(H120),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD120" s="21">
-        <f>MAX(0, MIN(I120, DATE(YEAR(H120),7,31)) - MAX(H120, DATE(YEAR(H120),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE120" s="21">
-        <f>MAX(0, MIN(I120, DATE(YEAR(H120),8,31)) - MAX(H120, DATE(YEAR(H120),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF120" s="21">
-        <f>MAX(0, MIN(I120, DATE(YEAR(H120),9,31)) - MAX(H120, DATE(YEAR(H120),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG120" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH120" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI120" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -19998,39 +20020,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA121" s="21">
-        <f>V121/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB121" s="21">
-        <f>MAX(0, MIN(I121, DATE(YEAR(H121),5,31)) - MAX(H121, DATE(YEAR(H121),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC121" s="21">
-        <f>MAX(0, MIN(I121, DATE(YEAR(H121),6,31)) - MAX(H121, DATE(YEAR(H121),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD121" s="21">
-        <f>MAX(0, MIN(I121, DATE(YEAR(H121),7,31)) - MAX(H121, DATE(YEAR(H121),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE121" s="21">
-        <f>MAX(0, MIN(I121, DATE(YEAR(H121),8,31)) - MAX(H121, DATE(YEAR(H121),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF121" s="21">
-        <f>MAX(0, MIN(I121, DATE(YEAR(H121),9,31)) - MAX(H121, DATE(YEAR(H121),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG121" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH121" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI121" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -20111,39 +20133,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA122" s="21">
-        <f>V122/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB122" s="21">
-        <f>MAX(0, MIN(I122, DATE(YEAR(H122),5,31)) - MAX(H122, DATE(YEAR(H122),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC122" s="21">
-        <f>MAX(0, MIN(I122, DATE(YEAR(H122),6,31)) - MAX(H122, DATE(YEAR(H122),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD122" s="21">
-        <f>MAX(0, MIN(I122, DATE(YEAR(H122),7,31)) - MAX(H122, DATE(YEAR(H122),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE122" s="21">
-        <f>MAX(0, MIN(I122, DATE(YEAR(H122),8,31)) - MAX(H122, DATE(YEAR(H122),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF122" s="21">
-        <f>MAX(0, MIN(I122, DATE(YEAR(H122),9,31)) - MAX(H122, DATE(YEAR(H122),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG122" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH122" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI122" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -20224,39 +20246,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA123" s="21">
-        <f>V123/153</f>
+        <f t="shared" si="24"/>
         <v>0.23529411764705882</v>
       </c>
       <c r="AB123" s="21">
-        <f>MAX(0, MIN(I123, DATE(YEAR(H123),5,31)) - MAX(H123, DATE(YEAR(H123),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC123" s="21">
-        <f>MAX(0, MIN(I123, DATE(YEAR(H123),6,31)) - MAX(H123, DATE(YEAR(H123),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>5</v>
       </c>
       <c r="AD123" s="21">
-        <f>MAX(0, MIN(I123, DATE(YEAR(H123),7,31)) - MAX(H123, DATE(YEAR(H123),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE123" s="21">
-        <f>MAX(0, MIN(I123, DATE(YEAR(H123),8,31)) - MAX(H123, DATE(YEAR(H123),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF123" s="21">
-        <f>MAX(0, MIN(I123, DATE(YEAR(H123),9,31)) - MAX(H123, DATE(YEAR(H123),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG123" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>1</v>
       </c>
       <c r="AH123" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>FAIL</v>
       </c>
       <c r="AI123" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -20337,39 +20359,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA124" s="21">
-        <f>V124/153</f>
+        <f t="shared" si="24"/>
         <v>0.73856209150326801</v>
       </c>
       <c r="AB124" s="21">
-        <f>MAX(0, MIN(I124, DATE(YEAR(H124),5,31)) - MAX(H124, DATE(YEAR(H124),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>0</v>
       </c>
       <c r="AC124" s="21">
-        <f>MAX(0, MIN(I124, DATE(YEAR(H124),6,31)) - MAX(H124, DATE(YEAR(H124),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>22</v>
       </c>
       <c r="AD124" s="21">
-        <f>MAX(0, MIN(I124, DATE(YEAR(H124),7,31)) - MAX(H124, DATE(YEAR(H124),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE124" s="21">
-        <f>MAX(0, MIN(I124, DATE(YEAR(H124),8,31)) - MAX(H124, DATE(YEAR(H124),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF124" s="21">
-        <f>MAX(0, MIN(I124, DATE(YEAR(H124),9,31)) - MAX(H124, DATE(YEAR(H124),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG124" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>4</v>
       </c>
       <c r="AH124" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI124" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -20450,39 +20472,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA125" s="21">
-        <f>V125/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB125" s="21">
-        <f>MAX(0, MIN(I125, DATE(YEAR(H125),5,31)) - MAX(H125, DATE(YEAR(H125),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC125" s="21">
-        <f>MAX(0, MIN(I125, DATE(YEAR(H125),6,31)) - MAX(H125, DATE(YEAR(H125),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD125" s="21">
-        <f>MAX(0, MIN(I125, DATE(YEAR(H125),7,31)) - MAX(H125, DATE(YEAR(H125),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE125" s="21">
-        <f>MAX(0, MIN(I125, DATE(YEAR(H125),8,31)) - MAX(H125, DATE(YEAR(H125),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF125" s="21">
-        <f>MAX(0, MIN(I125, DATE(YEAR(H125),9,31)) - MAX(H125, DATE(YEAR(H125),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG125" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH125" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI125" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -20563,39 +20585,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA126" s="21">
-        <f>V126/153</f>
+        <f t="shared" si="24"/>
         <v>0.38562091503267976</v>
       </c>
       <c r="AB126" s="21">
-        <f>MAX(0, MIN(I126, DATE(YEAR(H126),5,31)) - MAX(H126, DATE(YEAR(H126),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC126" s="21">
-        <f>MAX(0, MIN(I126, DATE(YEAR(H126),6,31)) - MAX(H126, DATE(YEAR(H126),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>28</v>
       </c>
       <c r="AD126" s="21">
-        <f>MAX(0, MIN(I126, DATE(YEAR(H126),7,31)) - MAX(H126, DATE(YEAR(H126),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>0</v>
       </c>
       <c r="AE126" s="21">
-        <f>MAX(0, MIN(I126, DATE(YEAR(H126),8,31)) - MAX(H126, DATE(YEAR(H126),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="AF126" s="21">
-        <f>MAX(0, MIN(I126, DATE(YEAR(H126),9,31)) - MAX(H126, DATE(YEAR(H126),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="AG126" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>2</v>
       </c>
       <c r="AH126" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>FAIL</v>
       </c>
       <c r="AI126" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -20676,39 +20698,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA127" s="21">
-        <f>V127/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB127" s="21">
-        <f>MAX(0, MIN(I127, DATE(YEAR(H127),5,31)) - MAX(H127, DATE(YEAR(H127),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC127" s="21">
-        <f>MAX(0, MIN(I127, DATE(YEAR(H127),6,31)) - MAX(H127, DATE(YEAR(H127),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD127" s="21">
-        <f>MAX(0, MIN(I127, DATE(YEAR(H127),7,31)) - MAX(H127, DATE(YEAR(H127),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE127" s="21">
-        <f>MAX(0, MIN(I127, DATE(YEAR(H127),8,31)) - MAX(H127, DATE(YEAR(H127),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF127" s="21">
-        <f>MAX(0, MIN(I127, DATE(YEAR(H127),9,31)) - MAX(H127, DATE(YEAR(H127),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG127" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH127" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI127" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -20789,39 +20811,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA128" s="21">
-        <f>V128/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB128" s="21">
-        <f>MAX(0, MIN(I128, DATE(YEAR(H128),5,31)) - MAX(H128, DATE(YEAR(H128),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC128" s="21">
-        <f>MAX(0, MIN(I128, DATE(YEAR(H128),6,31)) - MAX(H128, DATE(YEAR(H128),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD128" s="21">
-        <f>MAX(0, MIN(I128, DATE(YEAR(H128),7,31)) - MAX(H128, DATE(YEAR(H128),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE128" s="21">
-        <f>MAX(0, MIN(I128, DATE(YEAR(H128),8,31)) - MAX(H128, DATE(YEAR(H128),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF128" s="21">
-        <f>MAX(0, MIN(I128, DATE(YEAR(H128),9,31)) - MAX(H128, DATE(YEAR(H128),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG128" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH128" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI128" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -20902,39 +20924,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA129" s="21">
-        <f>V129/153</f>
+        <f t="shared" si="24"/>
         <v>1</v>
       </c>
       <c r="AB129" s="21">
-        <f>MAX(0, MIN(I129, DATE(YEAR(H129),5,31)) - MAX(H129, DATE(YEAR(H129),5,1)) + 1)</f>
+        <f t="shared" si="25"/>
         <v>31</v>
       </c>
       <c r="AC129" s="21">
-        <f>MAX(0, MIN(I129, DATE(YEAR(H129),6,31)) - MAX(H129, DATE(YEAR(H129),6,1)) + 1)</f>
+        <f t="shared" si="26"/>
         <v>31</v>
       </c>
       <c r="AD129" s="21">
-        <f>MAX(0, MIN(I129, DATE(YEAR(H129),7,31)) - MAX(H129, DATE(YEAR(H129),7,1)) + 1)</f>
+        <f t="shared" si="27"/>
         <v>31</v>
       </c>
       <c r="AE129" s="21">
-        <f>MAX(0, MIN(I129, DATE(YEAR(H129),8,31)) - MAX(H129, DATE(YEAR(H129),8,1)) + 1)</f>
+        <f t="shared" si="28"/>
         <v>31</v>
       </c>
       <c r="AF129" s="21">
-        <f>MAX(0, MIN(I129, DATE(YEAR(H129),9,31)) - MAX(H129, DATE(YEAR(H129),9,1)) + 1)</f>
+        <f t="shared" si="29"/>
         <v>30</v>
       </c>
       <c r="AG129" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH129" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI129" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -21015,39 +21037,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA130" s="21">
-        <f>V130/153</f>
+        <f t="shared" ref="AA130:AA161" si="30">V130/153</f>
         <v>1</v>
       </c>
       <c r="AB130" s="21">
-        <f>MAX(0, MIN(I130, DATE(YEAR(H130),5,31)) - MAX(H130, DATE(YEAR(H130),5,1)) + 1)</f>
+        <f t="shared" ref="AB130:AB161" si="31">MAX(0, MIN(I130, DATE(YEAR(H130),5,31)) - MAX(H130, DATE(YEAR(H130),5,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AC130" s="21">
-        <f>MAX(0, MIN(I130, DATE(YEAR(H130),6,31)) - MAX(H130, DATE(YEAR(H130),6,1)) + 1)</f>
+        <f t="shared" ref="AC130:AC161" si="32">MAX(0, MIN(I130, DATE(YEAR(H130),6,31)) - MAX(H130, DATE(YEAR(H130),6,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AD130" s="21">
-        <f>MAX(0, MIN(I130, DATE(YEAR(H130),7,31)) - MAX(H130, DATE(YEAR(H130),7,1)) + 1)</f>
+        <f t="shared" ref="AD130:AD161" si="33">MAX(0, MIN(I130, DATE(YEAR(H130),7,31)) - MAX(H130, DATE(YEAR(H130),7,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AE130" s="21">
-        <f>MAX(0, MIN(I130, DATE(YEAR(H130),8,31)) - MAX(H130, DATE(YEAR(H130),8,1)) + 1)</f>
+        <f t="shared" ref="AE130:AE161" si="34">MAX(0, MIN(I130, DATE(YEAR(H130),8,31)) - MAX(H130, DATE(YEAR(H130),8,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AF130" s="21">
-        <f>MAX(0, MIN(I130, DATE(YEAR(H130),9,31)) - MAX(H130, DATE(YEAR(H130),9,1)) + 1)</f>
+        <f t="shared" ref="AF130:AF161" si="35">MAX(0, MIN(I130, DATE(YEAR(H130),9,31)) - MAX(H130, DATE(YEAR(H130),9,1)) + 1)</f>
         <v>30</v>
       </c>
       <c r="AG130" s="21">
-        <f t="shared" si="3"/>
+        <f t="shared" si="21"/>
         <v>5</v>
       </c>
       <c r="AH130" s="21" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="22"/>
         <v>PASS</v>
       </c>
       <c r="AI130" s="21" t="str">
-        <f t="shared" si="5"/>
+        <f t="shared" si="23"/>
         <v>PASS</v>
       </c>
     </row>
@@ -21128,39 +21150,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA131" s="21">
-        <f>V131/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB131" s="21">
-        <f>MAX(0, MIN(I131, DATE(YEAR(H131),5,31)) - MAX(H131, DATE(YEAR(H131),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC131" s="21">
-        <f>MAX(0, MIN(I131, DATE(YEAR(H131),6,31)) - MAX(H131, DATE(YEAR(H131),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD131" s="21">
-        <f>MAX(0, MIN(I131, DATE(YEAR(H131),7,31)) - MAX(H131, DATE(YEAR(H131),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE131" s="21">
-        <f>MAX(0, MIN(I131, DATE(YEAR(H131),8,31)) - MAX(H131, DATE(YEAR(H131),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF131" s="21">
-        <f>MAX(0, MIN(I131, DATE(YEAR(H131),9,31)) - MAX(H131, DATE(YEAR(H131),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG131" s="21">
-        <f t="shared" ref="AG131:AG140" si="6">COUNTIF(AB131:AF131, "&gt;=10")</f>
+        <f t="shared" ref="AG131:AG140" si="36">COUNTIF(AB131:AF131, "&gt;=10")</f>
         <v>5</v>
       </c>
       <c r="AH131" s="21" t="str">
-        <f t="shared" ref="AH131:AH140" si="7">IF(COUNTIF(AB131:AF131,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
+        <f t="shared" ref="AH131:AH140" si="37">IF(COUNTIF(AB131:AF131,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
         <v>PASS</v>
       </c>
       <c r="AI131" s="21" t="str">
-        <f t="shared" ref="AI131:AI140" si="8">IF(AND(AA131&gt;=0.8, COUNTIF(AB131:AF131, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
+        <f t="shared" ref="AI131:AI140" si="38">IF(AND(AA131&gt;=0.8, COUNTIF(AB131:AF131, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
         <v>PASS</v>
       </c>
     </row>
@@ -21241,39 +21263,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA132" s="21">
-        <f>V132/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB132" s="21">
-        <f>MAX(0, MIN(I132, DATE(YEAR(H132),5,31)) - MAX(H132, DATE(YEAR(H132),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC132" s="21">
-        <f>MAX(0, MIN(I132, DATE(YEAR(H132),6,31)) - MAX(H132, DATE(YEAR(H132),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD132" s="21">
-        <f>MAX(0, MIN(I132, DATE(YEAR(H132),7,31)) - MAX(H132, DATE(YEAR(H132),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE132" s="21">
-        <f>MAX(0, MIN(I132, DATE(YEAR(H132),8,31)) - MAX(H132, DATE(YEAR(H132),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF132" s="21">
-        <f>MAX(0, MIN(I132, DATE(YEAR(H132),9,31)) - MAX(H132, DATE(YEAR(H132),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG132" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
       <c r="AH132" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>PASS</v>
       </c>
       <c r="AI132" s="21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>PASS</v>
       </c>
     </row>
@@ -21354,39 +21376,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA133" s="21">
-        <f>V133/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB133" s="21">
-        <f>MAX(0, MIN(I133, DATE(YEAR(H133),5,31)) - MAX(H133, DATE(YEAR(H133),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC133" s="21">
-        <f>MAX(0, MIN(I133, DATE(YEAR(H133),6,31)) - MAX(H133, DATE(YEAR(H133),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD133" s="21">
-        <f>MAX(0, MIN(I133, DATE(YEAR(H133),7,31)) - MAX(H133, DATE(YEAR(H133),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE133" s="21">
-        <f>MAX(0, MIN(I133, DATE(YEAR(H133),8,31)) - MAX(H133, DATE(YEAR(H133),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF133" s="21">
-        <f>MAX(0, MIN(I133, DATE(YEAR(H133),9,31)) - MAX(H133, DATE(YEAR(H133),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG133" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
       <c r="AH133" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>PASS</v>
       </c>
       <c r="AI133" s="21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>PASS</v>
       </c>
     </row>
@@ -21467,39 +21489,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA134" s="21">
-        <f>V134/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB134" s="21">
-        <f>MAX(0, MIN(I134, DATE(YEAR(H134),5,31)) - MAX(H134, DATE(YEAR(H134),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC134" s="21">
-        <f>MAX(0, MIN(I134, DATE(YEAR(H134),6,31)) - MAX(H134, DATE(YEAR(H134),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD134" s="21">
-        <f>MAX(0, MIN(I134, DATE(YEAR(H134),7,31)) - MAX(H134, DATE(YEAR(H134),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE134" s="21">
-        <f>MAX(0, MIN(I134, DATE(YEAR(H134),8,31)) - MAX(H134, DATE(YEAR(H134),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF134" s="21">
-        <f>MAX(0, MIN(I134, DATE(YEAR(H134),9,31)) - MAX(H134, DATE(YEAR(H134),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG134" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
       <c r="AH134" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>PASS</v>
       </c>
       <c r="AI134" s="21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>PASS</v>
       </c>
     </row>
@@ -21580,39 +21602,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA135" s="21">
-        <f>V135/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB135" s="21">
-        <f>MAX(0, MIN(I135, DATE(YEAR(H135),5,31)) - MAX(H135, DATE(YEAR(H135),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC135" s="21">
-        <f>MAX(0, MIN(I135, DATE(YEAR(H135),6,31)) - MAX(H135, DATE(YEAR(H135),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD135" s="21">
-        <f>MAX(0, MIN(I135, DATE(YEAR(H135),7,31)) - MAX(H135, DATE(YEAR(H135),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE135" s="21">
-        <f>MAX(0, MIN(I135, DATE(YEAR(H135),8,31)) - MAX(H135, DATE(YEAR(H135),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF135" s="21">
-        <f>MAX(0, MIN(I135, DATE(YEAR(H135),9,31)) - MAX(H135, DATE(YEAR(H135),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG135" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
       <c r="AH135" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>PASS</v>
       </c>
       <c r="AI135" s="21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>PASS</v>
       </c>
     </row>
@@ -21693,39 +21715,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA136" s="21">
-        <f>V136/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB136" s="21">
-        <f>MAX(0, MIN(I136, DATE(YEAR(H136),5,31)) - MAX(H136, DATE(YEAR(H136),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC136" s="21">
-        <f>MAX(0, MIN(I136, DATE(YEAR(H136),6,31)) - MAX(H136, DATE(YEAR(H136),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD136" s="21">
-        <f>MAX(0, MIN(I136, DATE(YEAR(H136),7,31)) - MAX(H136, DATE(YEAR(H136),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE136" s="21">
-        <f>MAX(0, MIN(I136, DATE(YEAR(H136),8,31)) - MAX(H136, DATE(YEAR(H136),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF136" s="21">
-        <f>MAX(0, MIN(I136, DATE(YEAR(H136),9,31)) - MAX(H136, DATE(YEAR(H136),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG136" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
       <c r="AH136" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>PASS</v>
       </c>
       <c r="AI136" s="21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>PASS</v>
       </c>
     </row>
@@ -21806,39 +21828,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA137" s="21">
-        <f>V137/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB137" s="21">
-        <f>MAX(0, MIN(I137, DATE(YEAR(H137),5,31)) - MAX(H137, DATE(YEAR(H137),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC137" s="21">
-        <f>MAX(0, MIN(I137, DATE(YEAR(H137),6,31)) - MAX(H137, DATE(YEAR(H137),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD137" s="21">
-        <f>MAX(0, MIN(I137, DATE(YEAR(H137),7,31)) - MAX(H137, DATE(YEAR(H137),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE137" s="21">
-        <f>MAX(0, MIN(I137, DATE(YEAR(H137),8,31)) - MAX(H137, DATE(YEAR(H137),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF137" s="21">
-        <f>MAX(0, MIN(I137, DATE(YEAR(H137),9,31)) - MAX(H137, DATE(YEAR(H137),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG137" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
       <c r="AH137" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>PASS</v>
       </c>
       <c r="AI137" s="21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>PASS</v>
       </c>
     </row>
@@ -21919,39 +21941,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA138" s="21">
-        <f>V138/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB138" s="21">
-        <f>MAX(0, MIN(I138, DATE(YEAR(H138),5,31)) - MAX(H138, DATE(YEAR(H138),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC138" s="21">
-        <f>MAX(0, MIN(I138, DATE(YEAR(H138),6,31)) - MAX(H138, DATE(YEAR(H138),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD138" s="21">
-        <f>MAX(0, MIN(I138, DATE(YEAR(H138),7,31)) - MAX(H138, DATE(YEAR(H138),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE138" s="21">
-        <f>MAX(0, MIN(I138, DATE(YEAR(H138),8,31)) - MAX(H138, DATE(YEAR(H138),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF138" s="21">
-        <f>MAX(0, MIN(I138, DATE(YEAR(H138),9,31)) - MAX(H138, DATE(YEAR(H138),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG138" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
       <c r="AH138" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>PASS</v>
       </c>
       <c r="AI138" s="21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>PASS</v>
       </c>
     </row>
@@ -22032,39 +22054,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA139" s="21">
-        <f>V139/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB139" s="21">
-        <f>MAX(0, MIN(I139, DATE(YEAR(H139),5,31)) - MAX(H139, DATE(YEAR(H139),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC139" s="21">
-        <f>MAX(0, MIN(I139, DATE(YEAR(H139),6,31)) - MAX(H139, DATE(YEAR(H139),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD139" s="21">
-        <f>MAX(0, MIN(I139, DATE(YEAR(H139),7,31)) - MAX(H139, DATE(YEAR(H139),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE139" s="21">
-        <f>MAX(0, MIN(I139, DATE(YEAR(H139),8,31)) - MAX(H139, DATE(YEAR(H139),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF139" s="21">
-        <f>MAX(0, MIN(I139, DATE(YEAR(H139),9,31)) - MAX(H139, DATE(YEAR(H139),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG139" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>5</v>
       </c>
       <c r="AH139" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>PASS</v>
       </c>
       <c r="AI139" s="21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>PASS</v>
       </c>
     </row>
@@ -22145,39 +22167,39 @@
         <v>-75.182500000000005</v>
       </c>
       <c r="AA140" s="21">
-        <f>V140/153</f>
+        <f t="shared" si="30"/>
         <v>0.23529411764705882</v>
       </c>
       <c r="AB140" s="21">
-        <f>MAX(0, MIN(I140, DATE(YEAR(H140),5,31)) - MAX(H140, DATE(YEAR(H140),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC140" s="21">
-        <f>MAX(0, MIN(I140, DATE(YEAR(H140),6,31)) - MAX(H140, DATE(YEAR(H140),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>5</v>
       </c>
       <c r="AD140" s="21">
-        <f>MAX(0, MIN(I140, DATE(YEAR(H140),7,31)) - MAX(H140, DATE(YEAR(H140),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AE140" s="21">
-        <f>MAX(0, MIN(I140, DATE(YEAR(H140),8,31)) - MAX(H140, DATE(YEAR(H140),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AF140" s="21">
-        <f>MAX(0, MIN(I140, DATE(YEAR(H140),9,31)) - MAX(H140, DATE(YEAR(H140),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AG140" s="21">
-        <f t="shared" si="6"/>
+        <f t="shared" si="36"/>
         <v>1</v>
       </c>
       <c r="AH140" s="21" t="str">
-        <f t="shared" si="7"/>
+        <f t="shared" si="37"/>
         <v>FAIL</v>
       </c>
       <c r="AI140" s="21" t="str">
-        <f t="shared" si="8"/>
+        <f t="shared" si="38"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -22258,39 +22280,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA141" s="21">
-        <f>V141/153</f>
+        <f t="shared" si="30"/>
         <v>9.8039215686274508E-2</v>
       </c>
       <c r="AB141" s="21">
-        <f>MAX(0, MIN(I141, DATE(YEAR(H141),5,31)) - MAX(H141, DATE(YEAR(H141),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>5</v>
       </c>
       <c r="AC141" s="21">
-        <f>MAX(0, MIN(I141, DATE(YEAR(H141),6,31)) - MAX(H141, DATE(YEAR(H141),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>10</v>
       </c>
       <c r="AD141" s="21">
-        <f>MAX(0, MIN(I141, DATE(YEAR(H141),7,31)) - MAX(H141, DATE(YEAR(H141),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AE141" s="21">
-        <f>MAX(0, MIN(I141, DATE(YEAR(H141),8,31)) - MAX(H141, DATE(YEAR(H141),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AF141" s="21">
-        <f>MAX(0, MIN(I141, DATE(YEAR(H141),9,31)) - MAX(H141, DATE(YEAR(H141),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AG141" s="21">
-        <f t="shared" ref="AG141:AG155" si="9">COUNTIF(AB141:AF141, "&gt;=10")</f>
+        <f t="shared" ref="AG141:AG155" si="39">COUNTIF(AB141:AF141, "&gt;=10")</f>
         <v>1</v>
       </c>
       <c r="AH141" s="21" t="str">
-        <f t="shared" ref="AH141:AH155" si="10">IF(COUNTIF(AB141:AF141,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
+        <f t="shared" ref="AH141:AH155" si="40">IF(COUNTIF(AB141:AF141,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
       <c r="AI141" s="21" t="str">
-        <f t="shared" ref="AI141:AI155" si="11">IF(AND(AA141&gt;=0.8, COUNTIF(AB141:AF141, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
+        <f t="shared" ref="AI141:AI155" si="41">IF(AND(AA141&gt;=0.8, COUNTIF(AB141:AF141, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
         <v>FAIL</v>
       </c>
     </row>
@@ -22371,39 +22393,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA142" s="21">
-        <f>V142/153</f>
+        <f t="shared" si="30"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="AB142" s="21">
-        <f>MAX(0, MIN(I142, DATE(YEAR(H142),5,31)) - MAX(H142, DATE(YEAR(H142),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AC142" s="21">
-        <f>MAX(0, MIN(I142, DATE(YEAR(H142),6,31)) - MAX(H142, DATE(YEAR(H142),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD142" s="21">
-        <f>MAX(0, MIN(I142, DATE(YEAR(H142),7,31)) - MAX(H142, DATE(YEAR(H142),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AE142" s="21">
-        <f>MAX(0, MIN(I142, DATE(YEAR(H142),8,31)) - MAX(H142, DATE(YEAR(H142),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>27</v>
       </c>
       <c r="AF142" s="21">
-        <f>MAX(0, MIN(I142, DATE(YEAR(H142),9,31)) - MAX(H142, DATE(YEAR(H142),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>7</v>
       </c>
       <c r="AG142" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="AH142" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>FAIL</v>
       </c>
       <c r="AI142" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -22484,39 +22506,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA143" s="21">
-        <f>V143/153</f>
+        <f t="shared" si="30"/>
         <v>0.13071895424836602</v>
       </c>
       <c r="AB143" s="21">
-        <f>MAX(0, MIN(I143, DATE(YEAR(H143),5,31)) - MAX(H143, DATE(YEAR(H143),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AC143" s="21">
-        <f>MAX(0, MIN(I143, DATE(YEAR(H143),6,31)) - MAX(H143, DATE(YEAR(H143),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD143" s="21">
-        <f>MAX(0, MIN(I143, DATE(YEAR(H143),7,31)) - MAX(H143, DATE(YEAR(H143),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>13</v>
       </c>
       <c r="AE143" s="21">
-        <f>MAX(0, MIN(I143, DATE(YEAR(H143),8,31)) - MAX(H143, DATE(YEAR(H143),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>7</v>
       </c>
       <c r="AF143" s="21">
-        <f>MAX(0, MIN(I143, DATE(YEAR(H143),9,31)) - MAX(H143, DATE(YEAR(H143),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AG143" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="AH143" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>FAIL</v>
       </c>
       <c r="AI143" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -22597,39 +22619,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA144" s="21">
-        <f>V144/153</f>
+        <f t="shared" si="30"/>
         <v>0.12418300653594772</v>
       </c>
       <c r="AB144" s="21">
-        <f>MAX(0, MIN(I144, DATE(YEAR(H144),5,31)) - MAX(H144, DATE(YEAR(H144),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AC144" s="21">
-        <f>MAX(0, MIN(I144, DATE(YEAR(H144),6,31)) - MAX(H144, DATE(YEAR(H144),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD144" s="21">
-        <f>MAX(0, MIN(I144, DATE(YEAR(H144),7,31)) - MAX(H144, DATE(YEAR(H144),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>7</v>
       </c>
       <c r="AE144" s="21">
-        <f>MAX(0, MIN(I144, DATE(YEAR(H144),8,31)) - MAX(H144, DATE(YEAR(H144),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>12</v>
       </c>
       <c r="AF144" s="21">
-        <f>MAX(0, MIN(I144, DATE(YEAR(H144),9,31)) - MAX(H144, DATE(YEAR(H144),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AG144" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="AH144" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>FAIL</v>
       </c>
       <c r="AI144" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -22710,39 +22732,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA145" s="21">
-        <f>V145/153</f>
+        <f t="shared" si="30"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="AB145" s="21">
-        <f>MAX(0, MIN(I145, DATE(YEAR(H145),5,31)) - MAX(H145, DATE(YEAR(H145),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AC145" s="21">
-        <f>MAX(0, MIN(I145, DATE(YEAR(H145),6,31)) - MAX(H145, DATE(YEAR(H145),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD145" s="21">
-        <f>MAX(0, MIN(I145, DATE(YEAR(H145),7,31)) - MAX(H145, DATE(YEAR(H145),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AE145" s="21">
-        <f>MAX(0, MIN(I145, DATE(YEAR(H145),8,31)) - MAX(H145, DATE(YEAR(H145),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>17</v>
       </c>
       <c r="AF145" s="21">
-        <f>MAX(0, MIN(I145, DATE(YEAR(H145),9,31)) - MAX(H145, DATE(YEAR(H145),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AG145" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="AH145" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>FAIL</v>
       </c>
       <c r="AI145" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -22823,39 +22845,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA146" s="21">
-        <f>V146/153</f>
+        <f t="shared" si="30"/>
         <v>8.4967320261437912E-2</v>
       </c>
       <c r="AB146" s="21">
-        <f>MAX(0, MIN(I146, DATE(YEAR(H146),5,31)) - MAX(H146, DATE(YEAR(H146),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AC146" s="21">
-        <f>MAX(0, MIN(I146, DATE(YEAR(H146),6,31)) - MAX(H146, DATE(YEAR(H146),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD146" s="21">
-        <f>MAX(0, MIN(I146, DATE(YEAR(H146),7,31)) - MAX(H146, DATE(YEAR(H146),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AE146" s="21">
-        <f>MAX(0, MIN(I146, DATE(YEAR(H146),8,31)) - MAX(H146, DATE(YEAR(H146),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>1</v>
       </c>
       <c r="AF146" s="21">
-        <f>MAX(0, MIN(I146, DATE(YEAR(H146),9,31)) - MAX(H146, DATE(YEAR(H146),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>12</v>
       </c>
       <c r="AG146" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>1</v>
       </c>
       <c r="AH146" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>FAIL</v>
       </c>
       <c r="AI146" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -22936,39 +22958,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA147" s="21">
-        <f>V147/153</f>
+        <f t="shared" si="30"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AB147" s="21">
-        <f>MAX(0, MIN(I147, DATE(YEAR(H147),5,31)) - MAX(H147, DATE(YEAR(H147),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AC147" s="21">
-        <f>MAX(0, MIN(I147, DATE(YEAR(H147),6,31)) - MAX(H147, DATE(YEAR(H147),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD147" s="21">
-        <f>MAX(0, MIN(I147, DATE(YEAR(H147),7,31)) - MAX(H147, DATE(YEAR(H147),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AE147" s="21">
-        <f>MAX(0, MIN(I147, DATE(YEAR(H147),8,31)) - MAX(H147, DATE(YEAR(H147),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>21</v>
       </c>
       <c r="AF147" s="21">
-        <f>MAX(0, MIN(I147, DATE(YEAR(H147),9,31)) - MAX(H147, DATE(YEAR(H147),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG147" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>2</v>
       </c>
       <c r="AH147" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>FAIL</v>
       </c>
       <c r="AI147" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -23049,39 +23071,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA148" s="21">
-        <f>V148/153</f>
+        <f t="shared" si="30"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="AB148" s="21">
-        <f>MAX(0, MIN(I148, DATE(YEAR(H148),5,31)) - MAX(H148, DATE(YEAR(H148),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AC148" s="21">
-        <f>MAX(0, MIN(I148, DATE(YEAR(H148),6,31)) - MAX(H148, DATE(YEAR(H148),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>11</v>
       </c>
       <c r="AD148" s="21">
-        <f>MAX(0, MIN(I148, DATE(YEAR(H148),7,31)) - MAX(H148, DATE(YEAR(H148),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE148" s="21">
-        <f>MAX(0, MIN(I148, DATE(YEAR(H148),8,31)) - MAX(H148, DATE(YEAR(H148),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF148" s="21">
-        <f>MAX(0, MIN(I148, DATE(YEAR(H148),9,31)) - MAX(H148, DATE(YEAR(H148),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG148" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>4</v>
       </c>
       <c r="AH148" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>PASS</v>
       </c>
       <c r="AI148" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -23162,39 +23184,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA149" s="21">
-        <f>V149/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB149" s="21">
-        <f>MAX(0, MIN(I149, DATE(YEAR(H149),5,31)) - MAX(H149, DATE(YEAR(H149),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC149" s="21">
-        <f>MAX(0, MIN(I149, DATE(YEAR(H149),6,31)) - MAX(H149, DATE(YEAR(H149),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD149" s="21">
-        <f>MAX(0, MIN(I149, DATE(YEAR(H149),7,31)) - MAX(H149, DATE(YEAR(H149),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE149" s="21">
-        <f>MAX(0, MIN(I149, DATE(YEAR(H149),8,31)) - MAX(H149, DATE(YEAR(H149),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF149" s="21">
-        <f>MAX(0, MIN(I149, DATE(YEAR(H149),9,31)) - MAX(H149, DATE(YEAR(H149),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG149" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>5</v>
       </c>
       <c r="AH149" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>PASS</v>
       </c>
       <c r="AI149" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>PASS</v>
       </c>
     </row>
@@ -23275,39 +23297,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA150" s="21">
-        <f>V150/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB150" s="21">
-        <f>MAX(0, MIN(I150, DATE(YEAR(H150),5,31)) - MAX(H150, DATE(YEAR(H150),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC150" s="21">
-        <f>MAX(0, MIN(I150, DATE(YEAR(H150),6,31)) - MAX(H150, DATE(YEAR(H150),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD150" s="21">
-        <f>MAX(0, MIN(I150, DATE(YEAR(H150),7,31)) - MAX(H150, DATE(YEAR(H150),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE150" s="21">
-        <f>MAX(0, MIN(I150, DATE(YEAR(H150),8,31)) - MAX(H150, DATE(YEAR(H150),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF150" s="21">
-        <f>MAX(0, MIN(I150, DATE(YEAR(H150),9,31)) - MAX(H150, DATE(YEAR(H150),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG150" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>5</v>
       </c>
       <c r="AH150" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>PASS</v>
       </c>
       <c r="AI150" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>PASS</v>
       </c>
     </row>
@@ -23388,39 +23410,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA151" s="21">
-        <f>V151/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB151" s="21">
-        <f>MAX(0, MIN(I151, DATE(YEAR(H151),5,31)) - MAX(H151, DATE(YEAR(H151),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC151" s="21">
-        <f>MAX(0, MIN(I151, DATE(YEAR(H151),6,31)) - MAX(H151, DATE(YEAR(H151),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD151" s="21">
-        <f>MAX(0, MIN(I151, DATE(YEAR(H151),7,31)) - MAX(H151, DATE(YEAR(H151),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE151" s="21">
-        <f>MAX(0, MIN(I151, DATE(YEAR(H151),8,31)) - MAX(H151, DATE(YEAR(H151),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF151" s="21">
-        <f>MAX(0, MIN(I151, DATE(YEAR(H151),9,31)) - MAX(H151, DATE(YEAR(H151),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG151" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>5</v>
       </c>
       <c r="AH151" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>PASS</v>
       </c>
       <c r="AI151" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>PASS</v>
       </c>
     </row>
@@ -23501,39 +23523,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA152" s="21">
-        <f>V152/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB152" s="21">
-        <f>MAX(0, MIN(I152, DATE(YEAR(H152),5,31)) - MAX(H152, DATE(YEAR(H152),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC152" s="21">
-        <f>MAX(0, MIN(I152, DATE(YEAR(H152),6,31)) - MAX(H152, DATE(YEAR(H152),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD152" s="21">
-        <f>MAX(0, MIN(I152, DATE(YEAR(H152),7,31)) - MAX(H152, DATE(YEAR(H152),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE152" s="21">
-        <f>MAX(0, MIN(I152, DATE(YEAR(H152),8,31)) - MAX(H152, DATE(YEAR(H152),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF152" s="21">
-        <f>MAX(0, MIN(I152, DATE(YEAR(H152),9,31)) - MAX(H152, DATE(YEAR(H152),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG152" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>5</v>
       </c>
       <c r="AH152" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>PASS</v>
       </c>
       <c r="AI152" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>PASS</v>
       </c>
     </row>
@@ -23614,39 +23636,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA153" s="21">
-        <f>V153/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB153" s="21">
-        <f>MAX(0, MIN(I153, DATE(YEAR(H153),5,31)) - MAX(H153, DATE(YEAR(H153),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC153" s="21">
-        <f>MAX(0, MIN(I153, DATE(YEAR(H153),6,31)) - MAX(H153, DATE(YEAR(H153),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD153" s="21">
-        <f>MAX(0, MIN(I153, DATE(YEAR(H153),7,31)) - MAX(H153, DATE(YEAR(H153),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE153" s="21">
-        <f>MAX(0, MIN(I153, DATE(YEAR(H153),8,31)) - MAX(H153, DATE(YEAR(H153),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF153" s="21">
-        <f>MAX(0, MIN(I153, DATE(YEAR(H153),9,31)) - MAX(H153, DATE(YEAR(H153),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG153" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>5</v>
       </c>
       <c r="AH153" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>PASS</v>
       </c>
       <c r="AI153" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>PASS</v>
       </c>
     </row>
@@ -23727,39 +23749,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA154" s="21">
-        <f>V154/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB154" s="21">
-        <f>MAX(0, MIN(I154, DATE(YEAR(H154),5,31)) - MAX(H154, DATE(YEAR(H154),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC154" s="21">
-        <f>MAX(0, MIN(I154, DATE(YEAR(H154),6,31)) - MAX(H154, DATE(YEAR(H154),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD154" s="21">
-        <f>MAX(0, MIN(I154, DATE(YEAR(H154),7,31)) - MAX(H154, DATE(YEAR(H154),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE154" s="21">
-        <f>MAX(0, MIN(I154, DATE(YEAR(H154),8,31)) - MAX(H154, DATE(YEAR(H154),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF154" s="21">
-        <f>MAX(0, MIN(I154, DATE(YEAR(H154),9,31)) - MAX(H154, DATE(YEAR(H154),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG154" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>5</v>
       </c>
       <c r="AH154" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>PASS</v>
       </c>
       <c r="AI154" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>PASS</v>
       </c>
     </row>
@@ -23840,39 +23862,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA155" s="21">
-        <f>V155/153</f>
+        <f t="shared" si="30"/>
         <v>0.6470588235294118</v>
       </c>
       <c r="AB155" s="21">
-        <f>MAX(0, MIN(I155, DATE(YEAR(H155),5,31)) - MAX(H155, DATE(YEAR(H155),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC155" s="21">
-        <f>MAX(0, MIN(I155, DATE(YEAR(H155),6,31)) - MAX(H155, DATE(YEAR(H155),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD155" s="21">
-        <f>MAX(0, MIN(I155, DATE(YEAR(H155),7,31)) - MAX(H155, DATE(YEAR(H155),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE155" s="21">
-        <f>MAX(0, MIN(I155, DATE(YEAR(H155),8,31)) - MAX(H155, DATE(YEAR(H155),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>7</v>
       </c>
       <c r="AF155" s="21">
-        <f>MAX(0, MIN(I155, DATE(YEAR(H155),9,31)) - MAX(H155, DATE(YEAR(H155),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AG155" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="39"/>
         <v>3</v>
       </c>
       <c r="AH155" s="21" t="str">
-        <f t="shared" si="10"/>
+        <f t="shared" si="40"/>
         <v>PASS</v>
       </c>
       <c r="AI155" s="21" t="str">
-        <f t="shared" si="11"/>
+        <f t="shared" si="41"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -23953,39 +23975,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA156" s="21">
-        <f>V156/153</f>
+        <f t="shared" si="30"/>
         <v>9.8039215686274508E-2</v>
       </c>
       <c r="AB156" s="21">
-        <f>MAX(0, MIN(I156, DATE(YEAR(H156),5,31)) - MAX(H156, DATE(YEAR(H156),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>5</v>
       </c>
       <c r="AC156" s="21">
-        <f>MAX(0, MIN(I156, DATE(YEAR(H156),6,31)) - MAX(H156, DATE(YEAR(H156),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>10</v>
       </c>
       <c r="AD156" s="21">
-        <f>MAX(0, MIN(I156, DATE(YEAR(H156),7,31)) - MAX(H156, DATE(YEAR(H156),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AE156" s="21">
-        <f>MAX(0, MIN(I156, DATE(YEAR(H156),8,31)) - MAX(H156, DATE(YEAR(H156),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>0</v>
       </c>
       <c r="AF156" s="21">
-        <f>MAX(0, MIN(I156, DATE(YEAR(H156),9,31)) - MAX(H156, DATE(YEAR(H156),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>0</v>
       </c>
       <c r="AG156" s="21">
-        <f t="shared" ref="AG156:AG162" si="12">COUNTIF(AB156:AF156, "&gt;=10")</f>
+        <f t="shared" ref="AG156:AG162" si="42">COUNTIF(AB156:AF156, "&gt;=10")</f>
         <v>1</v>
       </c>
       <c r="AH156" s="21" t="str">
-        <f t="shared" ref="AH156:AH162" si="13">IF(COUNTIF(AB156:AF156,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
+        <f t="shared" ref="AH156:AH162" si="43">IF(COUNTIF(AB156:AF156,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
       <c r="AI156" s="21" t="str">
-        <f t="shared" ref="AI156:AI162" si="14">IF(AND(AA156&gt;=0.8, COUNTIF(AB156:AF156, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
+        <f t="shared" ref="AI156:AI162" si="44">IF(AND(AA156&gt;=0.8, COUNTIF(AB156:AF156, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
         <v>FAIL</v>
       </c>
     </row>
@@ -24066,39 +24088,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA157" s="21">
-        <f>V157/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB157" s="21">
-        <f>MAX(0, MIN(I157, DATE(YEAR(H157),5,31)) - MAX(H157, DATE(YEAR(H157),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC157" s="21">
-        <f>MAX(0, MIN(I157, DATE(YEAR(H157),6,31)) - MAX(H157, DATE(YEAR(H157),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD157" s="21">
-        <f>MAX(0, MIN(I157, DATE(YEAR(H157),7,31)) - MAX(H157, DATE(YEAR(H157),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE157" s="21">
-        <f>MAX(0, MIN(I157, DATE(YEAR(H157),8,31)) - MAX(H157, DATE(YEAR(H157),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF157" s="21">
-        <f>MAX(0, MIN(I157, DATE(YEAR(H157),9,31)) - MAX(H157, DATE(YEAR(H157),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG157" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="AH157" s="21" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="43"/>
         <v>PASS</v>
       </c>
       <c r="AI157" s="21" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>PASS</v>
       </c>
     </row>
@@ -24179,39 +24201,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA158" s="21">
-        <f>V158/153</f>
+        <f t="shared" si="30"/>
         <v>0.37254901960784315</v>
       </c>
       <c r="AB158" s="21">
-        <f>MAX(0, MIN(I158, DATE(YEAR(H158),5,31)) - MAX(H158, DATE(YEAR(H158),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>0</v>
       </c>
       <c r="AC158" s="21">
-        <f>MAX(0, MIN(I158, DATE(YEAR(H158),6,31)) - MAX(H158, DATE(YEAR(H158),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>0</v>
       </c>
       <c r="AD158" s="21">
-        <f>MAX(0, MIN(I158, DATE(YEAR(H158),7,31)) - MAX(H158, DATE(YEAR(H158),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>0</v>
       </c>
       <c r="AE158" s="21">
-        <f>MAX(0, MIN(I158, DATE(YEAR(H158),8,31)) - MAX(H158, DATE(YEAR(H158),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>27</v>
       </c>
       <c r="AF158" s="21">
-        <f>MAX(0, MIN(I158, DATE(YEAR(H158),9,31)) - MAX(H158, DATE(YEAR(H158),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG158" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>2</v>
       </c>
       <c r="AH158" s="21" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="43"/>
         <v>FAIL</v>
       </c>
       <c r="AI158" s="21" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -24292,39 +24314,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA159" s="21">
-        <f>V159/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB159" s="21">
-        <f>MAX(0, MIN(I159, DATE(YEAR(H159),5,31)) - MAX(H159, DATE(YEAR(H159),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC159" s="21">
-        <f>MAX(0, MIN(I159, DATE(YEAR(H159),6,31)) - MAX(H159, DATE(YEAR(H159),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD159" s="21">
-        <f>MAX(0, MIN(I159, DATE(YEAR(H159),7,31)) - MAX(H159, DATE(YEAR(H159),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE159" s="21">
-        <f>MAX(0, MIN(I159, DATE(YEAR(H159),8,31)) - MAX(H159, DATE(YEAR(H159),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF159" s="21">
-        <f>MAX(0, MIN(I159, DATE(YEAR(H159),9,31)) - MAX(H159, DATE(YEAR(H159),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG159" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="AH159" s="21" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="43"/>
         <v>PASS</v>
       </c>
       <c r="AI159" s="21" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>PASS</v>
       </c>
     </row>
@@ -24405,39 +24427,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA160" s="21">
-        <f>V160/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB160" s="21">
-        <f>MAX(0, MIN(I160, DATE(YEAR(H160),5,31)) - MAX(H160, DATE(YEAR(H160),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC160" s="21">
-        <f>MAX(0, MIN(I160, DATE(YEAR(H160),6,31)) - MAX(H160, DATE(YEAR(H160),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD160" s="21">
-        <f>MAX(0, MIN(I160, DATE(YEAR(H160),7,31)) - MAX(H160, DATE(YEAR(H160),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE160" s="21">
-        <f>MAX(0, MIN(I160, DATE(YEAR(H160),8,31)) - MAX(H160, DATE(YEAR(H160),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF160" s="21">
-        <f>MAX(0, MIN(I160, DATE(YEAR(H160),9,31)) - MAX(H160, DATE(YEAR(H160),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG160" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="AH160" s="21" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="43"/>
         <v>PASS</v>
       </c>
       <c r="AI160" s="21" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>PASS</v>
       </c>
     </row>
@@ -24518,39 +24540,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA161" s="21">
-        <f>V161/153</f>
+        <f t="shared" si="30"/>
         <v>1</v>
       </c>
       <c r="AB161" s="21">
-        <f>MAX(0, MIN(I161, DATE(YEAR(H161),5,31)) - MAX(H161, DATE(YEAR(H161),5,1)) + 1)</f>
+        <f t="shared" si="31"/>
         <v>31</v>
       </c>
       <c r="AC161" s="21">
-        <f>MAX(0, MIN(I161, DATE(YEAR(H161),6,31)) - MAX(H161, DATE(YEAR(H161),6,1)) + 1)</f>
+        <f t="shared" si="32"/>
         <v>31</v>
       </c>
       <c r="AD161" s="21">
-        <f>MAX(0, MIN(I161, DATE(YEAR(H161),7,31)) - MAX(H161, DATE(YEAR(H161),7,1)) + 1)</f>
+        <f t="shared" si="33"/>
         <v>31</v>
       </c>
       <c r="AE161" s="21">
-        <f>MAX(0, MIN(I161, DATE(YEAR(H161),8,31)) - MAX(H161, DATE(YEAR(H161),8,1)) + 1)</f>
+        <f t="shared" si="34"/>
         <v>31</v>
       </c>
       <c r="AF161" s="21">
-        <f>MAX(0, MIN(I161, DATE(YEAR(H161),9,31)) - MAX(H161, DATE(YEAR(H161),9,1)) + 1)</f>
+        <f t="shared" si="35"/>
         <v>30</v>
       </c>
       <c r="AG161" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>5</v>
       </c>
       <c r="AH161" s="21" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="43"/>
         <v>PASS</v>
       </c>
       <c r="AI161" s="21" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>PASS</v>
       </c>
     </row>
@@ -24631,39 +24653,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA162" s="21">
-        <f>V162/153</f>
+        <f t="shared" ref="AA162:AA193" si="45">V162/153</f>
         <v>0.6470588235294118</v>
       </c>
       <c r="AB162" s="21">
-        <f>MAX(0, MIN(I162, DATE(YEAR(H162),5,31)) - MAX(H162, DATE(YEAR(H162),5,1)) + 1)</f>
+        <f t="shared" ref="AB162:AB193" si="46">MAX(0, MIN(I162, DATE(YEAR(H162),5,31)) - MAX(H162, DATE(YEAR(H162),5,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AC162" s="21">
-        <f>MAX(0, MIN(I162, DATE(YEAR(H162),6,31)) - MAX(H162, DATE(YEAR(H162),6,1)) + 1)</f>
+        <f t="shared" ref="AC162:AC193" si="47">MAX(0, MIN(I162, DATE(YEAR(H162),6,31)) - MAX(H162, DATE(YEAR(H162),6,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AD162" s="21">
-        <f>MAX(0, MIN(I162, DATE(YEAR(H162),7,31)) - MAX(H162, DATE(YEAR(H162),7,1)) + 1)</f>
+        <f t="shared" ref="AD162:AD193" si="48">MAX(0, MIN(I162, DATE(YEAR(H162),7,31)) - MAX(H162, DATE(YEAR(H162),7,1)) + 1)</f>
         <v>31</v>
       </c>
       <c r="AE162" s="21">
-        <f>MAX(0, MIN(I162, DATE(YEAR(H162),8,31)) - MAX(H162, DATE(YEAR(H162),8,1)) + 1)</f>
+        <f t="shared" ref="AE162:AE193" si="49">MAX(0, MIN(I162, DATE(YEAR(H162),8,31)) - MAX(H162, DATE(YEAR(H162),8,1)) + 1)</f>
         <v>7</v>
       </c>
       <c r="AF162" s="21">
-        <f>MAX(0, MIN(I162, DATE(YEAR(H162),9,31)) - MAX(H162, DATE(YEAR(H162),9,1)) + 1)</f>
+        <f t="shared" ref="AF162:AF193" si="50">MAX(0, MIN(I162, DATE(YEAR(H162),9,31)) - MAX(H162, DATE(YEAR(H162),9,1)) + 1)</f>
         <v>0</v>
       </c>
       <c r="AG162" s="21">
-        <f t="shared" si="12"/>
+        <f t="shared" si="42"/>
         <v>3</v>
       </c>
       <c r="AH162" s="21" t="str">
-        <f t="shared" si="13"/>
+        <f t="shared" si="43"/>
         <v>PASS</v>
       </c>
       <c r="AI162" s="21" t="str">
-        <f t="shared" si="14"/>
+        <f t="shared" si="44"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -24744,39 +24766,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA163" s="21">
-        <f>V163/153</f>
+        <f t="shared" si="45"/>
         <v>9.8039215686274508E-2</v>
       </c>
       <c r="AB163" s="21">
-        <f>MAX(0, MIN(I163, DATE(YEAR(H163),5,31)) - MAX(H163, DATE(YEAR(H163),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>5</v>
       </c>
       <c r="AC163" s="21">
-        <f>MAX(0, MIN(I163, DATE(YEAR(H163),6,31)) - MAX(H163, DATE(YEAR(H163),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>10</v>
       </c>
       <c r="AD163" s="21">
-        <f>MAX(0, MIN(I163, DATE(YEAR(H163),7,31)) - MAX(H163, DATE(YEAR(H163),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE163" s="21">
-        <f>MAX(0, MIN(I163, DATE(YEAR(H163),8,31)) - MAX(H163, DATE(YEAR(H163),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AF163" s="21">
-        <f>MAX(0, MIN(I163, DATE(YEAR(H163),9,31)) - MAX(H163, DATE(YEAR(H163),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG163" s="21">
-        <f t="shared" ref="AG163:AG183" si="15">COUNTIF(AB163:AF163, "&gt;=10")</f>
+        <f t="shared" ref="AG163:AG183" si="51">COUNTIF(AB163:AF163, "&gt;=10")</f>
         <v>1</v>
       </c>
       <c r="AH163" s="21" t="str">
-        <f t="shared" ref="AH163:AH183" si="16">IF(COUNTIF(AB163:AF163,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
+        <f t="shared" ref="AH163:AH183" si="52">IF(COUNTIF(AB163:AF163,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
       <c r="AI163" s="21" t="str">
-        <f t="shared" ref="AI163:AI183" si="17">IF(AND(AA163&gt;=0.8, COUNTIF(AB163:AF163, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
+        <f t="shared" ref="AI163:AI183" si="53">IF(AND(AA163&gt;=0.8, COUNTIF(AB163:AF163, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
         <v>FAIL</v>
       </c>
     </row>
@@ -24857,39 +24879,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA164" s="21">
-        <f>V164/153</f>
+        <f t="shared" si="45"/>
         <v>0.22222222222222221</v>
       </c>
       <c r="AB164" s="21">
-        <f>MAX(0, MIN(I164, DATE(YEAR(H164),5,31)) - MAX(H164, DATE(YEAR(H164),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC164" s="21">
-        <f>MAX(0, MIN(I164, DATE(YEAR(H164),6,31)) - MAX(H164, DATE(YEAR(H164),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD164" s="21">
-        <f>MAX(0, MIN(I164, DATE(YEAR(H164),7,31)) - MAX(H164, DATE(YEAR(H164),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE164" s="21">
-        <f>MAX(0, MIN(I164, DATE(YEAR(H164),8,31)) - MAX(H164, DATE(YEAR(H164),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>27</v>
       </c>
       <c r="AF164" s="21">
-        <f>MAX(0, MIN(I164, DATE(YEAR(H164),9,31)) - MAX(H164, DATE(YEAR(H164),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>7</v>
       </c>
       <c r="AG164" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>1</v>
       </c>
       <c r="AH164" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>FAIL</v>
       </c>
       <c r="AI164" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -24970,39 +24992,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA165" s="21">
-        <f>V165/153</f>
+        <f t="shared" si="45"/>
         <v>0.13071895424836602</v>
       </c>
       <c r="AB165" s="21">
-        <f>MAX(0, MIN(I165, DATE(YEAR(H165),5,31)) - MAX(H165, DATE(YEAR(H165),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC165" s="21">
-        <f>MAX(0, MIN(I165, DATE(YEAR(H165),6,31)) - MAX(H165, DATE(YEAR(H165),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD165" s="21">
-        <f>MAX(0, MIN(I165, DATE(YEAR(H165),7,31)) - MAX(H165, DATE(YEAR(H165),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>13</v>
       </c>
       <c r="AE165" s="21">
-        <f>MAX(0, MIN(I165, DATE(YEAR(H165),8,31)) - MAX(H165, DATE(YEAR(H165),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>7</v>
       </c>
       <c r="AF165" s="21">
-        <f>MAX(0, MIN(I165, DATE(YEAR(H165),9,31)) - MAX(H165, DATE(YEAR(H165),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG165" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>1</v>
       </c>
       <c r="AH165" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>FAIL</v>
       </c>
       <c r="AI165" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -25083,39 +25105,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA166" s="21">
-        <f>V166/153</f>
+        <f t="shared" si="45"/>
         <v>0.12418300653594772</v>
       </c>
       <c r="AB166" s="21">
-        <f>MAX(0, MIN(I166, DATE(YEAR(H166),5,31)) - MAX(H166, DATE(YEAR(H166),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC166" s="21">
-        <f>MAX(0, MIN(I166, DATE(YEAR(H166),6,31)) - MAX(H166, DATE(YEAR(H166),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD166" s="21">
-        <f>MAX(0, MIN(I166, DATE(YEAR(H166),7,31)) - MAX(H166, DATE(YEAR(H166),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>7</v>
       </c>
       <c r="AE166" s="21">
-        <f>MAX(0, MIN(I166, DATE(YEAR(H166),8,31)) - MAX(H166, DATE(YEAR(H166),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>12</v>
       </c>
       <c r="AF166" s="21">
-        <f>MAX(0, MIN(I166, DATE(YEAR(H166),9,31)) - MAX(H166, DATE(YEAR(H166),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG166" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>1</v>
       </c>
       <c r="AH166" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>FAIL</v>
       </c>
       <c r="AI166" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -25196,39 +25218,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA167" s="21">
-        <f>V167/153</f>
+        <f t="shared" si="45"/>
         <v>5.8823529411764705E-2</v>
       </c>
       <c r="AB167" s="21">
-        <f>MAX(0, MIN(I167, DATE(YEAR(H167),5,31)) - MAX(H167, DATE(YEAR(H167),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC167" s="21">
-        <f>MAX(0, MIN(I167, DATE(YEAR(H167),6,31)) - MAX(H167, DATE(YEAR(H167),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD167" s="21">
-        <f>MAX(0, MIN(I167, DATE(YEAR(H167),7,31)) - MAX(H167, DATE(YEAR(H167),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE167" s="21">
-        <f>MAX(0, MIN(I167, DATE(YEAR(H167),8,31)) - MAX(H167, DATE(YEAR(H167),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>9</v>
       </c>
       <c r="AF167" s="21">
-        <f>MAX(0, MIN(I167, DATE(YEAR(H167),9,31)) - MAX(H167, DATE(YEAR(H167),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG167" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>0</v>
       </c>
       <c r="AH167" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>FAIL</v>
       </c>
       <c r="AI167" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -25309,39 +25331,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA168" s="21">
-        <f>V168/153</f>
+        <f t="shared" si="45"/>
         <v>0.1111111111111111</v>
       </c>
       <c r="AB168" s="21">
-        <f>MAX(0, MIN(I168, DATE(YEAR(H168),5,31)) - MAX(H168, DATE(YEAR(H168),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC168" s="21">
-        <f>MAX(0, MIN(I168, DATE(YEAR(H168),6,31)) - MAX(H168, DATE(YEAR(H168),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD168" s="21">
-        <f>MAX(0, MIN(I168, DATE(YEAR(H168),7,31)) - MAX(H168, DATE(YEAR(H168),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE168" s="21">
-        <f>MAX(0, MIN(I168, DATE(YEAR(H168),8,31)) - MAX(H168, DATE(YEAR(H168),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>17</v>
       </c>
       <c r="AF168" s="21">
-        <f>MAX(0, MIN(I168, DATE(YEAR(H168),9,31)) - MAX(H168, DATE(YEAR(H168),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG168" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>1</v>
       </c>
       <c r="AH168" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>FAIL</v>
       </c>
       <c r="AI168" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -25422,39 +25444,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA169" s="21">
-        <f>V169/153</f>
+        <f t="shared" si="45"/>
         <v>8.4967320261437912E-2</v>
       </c>
       <c r="AB169" s="21">
-        <f>MAX(0, MIN(I169, DATE(YEAR(H169),5,31)) - MAX(H169, DATE(YEAR(H169),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC169" s="21">
-        <f>MAX(0, MIN(I169, DATE(YEAR(H169),6,31)) - MAX(H169, DATE(YEAR(H169),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD169" s="21">
-        <f>MAX(0, MIN(I169, DATE(YEAR(H169),7,31)) - MAX(H169, DATE(YEAR(H169),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE169" s="21">
-        <f>MAX(0, MIN(I169, DATE(YEAR(H169),8,31)) - MAX(H169, DATE(YEAR(H169),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>1</v>
       </c>
       <c r="AF169" s="21">
-        <f>MAX(0, MIN(I169, DATE(YEAR(H169),9,31)) - MAX(H169, DATE(YEAR(H169),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>12</v>
       </c>
       <c r="AG169" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>1</v>
       </c>
       <c r="AH169" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>FAIL</v>
       </c>
       <c r="AI169" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -25535,39 +25557,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA170" s="21">
-        <f>V170/153</f>
+        <f t="shared" si="45"/>
         <v>0.33333333333333331</v>
       </c>
       <c r="AB170" s="21">
-        <f>MAX(0, MIN(I170, DATE(YEAR(H170),5,31)) - MAX(H170, DATE(YEAR(H170),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC170" s="21">
-        <f>MAX(0, MIN(I170, DATE(YEAR(H170),6,31)) - MAX(H170, DATE(YEAR(H170),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD170" s="21">
-        <f>MAX(0, MIN(I170, DATE(YEAR(H170),7,31)) - MAX(H170, DATE(YEAR(H170),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE170" s="21">
-        <f>MAX(0, MIN(I170, DATE(YEAR(H170),8,31)) - MAX(H170, DATE(YEAR(H170),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>21</v>
       </c>
       <c r="AF170" s="21">
-        <f>MAX(0, MIN(I170, DATE(YEAR(H170),9,31)) - MAX(H170, DATE(YEAR(H170),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG170" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>2</v>
       </c>
       <c r="AH170" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>FAIL</v>
       </c>
       <c r="AI170" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -25648,39 +25670,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA171" s="21">
-        <f>V171/153</f>
+        <f t="shared" si="45"/>
         <v>0.66666666666666663</v>
       </c>
       <c r="AB171" s="21">
-        <f>MAX(0, MIN(I171, DATE(YEAR(H171),5,31)) - MAX(H171, DATE(YEAR(H171),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC171" s="21">
-        <f>MAX(0, MIN(I171, DATE(YEAR(H171),6,31)) - MAX(H171, DATE(YEAR(H171),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>11</v>
       </c>
       <c r="AD171" s="21">
-        <f>MAX(0, MIN(I171, DATE(YEAR(H171),7,31)) - MAX(H171, DATE(YEAR(H171),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE171" s="21">
-        <f>MAX(0, MIN(I171, DATE(YEAR(H171),8,31)) - MAX(H171, DATE(YEAR(H171),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AF171" s="21">
-        <f>MAX(0, MIN(I171, DATE(YEAR(H171),9,31)) - MAX(H171, DATE(YEAR(H171),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG171" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>4</v>
       </c>
       <c r="AH171" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>PASS</v>
       </c>
       <c r="AI171" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -25761,39 +25783,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA172" s="21">
-        <f>V172/153</f>
+        <f t="shared" si="45"/>
         <v>0.73202614379084963</v>
       </c>
       <c r="AB172" s="21">
-        <f>MAX(0, MIN(I172, DATE(YEAR(H172),5,31)) - MAX(H172, DATE(YEAR(H172),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC172" s="21">
-        <f>MAX(0, MIN(I172, DATE(YEAR(H172),6,31)) - MAX(H172, DATE(YEAR(H172),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD172" s="21">
-        <f>MAX(0, MIN(I172, DATE(YEAR(H172),7,31)) - MAX(H172, DATE(YEAR(H172),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE172" s="21">
-        <f>MAX(0, MIN(I172, DATE(YEAR(H172),8,31)) - MAX(H172, DATE(YEAR(H172),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>20</v>
       </c>
       <c r="AF172" s="21">
-        <f>MAX(0, MIN(I172, DATE(YEAR(H172),9,31)) - MAX(H172, DATE(YEAR(H172),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG172" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>4</v>
       </c>
       <c r="AH172" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>PASS</v>
       </c>
       <c r="AI172" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -25874,39 +25896,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA173" s="21">
-        <f>V173/153</f>
+        <f t="shared" si="45"/>
         <v>0.28758169934640521</v>
       </c>
       <c r="AB173" s="21">
-        <f>MAX(0, MIN(I173, DATE(YEAR(H173),5,31)) - MAX(H173, DATE(YEAR(H173),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC173" s="21">
-        <f>MAX(0, MIN(I173, DATE(YEAR(H173),6,31)) - MAX(H173, DATE(YEAR(H173),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD173" s="21">
-        <f>MAX(0, MIN(I173, DATE(YEAR(H173),7,31)) - MAX(H173, DATE(YEAR(H173),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE173" s="21">
-        <f>MAX(0, MIN(I173, DATE(YEAR(H173),8,31)) - MAX(H173, DATE(YEAR(H173),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>14</v>
       </c>
       <c r="AF173" s="21">
-        <f>MAX(0, MIN(I173, DATE(YEAR(H173),9,31)) - MAX(H173, DATE(YEAR(H173),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG173" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>2</v>
       </c>
       <c r="AH173" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>FAIL</v>
       </c>
       <c r="AI173" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -25987,39 +26009,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA174" s="21">
-        <f>V174/153</f>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="AB174" s="21">
-        <f>MAX(0, MIN(I174, DATE(YEAR(H174),5,31)) - MAX(H174, DATE(YEAR(H174),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC174" s="21">
-        <f>MAX(0, MIN(I174, DATE(YEAR(H174),6,31)) - MAX(H174, DATE(YEAR(H174),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD174" s="21">
-        <f>MAX(0, MIN(I174, DATE(YEAR(H174),7,31)) - MAX(H174, DATE(YEAR(H174),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE174" s="21">
-        <f>MAX(0, MIN(I174, DATE(YEAR(H174),8,31)) - MAX(H174, DATE(YEAR(H174),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AF174" s="21">
-        <f>MAX(0, MIN(I174, DATE(YEAR(H174),9,31)) - MAX(H174, DATE(YEAR(H174),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG174" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>5</v>
       </c>
       <c r="AH174" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>PASS</v>
       </c>
       <c r="AI174" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>PASS</v>
       </c>
     </row>
@@ -26100,39 +26122,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA175" s="21">
-        <f>V175/153</f>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="AB175" s="21">
-        <f>MAX(0, MIN(I175, DATE(YEAR(H175),5,31)) - MAX(H175, DATE(YEAR(H175),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC175" s="21">
-        <f>MAX(0, MIN(I175, DATE(YEAR(H175),6,31)) - MAX(H175, DATE(YEAR(H175),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD175" s="21">
-        <f>MAX(0, MIN(I175, DATE(YEAR(H175),7,31)) - MAX(H175, DATE(YEAR(H175),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE175" s="21">
-        <f>MAX(0, MIN(I175, DATE(YEAR(H175),8,31)) - MAX(H175, DATE(YEAR(H175),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AF175" s="21">
-        <f>MAX(0, MIN(I175, DATE(YEAR(H175),9,31)) - MAX(H175, DATE(YEAR(H175),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG175" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>5</v>
       </c>
       <c r="AH175" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>PASS</v>
       </c>
       <c r="AI175" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>PASS</v>
       </c>
     </row>
@@ -26213,39 +26235,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA176" s="21">
-        <f>V176/153</f>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="AB176" s="21">
-        <f>MAX(0, MIN(I176, DATE(YEAR(H176),5,31)) - MAX(H176, DATE(YEAR(H176),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC176" s="21">
-        <f>MAX(0, MIN(I176, DATE(YEAR(H176),6,31)) - MAX(H176, DATE(YEAR(H176),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD176" s="21">
-        <f>MAX(0, MIN(I176, DATE(YEAR(H176),7,31)) - MAX(H176, DATE(YEAR(H176),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE176" s="21">
-        <f>MAX(0, MIN(I176, DATE(YEAR(H176),8,31)) - MAX(H176, DATE(YEAR(H176),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AF176" s="21">
-        <f>MAX(0, MIN(I176, DATE(YEAR(H176),9,31)) - MAX(H176, DATE(YEAR(H176),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG176" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>5</v>
       </c>
       <c r="AH176" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>PASS</v>
       </c>
       <c r="AI176" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>PASS</v>
       </c>
     </row>
@@ -26326,39 +26348,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA177" s="21">
-        <f>V177/153</f>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="AB177" s="21">
-        <f>MAX(0, MIN(I177, DATE(YEAR(H177),5,31)) - MAX(H177, DATE(YEAR(H177),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC177" s="21">
-        <f>MAX(0, MIN(I177, DATE(YEAR(H177),6,31)) - MAX(H177, DATE(YEAR(H177),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD177" s="21">
-        <f>MAX(0, MIN(I177, DATE(YEAR(H177),7,31)) - MAX(H177, DATE(YEAR(H177),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE177" s="21">
-        <f>MAX(0, MIN(I177, DATE(YEAR(H177),8,31)) - MAX(H177, DATE(YEAR(H177),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AF177" s="21">
-        <f>MAX(0, MIN(I177, DATE(YEAR(H177),9,31)) - MAX(H177, DATE(YEAR(H177),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG177" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>5</v>
       </c>
       <c r="AH177" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>PASS</v>
       </c>
       <c r="AI177" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>PASS</v>
       </c>
     </row>
@@ -26439,39 +26461,39 @@
         <v>-72.938199999999995</v>
       </c>
       <c r="AA178" s="21">
-        <f>V178/153</f>
+        <f t="shared" si="45"/>
         <v>0.6470588235294118</v>
       </c>
       <c r="AB178" s="21">
-        <f>MAX(0, MIN(I178, DATE(YEAR(H178),5,31)) - MAX(H178, DATE(YEAR(H178),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC178" s="21">
-        <f>MAX(0, MIN(I178, DATE(YEAR(H178),6,31)) - MAX(H178, DATE(YEAR(H178),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD178" s="21">
-        <f>MAX(0, MIN(I178, DATE(YEAR(H178),7,31)) - MAX(H178, DATE(YEAR(H178),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE178" s="21">
-        <f>MAX(0, MIN(I178, DATE(YEAR(H178),8,31)) - MAX(H178, DATE(YEAR(H178),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>7</v>
       </c>
       <c r="AF178" s="21">
-        <f>MAX(0, MIN(I178, DATE(YEAR(H178),9,31)) - MAX(H178, DATE(YEAR(H178),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG178" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>3</v>
       </c>
       <c r="AH178" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>PASS</v>
       </c>
       <c r="AI178" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -26552,39 +26574,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA179" s="21">
-        <f>V179/153</f>
+        <f t="shared" si="45"/>
         <v>0.33986928104575165</v>
       </c>
       <c r="AB179" s="21">
-        <f>MAX(0, MIN(I179, DATE(YEAR(H179),5,31)) - MAX(H179, DATE(YEAR(H179),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC179" s="21">
-        <f>MAX(0, MIN(I179, DATE(YEAR(H179),6,31)) - MAX(H179, DATE(YEAR(H179),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD179" s="21">
-        <f>MAX(0, MIN(I179, DATE(YEAR(H179),7,31)) - MAX(H179, DATE(YEAR(H179),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE179" s="21">
-        <f>MAX(0, MIN(I179, DATE(YEAR(H179),8,31)) - MAX(H179, DATE(YEAR(H179),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>22</v>
       </c>
       <c r="AF179" s="21">
-        <f>MAX(0, MIN(I179, DATE(YEAR(H179),9,31)) - MAX(H179, DATE(YEAR(H179),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG179" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>2</v>
       </c>
       <c r="AH179" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>FAIL</v>
       </c>
       <c r="AI179" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -26665,39 +26687,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA180" s="21">
-        <f>V180/153</f>
+        <f t="shared" si="45"/>
         <v>0.33986928104575165</v>
       </c>
       <c r="AB180" s="21">
-        <f>MAX(0, MIN(I180, DATE(YEAR(H180),5,31)) - MAX(H180, DATE(YEAR(H180),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC180" s="21">
-        <f>MAX(0, MIN(I180, DATE(YEAR(H180),6,31)) - MAX(H180, DATE(YEAR(H180),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>21</v>
       </c>
       <c r="AD180" s="21">
-        <f>MAX(0, MIN(I180, DATE(YEAR(H180),7,31)) - MAX(H180, DATE(YEAR(H180),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE180" s="21">
-        <f>MAX(0, MIN(I180, DATE(YEAR(H180),8,31)) - MAX(H180, DATE(YEAR(H180),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AF180" s="21">
-        <f>MAX(0, MIN(I180, DATE(YEAR(H180),9,31)) - MAX(H180, DATE(YEAR(H180),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG180" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>2</v>
       </c>
       <c r="AH180" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>FAIL</v>
       </c>
       <c r="AI180" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -26778,39 +26800,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA181" s="21">
-        <f>V181/153</f>
+        <f t="shared" si="45"/>
         <v>0.40522875816993464</v>
       </c>
       <c r="AB181" s="21">
-        <f>MAX(0, MIN(I181, DATE(YEAR(H181),5,31)) - MAX(H181, DATE(YEAR(H181),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC181" s="21">
-        <f>MAX(0, MIN(I181, DATE(YEAR(H181),6,31)) - MAX(H181, DATE(YEAR(H181),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD181" s="21">
-        <f>MAX(0, MIN(I181, DATE(YEAR(H181),7,31)) - MAX(H181, DATE(YEAR(H181),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>1</v>
       </c>
       <c r="AE181" s="21">
-        <f>MAX(0, MIN(I181, DATE(YEAR(H181),8,31)) - MAX(H181, DATE(YEAR(H181),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AF181" s="21">
-        <f>MAX(0, MIN(I181, DATE(YEAR(H181),9,31)) - MAX(H181, DATE(YEAR(H181),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG181" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>2</v>
       </c>
       <c r="AH181" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>FAIL</v>
       </c>
       <c r="AI181" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -26891,39 +26913,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA182" s="21">
-        <f>V182/153</f>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="AB182" s="21">
-        <f>MAX(0, MIN(I182, DATE(YEAR(H182),5,31)) - MAX(H182, DATE(YEAR(H182),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC182" s="21">
-        <f>MAX(0, MIN(I182, DATE(YEAR(H182),6,31)) - MAX(H182, DATE(YEAR(H182),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD182" s="21">
-        <f>MAX(0, MIN(I182, DATE(YEAR(H182),7,31)) - MAX(H182, DATE(YEAR(H182),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE182" s="21">
-        <f>MAX(0, MIN(I182, DATE(YEAR(H182),8,31)) - MAX(H182, DATE(YEAR(H182),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AF182" s="21">
-        <f>MAX(0, MIN(I182, DATE(YEAR(H182),9,31)) - MAX(H182, DATE(YEAR(H182),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG182" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>5</v>
       </c>
       <c r="AH182" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>PASS</v>
       </c>
       <c r="AI182" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>PASS</v>
       </c>
     </row>
@@ -27004,39 +27026,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA183" s="21">
-        <f>V183/153</f>
+        <f t="shared" si="45"/>
         <v>0.6470588235294118</v>
       </c>
       <c r="AB183" s="21">
-        <f>MAX(0, MIN(I183, DATE(YEAR(H183),5,31)) - MAX(H183, DATE(YEAR(H183),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC183" s="21">
-        <f>MAX(0, MIN(I183, DATE(YEAR(H183),6,31)) - MAX(H183, DATE(YEAR(H183),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD183" s="21">
-        <f>MAX(0, MIN(I183, DATE(YEAR(H183),7,31)) - MAX(H183, DATE(YEAR(H183),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE183" s="21">
-        <f>MAX(0, MIN(I183, DATE(YEAR(H183),8,31)) - MAX(H183, DATE(YEAR(H183),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>7</v>
       </c>
       <c r="AF183" s="21">
-        <f>MAX(0, MIN(I183, DATE(YEAR(H183),9,31)) - MAX(H183, DATE(YEAR(H183),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG183" s="21">
-        <f t="shared" si="15"/>
+        <f t="shared" si="51"/>
         <v>3</v>
       </c>
       <c r="AH183" s="21" t="str">
-        <f t="shared" si="16"/>
+        <f t="shared" si="52"/>
         <v>PASS</v>
       </c>
       <c r="AI183" s="21" t="str">
-        <f t="shared" si="17"/>
+        <f t="shared" si="53"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -27117,39 +27139,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA184" s="21">
-        <f>V184/153</f>
+        <f t="shared" si="45"/>
         <v>0.33986928104575165</v>
       </c>
       <c r="AB184" s="21">
-        <f>MAX(0, MIN(I184, DATE(YEAR(H184),5,31)) - MAX(H184, DATE(YEAR(H184),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC184" s="21">
-        <f>MAX(0, MIN(I184, DATE(YEAR(H184),6,31)) - MAX(H184, DATE(YEAR(H184),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD184" s="21">
-        <f>MAX(0, MIN(I184, DATE(YEAR(H184),7,31)) - MAX(H184, DATE(YEAR(H184),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE184" s="21">
-        <f>MAX(0, MIN(I184, DATE(YEAR(H184),8,31)) - MAX(H184, DATE(YEAR(H184),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>22</v>
       </c>
       <c r="AF184" s="21">
-        <f>MAX(0, MIN(I184, DATE(YEAR(H184),9,31)) - MAX(H184, DATE(YEAR(H184),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG184" s="21">
-        <f t="shared" ref="AG184:AG193" si="18">COUNTIF(AB184:AF184, "&gt;=10")</f>
+        <f t="shared" ref="AG184:AG193" si="54">COUNTIF(AB184:AF184, "&gt;=10")</f>
         <v>2</v>
       </c>
       <c r="AH184" s="21" t="str">
-        <f t="shared" ref="AH184:AH193" si="19">IF(COUNTIF(AB184:AF184,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
+        <f t="shared" ref="AH184:AH193" si="55">IF(COUNTIF(AB184:AF184,"&gt;=10")&gt;=3,"PASS","FAIL")</f>
         <v>FAIL</v>
       </c>
       <c r="AI184" s="21" t="str">
-        <f t="shared" ref="AI184:AI193" si="20">IF(AND(AA184&gt;=0.8, COUNTIF(AB184:AF184, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
+        <f t="shared" ref="AI184:AI193" si="56">IF(AND(AA184&gt;=0.8, COUNTIF(AB184:AF184, "&gt;=10")&gt;=3), "PASS", "FAIL")</f>
         <v>FAIL</v>
       </c>
     </row>
@@ -27230,39 +27252,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA185" s="21">
-        <f>V185/153</f>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="AB185" s="21">
-        <f>MAX(0, MIN(I185, DATE(YEAR(H185),5,31)) - MAX(H185, DATE(YEAR(H185),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC185" s="21">
-        <f>MAX(0, MIN(I185, DATE(YEAR(H185),6,31)) - MAX(H185, DATE(YEAR(H185),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD185" s="21">
-        <f>MAX(0, MIN(I185, DATE(YEAR(H185),7,31)) - MAX(H185, DATE(YEAR(H185),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE185" s="21">
-        <f>MAX(0, MIN(I185, DATE(YEAR(H185),8,31)) - MAX(H185, DATE(YEAR(H185),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AF185" s="21">
-        <f>MAX(0, MIN(I185, DATE(YEAR(H185),9,31)) - MAX(H185, DATE(YEAR(H185),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG185" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>5</v>
       </c>
       <c r="AH185" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>PASS</v>
       </c>
       <c r="AI185" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>PASS</v>
       </c>
     </row>
@@ -27343,39 +27365,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA186" s="21">
-        <f>V186/153</f>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="AB186" s="21">
-        <f>MAX(0, MIN(I186, DATE(YEAR(H186),5,31)) - MAX(H186, DATE(YEAR(H186),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC186" s="21">
-        <f>MAX(0, MIN(I186, DATE(YEAR(H186),6,31)) - MAX(H186, DATE(YEAR(H186),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD186" s="21">
-        <f>MAX(0, MIN(I186, DATE(YEAR(H186),7,31)) - MAX(H186, DATE(YEAR(H186),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE186" s="21">
-        <f>MAX(0, MIN(I186, DATE(YEAR(H186),8,31)) - MAX(H186, DATE(YEAR(H186),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AF186" s="21">
-        <f>MAX(0, MIN(I186, DATE(YEAR(H186),9,31)) - MAX(H186, DATE(YEAR(H186),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG186" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>5</v>
       </c>
       <c r="AH186" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>PASS</v>
       </c>
       <c r="AI186" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>PASS</v>
       </c>
     </row>
@@ -27456,39 +27478,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA187" s="21">
-        <f>V187/153</f>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="AB187" s="21">
-        <f>MAX(0, MIN(I187, DATE(YEAR(H187),5,31)) - MAX(H187, DATE(YEAR(H187),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC187" s="21">
-        <f>MAX(0, MIN(I187, DATE(YEAR(H187),6,31)) - MAX(H187, DATE(YEAR(H187),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD187" s="21">
-        <f>MAX(0, MIN(I187, DATE(YEAR(H187),7,31)) - MAX(H187, DATE(YEAR(H187),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE187" s="21">
-        <f>MAX(0, MIN(I187, DATE(YEAR(H187),8,31)) - MAX(H187, DATE(YEAR(H187),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AF187" s="21">
-        <f>MAX(0, MIN(I187, DATE(YEAR(H187),9,31)) - MAX(H187, DATE(YEAR(H187),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG187" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>5</v>
       </c>
       <c r="AH187" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>PASS</v>
       </c>
       <c r="AI187" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>PASS</v>
       </c>
     </row>
@@ -27569,39 +27591,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA188" s="21">
-        <f>V188/153</f>
+        <f t="shared" si="45"/>
         <v>0.6470588235294118</v>
       </c>
       <c r="AB188" s="21">
-        <f>MAX(0, MIN(I188, DATE(YEAR(H188),5,31)) - MAX(H188, DATE(YEAR(H188),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC188" s="21">
-        <f>MAX(0, MIN(I188, DATE(YEAR(H188),6,31)) - MAX(H188, DATE(YEAR(H188),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD188" s="21">
-        <f>MAX(0, MIN(I188, DATE(YEAR(H188),7,31)) - MAX(H188, DATE(YEAR(H188),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE188" s="21">
-        <f>MAX(0, MIN(I188, DATE(YEAR(H188),8,31)) - MAX(H188, DATE(YEAR(H188),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>7</v>
       </c>
       <c r="AF188" s="21">
-        <f>MAX(0, MIN(I188, DATE(YEAR(H188),9,31)) - MAX(H188, DATE(YEAR(H188),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG188" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>3</v>
       </c>
       <c r="AH188" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>PASS</v>
       </c>
       <c r="AI188" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -27682,39 +27704,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA189" s="21">
-        <f>V189/153</f>
+        <f t="shared" si="45"/>
         <v>0.33986928104575165</v>
       </c>
       <c r="AB189" s="21">
-        <f>MAX(0, MIN(I189, DATE(YEAR(H189),5,31)) - MAX(H189, DATE(YEAR(H189),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC189" s="21">
-        <f>MAX(0, MIN(I189, DATE(YEAR(H189),6,31)) - MAX(H189, DATE(YEAR(H189),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD189" s="21">
-        <f>MAX(0, MIN(I189, DATE(YEAR(H189),7,31)) - MAX(H189, DATE(YEAR(H189),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE189" s="21">
-        <f>MAX(0, MIN(I189, DATE(YEAR(H189),8,31)) - MAX(H189, DATE(YEAR(H189),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>22</v>
       </c>
       <c r="AF189" s="21">
-        <f>MAX(0, MIN(I189, DATE(YEAR(H189),9,31)) - MAX(H189, DATE(YEAR(H189),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG189" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>2</v>
       </c>
       <c r="AH189" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>FAIL</v>
       </c>
       <c r="AI189" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -27795,39 +27817,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA190" s="21">
-        <f>V190/153</f>
+        <f t="shared" si="45"/>
         <v>1</v>
       </c>
       <c r="AB190" s="21">
-        <f>MAX(0, MIN(I190, DATE(YEAR(H190),5,31)) - MAX(H190, DATE(YEAR(H190),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC190" s="21">
-        <f>MAX(0, MIN(I190, DATE(YEAR(H190),6,31)) - MAX(H190, DATE(YEAR(H190),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD190" s="21">
-        <f>MAX(0, MIN(I190, DATE(YEAR(H190),7,31)) - MAX(H190, DATE(YEAR(H190),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE190" s="21">
-        <f>MAX(0, MIN(I190, DATE(YEAR(H190),8,31)) - MAX(H190, DATE(YEAR(H190),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>31</v>
       </c>
       <c r="AF190" s="21">
-        <f>MAX(0, MIN(I190, DATE(YEAR(H190),9,31)) - MAX(H190, DATE(YEAR(H190),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG190" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>5</v>
       </c>
       <c r="AH190" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>PASS</v>
       </c>
       <c r="AI190" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>PASS</v>
       </c>
     </row>
@@ -27908,39 +27930,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA191" s="21">
-        <f>V191/153</f>
+        <f t="shared" si="45"/>
         <v>0.60130718954248363</v>
       </c>
       <c r="AB191" s="21">
-        <f>MAX(0, MIN(I191, DATE(YEAR(H191),5,31)) - MAX(H191, DATE(YEAR(H191),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC191" s="21">
-        <f>MAX(0, MIN(I191, DATE(YEAR(H191),6,31)) - MAX(H191, DATE(YEAR(H191),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD191" s="21">
-        <f>MAX(0, MIN(I191, DATE(YEAR(H191),7,31)) - MAX(H191, DATE(YEAR(H191),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE191" s="21">
-        <f>MAX(0, MIN(I191, DATE(YEAR(H191),8,31)) - MAX(H191, DATE(YEAR(H191),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>0</v>
       </c>
       <c r="AF191" s="21">
-        <f>MAX(0, MIN(I191, DATE(YEAR(H191),9,31)) - MAX(H191, DATE(YEAR(H191),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG191" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>3</v>
       </c>
       <c r="AH191" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>PASS</v>
       </c>
       <c r="AI191" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -28021,39 +28043,39 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA192" s="21">
-        <f>V192/153</f>
+        <f t="shared" si="45"/>
         <v>0.32679738562091504</v>
       </c>
       <c r="AB192" s="21">
-        <f>MAX(0, MIN(I192, DATE(YEAR(H192),5,31)) - MAX(H192, DATE(YEAR(H192),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>0</v>
       </c>
       <c r="AC192" s="21">
-        <f>MAX(0, MIN(I192, DATE(YEAR(H192),6,31)) - MAX(H192, DATE(YEAR(H192),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>0</v>
       </c>
       <c r="AD192" s="21">
-        <f>MAX(0, MIN(I192, DATE(YEAR(H192),7,31)) - MAX(H192, DATE(YEAR(H192),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>0</v>
       </c>
       <c r="AE192" s="21">
-        <f>MAX(0, MIN(I192, DATE(YEAR(H192),8,31)) - MAX(H192, DATE(YEAR(H192),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>20</v>
       </c>
       <c r="AF192" s="21">
-        <f>MAX(0, MIN(I192, DATE(YEAR(H192),9,31)) - MAX(H192, DATE(YEAR(H192),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>30</v>
       </c>
       <c r="AG192" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>2</v>
       </c>
       <c r="AH192" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>FAIL</v>
       </c>
       <c r="AI192" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>FAIL</v>
       </c>
     </row>
@@ -28134,40 +28156,460 @@
         <v>-72.787999999999997</v>
       </c>
       <c r="AA193" s="21">
-        <f>V193/153</f>
+        <f t="shared" si="45"/>
         <v>0.6470588235294118</v>
       </c>
       <c r="AB193" s="21">
-        <f>MAX(0, MIN(I193, DATE(YEAR(H193),5,31)) - MAX(H193, DATE(YEAR(H193),5,1)) + 1)</f>
+        <f t="shared" si="46"/>
         <v>31</v>
       </c>
       <c r="AC193" s="21">
-        <f>MAX(0, MIN(I193, DATE(YEAR(H193),6,31)) - MAX(H193, DATE(YEAR(H193),6,1)) + 1)</f>
+        <f t="shared" si="47"/>
         <v>31</v>
       </c>
       <c r="AD193" s="21">
-        <f>MAX(0, MIN(I193, DATE(YEAR(H193),7,31)) - MAX(H193, DATE(YEAR(H193),7,1)) + 1)</f>
+        <f t="shared" si="48"/>
         <v>31</v>
       </c>
       <c r="AE193" s="21">
-        <f>MAX(0, MIN(I193, DATE(YEAR(H193),8,31)) - MAX(H193, DATE(YEAR(H193),8,1)) + 1)</f>
+        <f t="shared" si="49"/>
         <v>7</v>
       </c>
       <c r="AF193" s="21">
-        <f>MAX(0, MIN(I193, DATE(YEAR(H193),9,31)) - MAX(H193, DATE(YEAR(H193),9,1)) + 1)</f>
+        <f t="shared" si="50"/>
         <v>0</v>
       </c>
       <c r="AG193" s="21">
-        <f t="shared" si="18"/>
+        <f t="shared" si="54"/>
         <v>3</v>
       </c>
       <c r="AH193" s="21" t="str">
-        <f t="shared" si="19"/>
+        <f t="shared" si="55"/>
         <v>PASS</v>
       </c>
       <c r="AI193" s="21" t="str">
-        <f t="shared" si="20"/>
+        <f t="shared" si="56"/>
         <v>FAIL</v>
+      </c>
+    </row>
+    <row r="194" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A194" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B194" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C194" s="32">
+        <v>25</v>
+      </c>
+      <c r="D194" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E194" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F194" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="G194" s="20">
+        <v>2022</v>
+      </c>
+      <c r="H194" s="12">
+        <v>44785</v>
+      </c>
+      <c r="I194" s="12">
+        <v>44834</v>
+      </c>
+      <c r="J194" s="20">
+        <v>4.1154999999999999</v>
+      </c>
+      <c r="K194" s="20">
+        <v>-5653.3967499999999</v>
+      </c>
+      <c r="L194" s="20">
+        <v>8.2309999999999994E-2</v>
+      </c>
+      <c r="M194" s="20">
+        <v>-113.06793500000001</v>
+      </c>
+      <c r="N194" s="20">
+        <v>4.0447499999999996</v>
+      </c>
+      <c r="O194" s="20">
+        <v>20.271153000000002</v>
+      </c>
+      <c r="P194" s="20">
+        <v>25.963249999999999</v>
+      </c>
+      <c r="Q194" s="20">
+        <v>12.642250000000001</v>
+      </c>
+      <c r="R194" s="20">
+        <v>2</v>
+      </c>
+      <c r="S194" s="20">
+        <v>1</v>
+      </c>
+      <c r="T194" s="20">
+        <v>0.41666667000000002</v>
+      </c>
+      <c r="U194" s="20">
+        <v>0</v>
+      </c>
+      <c r="V194" s="20">
+        <v>50</v>
+      </c>
+      <c r="W194" s="20">
+        <v>0.83682007999999997</v>
+      </c>
+      <c r="X194" s="40"/>
+      <c r="Y194" s="41">
+        <v>42.058399000000001</v>
+      </c>
+      <c r="Z194" s="41">
+        <v>-70.161844000000002</v>
+      </c>
+      <c r="AA194" s="42">
+        <v>0.32679738600000002</v>
+      </c>
+      <c r="AB194" s="42">
+        <v>0</v>
+      </c>
+      <c r="AC194" s="42">
+        <v>0</v>
+      </c>
+      <c r="AD194" s="42">
+        <v>0</v>
+      </c>
+      <c r="AE194" s="42">
+        <v>20</v>
+      </c>
+      <c r="AF194" s="42">
+        <v>30</v>
+      </c>
+      <c r="AG194" s="42">
+        <v>2</v>
+      </c>
+      <c r="AH194" s="42" t="s">
+        <v>172</v>
+      </c>
+      <c r="AI194" s="42" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="195" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A195" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B195" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C195" s="32">
+        <v>25</v>
+      </c>
+      <c r="D195" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E195" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F195" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="G195" s="20">
+        <v>2023</v>
+      </c>
+      <c r="H195" s="12">
+        <v>45047</v>
+      </c>
+      <c r="I195" s="12">
+        <v>45199</v>
+      </c>
+      <c r="J195" s="20">
+        <v>306.18058300000001</v>
+      </c>
+      <c r="K195" s="20">
+        <v>-20836.740600000001</v>
+      </c>
+      <c r="L195" s="20">
+        <v>2.0011802799999998</v>
+      </c>
+      <c r="M195" s="20">
+        <v>-136.187847</v>
+      </c>
+      <c r="N195" s="20">
+        <v>35.016500000000001</v>
+      </c>
+      <c r="O195" s="20">
+        <v>19.395082200000001</v>
+      </c>
+      <c r="P195" s="20">
+        <v>27.973500000000001</v>
+      </c>
+      <c r="Q195" s="20">
+        <v>8.0824999999999996</v>
+      </c>
+      <c r="R195" s="20">
+        <v>16</v>
+      </c>
+      <c r="S195" s="20">
+        <v>33</v>
+      </c>
+      <c r="T195" s="20">
+        <v>0.49494948999999999</v>
+      </c>
+      <c r="U195" s="20">
+        <v>0.14791264000000001</v>
+      </c>
+      <c r="V195" s="20">
+        <v>153</v>
+      </c>
+      <c r="W195" s="20">
+        <v>10.6753813</v>
+      </c>
+      <c r="X195" s="32"/>
+      <c r="Y195" s="41">
+        <v>42.058399000000001</v>
+      </c>
+      <c r="Z195" s="41">
+        <v>-70.161844000000002</v>
+      </c>
+      <c r="AA195" s="42">
+        <v>1</v>
+      </c>
+      <c r="AB195" s="42">
+        <v>31</v>
+      </c>
+      <c r="AC195" s="42">
+        <v>31</v>
+      </c>
+      <c r="AD195" s="42">
+        <v>31</v>
+      </c>
+      <c r="AE195" s="42">
+        <v>31</v>
+      </c>
+      <c r="AF195" s="42">
+        <v>30</v>
+      </c>
+      <c r="AG195" s="42">
+        <v>5</v>
+      </c>
+      <c r="AH195" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="AI195" s="42" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="196" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A196" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B196" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C196" s="32">
+        <v>25</v>
+      </c>
+      <c r="D196" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E196" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F196" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="G196" s="20">
+        <v>2024</v>
+      </c>
+      <c r="H196" s="12">
+        <v>45413</v>
+      </c>
+      <c r="I196" s="12">
+        <v>45565</v>
+      </c>
+      <c r="J196" s="20">
+        <v>17.842500000000001</v>
+      </c>
+      <c r="K196" s="20">
+        <v>-20644.882600000001</v>
+      </c>
+      <c r="L196" s="20">
+        <v>0.13517045</v>
+      </c>
+      <c r="M196" s="20">
+        <v>-156.40062499999999</v>
+      </c>
+      <c r="N196" s="20">
+        <v>14.395250000000001</v>
+      </c>
+      <c r="O196" s="20">
+        <v>18.438853300000002</v>
+      </c>
+      <c r="P196" s="20">
+        <v>26.84225</v>
+      </c>
+      <c r="Q196" s="20">
+        <v>7.9874999999999998</v>
+      </c>
+      <c r="R196" s="20">
+        <v>5</v>
+      </c>
+      <c r="S196" s="20">
+        <v>4</v>
+      </c>
+      <c r="T196" s="20">
+        <v>0.32291667000000002</v>
+      </c>
+      <c r="U196" s="20">
+        <v>0.14370974</v>
+      </c>
+      <c r="V196" s="20">
+        <v>132</v>
+      </c>
+      <c r="W196" s="20">
+        <v>0.98443950000000002</v>
+      </c>
+      <c r="X196" s="32"/>
+      <c r="Y196" s="41">
+        <v>42.058399000000001</v>
+      </c>
+      <c r="Z196" s="41">
+        <v>-70.161844000000002</v>
+      </c>
+      <c r="AA196" s="42">
+        <v>0.86274509799999999</v>
+      </c>
+      <c r="AB196" s="42">
+        <v>31</v>
+      </c>
+      <c r="AC196" s="42">
+        <v>31</v>
+      </c>
+      <c r="AD196" s="42">
+        <v>31</v>
+      </c>
+      <c r="AE196" s="42">
+        <v>31</v>
+      </c>
+      <c r="AF196" s="42">
+        <v>30</v>
+      </c>
+      <c r="AG196" s="42">
+        <v>5</v>
+      </c>
+      <c r="AH196" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="AI196" s="42" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="197" spans="1:35" x14ac:dyDescent="0.25">
+      <c r="A197" s="32" t="s">
+        <v>28</v>
+      </c>
+      <c r="B197" s="32" t="s">
+        <v>29</v>
+      </c>
+      <c r="C197" s="32">
+        <v>25</v>
+      </c>
+      <c r="D197" s="32" t="s">
+        <v>127</v>
+      </c>
+      <c r="E197" s="20" t="s">
+        <v>128</v>
+      </c>
+      <c r="F197" s="32" t="s">
+        <v>37</v>
+      </c>
+      <c r="G197" s="20">
+        <v>2025</v>
+      </c>
+      <c r="H197" s="12">
+        <v>45778</v>
+      </c>
+      <c r="I197" s="12">
+        <v>45863</v>
+      </c>
+      <c r="J197" s="20">
+        <v>49.1205</v>
+      </c>
+      <c r="K197" s="20">
+        <v>-14011.498799999999</v>
+      </c>
+      <c r="L197" s="20">
+        <v>0.57116860000000003</v>
+      </c>
+      <c r="M197" s="20">
+        <v>-162.92440400000001</v>
+      </c>
+      <c r="N197" s="20">
+        <v>33.927250000000001</v>
+      </c>
+      <c r="O197" s="20">
+        <v>18.1866877</v>
+      </c>
+      <c r="P197" s="20">
+        <v>27.29</v>
+      </c>
+      <c r="Q197" s="20">
+        <v>5.6550000000000002</v>
+      </c>
+      <c r="R197" s="20">
+        <v>6</v>
+      </c>
+      <c r="S197" s="20">
+        <v>8</v>
+      </c>
+      <c r="T197" s="20">
+        <v>0.32291667000000002</v>
+      </c>
+      <c r="U197" s="20">
+        <v>0.21110507000000001</v>
+      </c>
+      <c r="V197" s="20">
+        <v>86</v>
+      </c>
+      <c r="W197" s="20">
+        <v>3.02734375</v>
+      </c>
+      <c r="X197" s="32"/>
+      <c r="Y197" s="41">
+        <v>42.058399000000001</v>
+      </c>
+      <c r="Z197" s="41">
+        <v>-70.161844000000002</v>
+      </c>
+      <c r="AA197" s="42">
+        <v>0.56209150299999999</v>
+      </c>
+      <c r="AB197" s="42">
+        <v>31</v>
+      </c>
+      <c r="AC197" s="42">
+        <v>31</v>
+      </c>
+      <c r="AD197" s="42">
+        <v>25</v>
+      </c>
+      <c r="AE197" s="42">
+        <v>0</v>
+      </c>
+      <c r="AF197" s="42">
+        <v>0</v>
+      </c>
+      <c r="AG197" s="42">
+        <v>3</v>
+      </c>
+      <c r="AH197" s="42" t="s">
+        <v>173</v>
+      </c>
+      <c r="AI197" s="42" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
